--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -14,9 +14,10 @@
     <sheet name="Mar 2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Apr 2026" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="May 2026" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2026 Incident Data" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Bucket Mapping" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Notes &amp; Methodology" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Jun 2026" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026 Incident Data" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Bucket Mapping" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Notes &amp; Methodology" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -544,14 +545,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1. January: 4 outages (5 min); February: 3 outages (9 min); March: 7 outages (57 min); April: 4 outages (25 min)</t>
+          <t>1. Jan: 4 outages (5 min); Feb: 3 outages (9 min); Mar: 7 outages (57 min); Apr: 4 outages (25 min); May: 2 outages (4 min)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Completed Months: January - April 2026 (May in progress, partial through May 16)</t>
+          <t>Completed Months: January - May 2026 (June in progress)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -563,31 +564,31 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>YTD Outages: 18 incidents (completed months)</t>
+          <t>YTD Outages: 20 incidents (completed months)</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>3. SAST Aviator (EU/AMS) continued brief outage pattern: Mar 11, 13, 17, 18 and Apr 9 (EU SAST, 2 min)</t>
+          <t>3. SAST Aviator (EU/AMS) continued brief outage pattern: Mar 11, 13, 17, 18; Apr 9 EU SAST 2 min; May 9 EU SAST 2 min, May 10 AMS SAST 2 min</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>YTD Outage Time: 96 minutes (1.60 hours) (completed months)</t>
+          <t>YTD Outage Time: 100 minutes (1.67 hours) (completed months)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>4. YTD uptime of 99.9444% continues to exceed the 99.9% SLA target across all four completed months</t>
+          <t>4. YTD uptime of 99.9540% continues to exceed the 99.9% SLA target across all five completed months</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>YTD Uptime: 99.9444% (completed months only)</t>
+          <t>YTD Uptime: 99.9540% (completed months only)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -712,22 +713,16 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>2*</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>4*</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>0.07*</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="n">
+      <c r="B19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E19" s="6" t="n">
         <v>0.999910394265233</v>
       </c>
     </row>
@@ -739,23 +734,21 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0*</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0*</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0.0*</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -927,71 +920,71 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.9994444444444445</v>
+        <v>0.9995401030169242</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* May 2026 is in progress. Partial data through May 16, 2026. Will be finalized after May 31, 2026.</t>
+          <t>* June 2026 is in progress. Will be finalized after June 30, 2026.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026 SLA Performance (Completed Months: Jan - Apr)</t>
+          <t>2026 SLA Performance (Completed Months: Jan - May)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Total Period Minutes (completed): 172,800</t>
+          <t>Total Period Minutes (completed): 217,440</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Total Outage Minutes: 96</t>
+          <t>Total Outage Minutes: 100</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Uptime Minutes: 172,704</t>
+          <t>Uptime Minutes: 217,340</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Uptime Percentage: 99.9444%</t>
+          <t>Uptime Percentage: 99.9540%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Outage Count: 18 incidents</t>
+          <t>Outage Count: 20 incidents</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Average Outage Duration: 5.33 minutes</t>
+          <t>Average Outage Duration: 5.00 minutes</t>
         </is>
       </c>
     </row>
@@ -1015,6 +1008,400 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Component Contains</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP Portal</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP API</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>FedRAMP</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AMS Portal</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>API - AMS</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AMS API</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>EMEA Portal</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>API - EMEA</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>EMEA API</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - APAC</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>APAC Portal</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>API - APAC</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>APAC API</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>APAC</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>SGP Portal</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>API - SGP</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>SGP API</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Vulncat</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Vulncat</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>EU SAST Aviator</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>AMS SAST Aviator</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>AMS</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Tenant Portal - EU</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>EU Portal</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>API - EU</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>EU API</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Debricked Fortify Integration</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Debricked Fortify Integration</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1064,7 +1451,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: May 16, 2026 (mid-month snapshot through May 16; 2 outages added: AMS SAST Aviator May 10 2 min, EU SAST Aviator May 9 2 min; maintenance added: APAC May 4, AMS May 8, SGP May 11-12; service degradation events: AMS May 7-8 and May 13; Apr 22 - May 4 AMS service degradation back-filled to April data).</t>
+          <t>Last updated: June 2, 2026 (May 2026 finalized; no outage events May 17-31; maintenance added: APAC/SGP May 27 BST, EMEA May 27-28 BST, EU/FedRAMP/AMS May 28 BST; service degradation May 14-26 AMS added).</t>
         </is>
       </c>
     </row>
@@ -1751,7 +2138,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Last updated: May 16, 2026</t>
+          <t>Last updated: June 2, 2026</t>
         </is>
       </c>
     </row>
@@ -1917,13 +2304,11 @@
       <c r="E5" s="12" t="n">
         <v>0.9999305555555555</v>
       </c>
-      <c r="F5" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
@@ -1956,7 +2341,7 @@
         </is>
       </c>
       <c r="N5" s="12" t="n">
-        <v>0.9997280092592593</v>
+        <v>0.9997838484179544</v>
       </c>
     </row>
     <row r="6">
@@ -1977,13 +2362,11 @@
       <c r="E6" s="12" t="n">
         <v>0.9999537037037037</v>
       </c>
-      <c r="F6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
@@ -2016,7 +2399,7 @@
         </is>
       </c>
       <c r="N6" s="12" t="n">
-        <v>0.9999421296296296</v>
+        <v>0.9999540103016924</v>
       </c>
     </row>
     <row r="7">
@@ -2037,13 +2420,11 @@
       <c r="E7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
@@ -2097,13 +2478,11 @@
       <c r="E8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
@@ -2157,13 +2536,11 @@
       <c r="E9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
@@ -2217,13 +2594,11 @@
       <c r="E10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
@@ -2277,13 +2652,11 @@
       <c r="E11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
@@ -2337,13 +2710,11 @@
       <c r="E12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
@@ -2397,13 +2768,11 @@
       <c r="E13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
@@ -2457,13 +2826,11 @@
       <c r="E14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
@@ -2496,7 +2863,7 @@
         </is>
       </c>
       <c r="N14" s="12" t="n">
-        <v>0.9999710648148148</v>
+        <v>0.9999770051508462</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2884,11 @@
       <c r="E15" s="12" t="n">
         <v>0.9997685185185186</v>
       </c>
-      <c r="F15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
@@ -2556,7 +2921,7 @@
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>0.9999421296296296</v>
+        <v>0.9999540103016924</v>
       </c>
     </row>
     <row r="16">
@@ -2577,13 +2942,11 @@
       <c r="E16" s="12" t="n">
         <v>0.9997685185185186</v>
       </c>
-      <c r="F16" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
@@ -2616,7 +2979,7 @@
         </is>
       </c>
       <c r="N16" s="12" t="n">
-        <v>0.9999421296296296</v>
+        <v>0.9999540103016924</v>
       </c>
     </row>
     <row r="18">
@@ -2716,13 +3079,11 @@
       <c r="E20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="12" t="n">
         <v>0.9999551971326165</v>
       </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
@@ -2755,7 +3116,7 @@
         </is>
       </c>
       <c r="N20" s="12" t="n">
-        <v>0.9999247685185185</v>
+        <v>0.9999310154525386</v>
       </c>
     </row>
     <row r="21">
@@ -2776,13 +3137,11 @@
       <c r="E21" s="12" t="n">
         <v>0.9999537037037037</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="12" t="n">
         <v>0.9999551971326165</v>
       </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G21" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
@@ -2815,7 +3174,7 @@
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>0.9999479166666667</v>
+        <v>0.9999494113318617</v>
       </c>
     </row>
     <row r="23">
@@ -2915,13 +3274,11 @@
       <c r="E25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
@@ -2975,13 +3332,11 @@
       <c r="E26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
@@ -3014,13 +3369,13 @@
         </is>
       </c>
       <c r="N26" s="12" t="n">
-        <v>0.999994212962963</v>
+        <v>0.9999954010301693</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* May 2026 is in progress. Partial data shown in italics.</t>
+          <t>* June 2026 is in progress. Partial data shown in italics.</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4514,232 +4869,225 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>May 2026 - Monthly Detail (Partial)</t>
+          <t>May 2026 - Monthly Detail</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Month in progress. Partial data through May 16, 2026. To be finalized after May 31, 2026.</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Summary</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Monthly Summary (Partial)</t>
+          <t>Period:</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>May 1 - 31, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Total Minutes:</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>44,640</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Period:</t>
+          <t>Outage Count:</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>May 1 - 31, 2026</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Total Minutes:</t>
+          <t>Outage Minutes:</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>44,640</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Outage Count (to date):</t>
+          <t>Uptime %:</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>99.9910%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Outage Minutes (to date):</t>
+          <t>SLA Status:</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Uptime % (partial, not final):</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>99.9910%</t>
+          <t>MEETING TARGET (99.9%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Status:</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>Daily Outage Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Outage Count</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Outage Minutes</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Uptime Percentage</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Daily Outage Report (Partial)</t>
-        </is>
+      <c r="A14" s="15" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0.9986111111111111</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Outage Count</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Outage Minutes</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Uptime Percentage</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n">
-        <v>46151</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="5" t="n">
+      <c r="A15" s="15" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.9986111111111111</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
-        <v>46152</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>0.9986111111111111</v>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Services Affected</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Services Affected (to date)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Detailed Incidents</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Detailed Incidents (to date)</t>
+          <t>1. May 09, 2026 - Outage (2 minutes)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>1. May 09, 2026 - Outage (2 minutes)</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Time: 7:11 PM GMT-7:13 PM GMT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Service: SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Time: 7:11 PM GMT-7:13 PM GMT</t>
+          <t>Impact: Brief service disruption</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Impact: Brief service disruption</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2. May 10, 2026 - Outage (2 minutes)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2. May 10, 2026 - Outage (2 minutes)</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Time: 9:09 PM GMT-9:11 PM GMT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Service: SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Time: 9:09 PM GMT-9:11 PM GMT</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Impact: Brief service disruption</t>
         </is>
@@ -4756,7 +5104,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>June 2026 - Monthly Detail (Partial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Month in progress. Will be finalized after June 30, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Summary (Partial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Period:</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>June 1 - 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Total Minutes:</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>43,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Outage Count (to date):</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Outage Minutes (to date):</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Uptime % (partial, not final):</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>100.0000%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Status:</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4802,17 +5264,17 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -4821,7 +5283,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -4832,17 +5294,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -4851,7 +5313,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -4867,21 +5329,21 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>673</v>
+        <v>57</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -4897,21 +5359,21 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>673</v>
+        <v>57</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -4922,26 +5384,26 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10T21:09:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>May 10, 2026 9:11 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -4952,26 +5414,26 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09T19:11:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>May 09, 2026 7:13 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -4987,21 +5449,21 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -5017,21 +5479,21 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -5042,26 +5504,26 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1395</v>
+        <v>122</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -5072,26 +5534,26 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1395</v>
+        <v>122</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -5107,21 +5569,21 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -5137,21 +5599,21 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -5162,17 +5624,17 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -5181,28 +5643,28 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>162</v>
+        <v>17374</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -5211,71 +5673,71 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>162</v>
+        <v>17374</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -5287,25 +5749,25 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>88</v>
+        <v>673</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -5317,85 +5779,85 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>88</v>
+        <v>673</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-10T21:09:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 10, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -5407,25 +5869,25 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>273</v>
+        <v>132</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -5437,85 +5899,85 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>273</v>
+        <v>132</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>273</v>
+        <v>1395</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>273</v>
+        <v>1395</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -5527,25 +5989,25 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>242</v>
+        <v>72</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -5557,42 +6019,42 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>242</v>
+        <v>72</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -5601,7 +6063,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>17272</v>
+        <v>162</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -5612,17 +6074,17 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -5631,7 +6093,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>17272</v>
+        <v>162</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -5647,21 +6109,21 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1187</v>
+        <v>78</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -5677,21 +6139,21 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1187</v>
+        <v>78</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -5707,21 +6169,21 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>4284</v>
+        <v>88</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -5737,21 +6199,21 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>4284</v>
+        <v>88</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -5762,26 +6224,26 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:28:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -5792,26 +6254,26 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:26:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -5827,21 +6289,21 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>96</v>
+        <v>273</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -5857,21 +6319,21 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>30</v>
+        <v>273</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -5882,26 +6344,26 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>273</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -5917,21 +6379,21 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -5942,26 +6404,26 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>2</v>
+        <v>242</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -5972,26 +6434,26 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>3</v>
+        <v>242</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -6007,12 +6469,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -6021,7 +6483,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>78</v>
+        <v>17272</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -6032,26 +6494,26 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>50</v>
+        <v>17272</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -6067,21 +6529,21 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>50</v>
+        <v>1187</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
@@ -6097,25 +6559,25 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>203</v>
+        <v>1187</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -6127,25 +6589,25 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>203</v>
+        <v>4284</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -6157,85 +6619,85 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>150</v>
+        <v>4284</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -6247,25 +6709,25 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -6277,55 +6739,55 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -6337,145 +6799,145 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -6487,25 +6949,25 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -6517,21 +6979,21 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
@@ -6542,26 +7004,26 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>2</v>
+        <v>203</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
@@ -6572,26 +7034,26 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
@@ -6602,26 +7064,26 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -6637,21 +7099,21 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -6667,21 +7129,21 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -6697,21 +7159,21 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -6727,21 +7189,21 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -6757,21 +7219,21 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
@@ -6787,21 +7249,21 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
@@ -6817,21 +7279,21 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
@@ -6847,21 +7309,21 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
@@ -6872,26 +7334,26 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -6907,21 +7369,21 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
@@ -6932,26 +7394,26 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
@@ -6967,21 +7429,21 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
@@ -6997,21 +7459,21 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
@@ -7027,21 +7489,21 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
@@ -7052,26 +7514,26 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -7082,30 +7544,30 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -7117,25 +7579,25 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -7147,25 +7609,25 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -7177,25 +7639,25 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -7207,85 +7669,85 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -7297,12 +7759,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -7311,11 +7773,11 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>282</v>
+        <v>95</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7789,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -7341,88 +7803,88 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>282</v>
+        <v>95</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -7431,28 +7893,28 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -7461,67 +7923,67 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
@@ -7537,25 +7999,25 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>4234</v>
+        <v>207</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7567,145 +8029,145 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>4234</v>
+        <v>207</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1595</v>
+        <v>2</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1595</v>
+        <v>2</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7717,55 +8179,55 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>4982</v>
+        <v>282</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7777,85 +8239,85 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1070</v>
+        <v>127</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7867,25 +8329,25 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7897,25 +8359,25 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7927,25 +8389,25 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -7957,21 +8419,21 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>137</v>
+        <v>4234</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
@@ -7987,21 +8449,21 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>38</v>
+        <v>4234</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
@@ -8012,431 +8474,457 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:46:00Z</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:45:00Z</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T16:24:00Z</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>4982</v>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T15:14:00Z</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T21:13:00Z</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:24:00Z</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-10T15:08:00Z</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E109" s="5" t="n">
+      <c r="E123" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F109" s="5" t="inlineStr">
+      <c r="F123" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: May 16, 2026</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>Component Contains</t>
-        </is>
-      </c>
-      <c r="B1" s="17" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="C1" s="17" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="D1" s="17" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>FedRAMP Portal</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>FedRAMP</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>FedRAMP API</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>FedRAMP</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>AMS Portal</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>AMS</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>API - AMS</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>AMS API</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>AMS</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>EMEA Portal</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>API - EMEA</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>EMEA API</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - APAC</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>APAC Portal</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>APAC</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>API - APAC</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>APAC API</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>APAC</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - SGP</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>SGP Portal</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>API - SGP</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>SGP API</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Vulncat</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Vulncat</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>EU SAST Aviator</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>AMS SAST Aviator</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>AMS</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Tenant Portal - EU</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>EU Portal</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>API - EU</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>EU API</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Debricked Fortify Integration</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Debricked Fortify Integration</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Service</t>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: June 02, 2026</t>
         </is>
       </c>
     </row>

--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -545,14 +545,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1. Jan: 4 outages (5 min); Feb: 3 outages (9 min); Mar: 7 outages (57 min); Apr: 4 outages (25 min); May: 2 outages (4 min)</t>
+          <t>1. Jan: 4 outages (5 min); Feb: 3 outages (9 min); Mar: 7 outages (57 min); Apr: 4 outages (25 min); May: 2 outages (4 min); Jun (partial thru Jun 16): 2 outages (4 min)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Completed Months: January - May 2026 (June in progress)</t>
+          <t>Completed Months: January - May 2026 (June partial through Jun 16, 2026)</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>3. SAST Aviator (EU/AMS) continued brief outage pattern: Mar 11, 13, 17, 18; Apr 9 EU SAST 2 min; May 9 EU SAST 2 min, May 10 AMS SAST 2 min</t>
+          <t>3. SAST Aviator (EU/AMS) continued brief outage pattern: Mar 11, 13, 17, 18; Apr 9 EU SAST 2 min; May 9 EU SAST 2 min, May 10 AMS SAST 2 min; Jun 8 EU SAST 2 min, Jun 9 AMS SAST 2 min</t>
         </is>
       </c>
     </row>
@@ -734,21 +734,21 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>0*</t>
+          <t>2*</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>0*</t>
+          <t>4*</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>0.0*</t>
+          <t>0.07*</t>
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>1</v>
+        <v>0.9999074074074074</v>
       </c>
     </row>
     <row r="21">
@@ -935,7 +935,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* June 2026 is in progress. Will be finalized after June 30, 2026.</t>
+          <t>* June 2026 is in progress (partial through June 16, 2026). Will be finalized after June 30, 2026.</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: June 2, 2026 (May 2026 finalized; no outage events May 17-31; maintenance added: APAC/SGP May 27 BST, EMEA May 27-28 BST, EU/FedRAMP/AMS May 28 BST; service degradation May 14-26 AMS added).</t>
+          <t>Last updated: June 16, 2026 (mid-month update; Jun 2026 partial data added through Jun 16: 2 outages (EU SAST Aviator Jun 8 2 min, AMS SAST Aviator Jun 9 2 min) + AMS service degradation Jun 9-10; times converted from BST to GMT).</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Last updated: June 2, 2026</t>
+          <t>Last updated: June 16, 2026</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
         <v>0.9999551971326165</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>1</v>
+        <v>0.9999537037037037</v>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>0.9999551971326165</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1</v>
+        <v>0.9999537037037037</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Month in progress. Will be finalized after June 30, 2026.</t>
+          <t>Month in progress. Partial data through June 16, 2026. Will be finalized after June 30, 2026.</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>100.0000%</t>
+          <t>99.9907%</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5264,120 +5264,120 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-09T21:09:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 09, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>106</v>
+        <v>1789</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>57</v>
+        <v>1789</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-08T19:11:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 08, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -5389,21 +5389,21 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -5419,21 +5419,21 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -5449,21 +5449,21 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -5479,21 +5479,21 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -5539,21 +5539,21 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -5569,21 +5569,21 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -5599,21 +5599,21 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -5624,26 +5624,26 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>17374</v>
+        <v>122</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -5654,26 +5654,26 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>17374</v>
+        <v>122</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -5684,26 +5684,26 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -5714,26 +5714,26 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -5744,26 +5744,26 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>673</v>
+        <v>17374</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -5774,26 +5774,26 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>673</v>
+        <v>17374</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -5804,26 +5804,26 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10T21:09:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>May 10, 2026 9:11 PM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -5834,26 +5834,26 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09T19:11:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>May 09, 2026 7:13 PM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -5869,21 +5869,21 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>132</v>
+        <v>673</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>132</v>
+        <v>673</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -5924,26 +5924,26 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-10T21:09:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 10, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1395</v>
+        <v>2</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -5954,26 +5954,26 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1395</v>
+        <v>2</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -5989,21 +5989,21 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -6019,21 +6019,21 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -6044,17 +6044,17 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -6063,28 +6063,28 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>162</v>
+        <v>1395</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -6093,11 +6093,11 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>162</v>
+        <v>1395</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -6109,25 +6109,25 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -6139,25 +6139,25 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -6169,21 +6169,21 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -6199,21 +6199,21 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -6229,21 +6229,21 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -6259,21 +6259,21 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -6289,21 +6289,21 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>273</v>
+        <v>88</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -6319,21 +6319,21 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>273</v>
+        <v>88</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -6349,21 +6349,21 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>273</v>
+        <v>73</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -6379,21 +6379,21 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>273</v>
+        <v>73</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -6409,21 +6409,21 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -6439,21 +6439,21 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -6464,26 +6464,26 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>17272</v>
+        <v>273</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -6494,26 +6494,26 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>17272</v>
+        <v>273</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -6529,21 +6529,21 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1187</v>
+        <v>242</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
@@ -6559,21 +6559,21 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1187</v>
+        <v>242</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -6584,17 +6584,17 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>4284</v>
+        <v>17272</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -6614,17 +6614,17 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>4284</v>
+        <v>17272</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -6644,17 +6644,17 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:28:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -6663,7 +6663,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>10</v>
+        <v>1187</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -6674,17 +6674,17 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:26:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>10</v>
+        <v>1187</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -6709,21 +6709,21 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>96</v>
+        <v>4284</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>30</v>
+        <v>4284</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -6769,21 +6769,21 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -6794,26 +6794,26 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>211</v>
+        <v>10</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
@@ -6824,26 +6824,26 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
@@ -6854,26 +6854,26 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
@@ -6884,26 +6884,26 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
@@ -6919,21 +6919,21 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>50</v>
+        <v>211</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
@@ -6944,17 +6944,17 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
@@ -6974,60 +6974,60 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>203</v>
+        <v>3</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -7039,25 +7039,25 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -7069,25 +7069,25 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -7099,21 +7099,21 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -7159,21 +7159,21 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -7219,21 +7219,21 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
@@ -7249,21 +7249,21 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
@@ -7279,21 +7279,21 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
@@ -7309,21 +7309,21 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
@@ -7334,17 +7334,17 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -7369,21 +7369,21 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>198</v>
+        <v>42</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
@@ -7399,21 +7399,21 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
@@ -7424,26 +7424,26 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
@@ -7459,12 +7459,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
@@ -7484,26 +7484,26 @@
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>4</v>
+        <v>198</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
@@ -7519,21 +7519,21 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -7544,26 +7544,26 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
@@ -7574,26 +7574,26 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
@@ -7604,26 +7604,26 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
@@ -7639,21 +7639,21 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
@@ -7669,21 +7669,21 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
@@ -7699,21 +7699,21 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
@@ -7729,21 +7729,21 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
@@ -7759,21 +7759,21 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
@@ -7789,21 +7789,21 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
@@ -7814,26 +7814,26 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
@@ -7844,26 +7844,26 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
@@ -7874,26 +7874,26 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
@@ -7904,26 +7904,26 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
@@ -7939,12 +7939,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
@@ -7969,17 +7969,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -7987,123 +7987,123 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>207</v>
+        <v>31</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>207</v>
+        <v>2</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>159</v>
+        <v>5</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
@@ -8114,26 +8114,26 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>207</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
@@ -8144,26 +8144,26 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>207</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
@@ -8179,21 +8179,21 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>282</v>
+        <v>159</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
@@ -8209,21 +8209,21 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>282</v>
+        <v>159</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
@@ -8234,26 +8234,26 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
@@ -8264,26 +8264,26 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
@@ -8299,21 +8299,21 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>98</v>
+        <v>282</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
@@ -8329,21 +8329,21 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>98</v>
+        <v>282</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -8359,21 +8359,21 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
@@ -8389,21 +8389,21 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
@@ -8419,25 +8419,25 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>4234</v>
+        <v>98</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -8449,85 +8449,85 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>4234</v>
+        <v>98</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -8539,21 +8539,21 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1595</v>
+        <v>4234</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
@@ -8569,21 +8569,21 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1595</v>
+        <v>4234</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
@@ -8594,26 +8594,26 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-01-27T14:46:00Z</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>4982</v>
+        <v>1</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
@@ -8629,17 +8629,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-01-27T14:45:00Z</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -8659,21 +8659,21 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1070</v>
+        <v>1595</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
@@ -8684,26 +8684,26 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>1595</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
@@ -8714,17 +8714,17 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-01-16T16:24:00Z</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -8733,7 +8733,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>4982</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
@@ -8744,26 +8744,26 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-16T15:14:00Z</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
@@ -8779,21 +8779,21 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-15T21:13:00Z</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>140</v>
+        <v>1070</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
@@ -8804,26 +8804,26 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-15T04:24:00Z</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
@@ -8834,26 +8834,26 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-10T15:08:00Z</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
@@ -8869,21 +8869,21 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-01-08T04:54:00Z</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
@@ -8899,32 +8899,152 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E123" s="5" t="n">
+      <c r="E127" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: June 02, 2026</t>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: June 16, 2026</t>
         </is>
       </c>
     </row>

--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -15,9 +15,10 @@
     <sheet name="Apr 2026" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="May 2026" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Jun 2026" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2026 Incident Data" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Bucket Mapping" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Notes &amp; Methodology" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Jul 2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026 Incident Data" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Bucket Mapping" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Notes &amp; Methodology" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,26 +546,26 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1. Jan: 4 outages (5 min); Feb: 3 outages (9 min); Mar: 7 outages (57 min); Apr: 4 outages (25 min); May: 2 outages (4 min); Jun (partial thru Jun 16): 2 outages (4 min)</t>
+          <t>1. Jan: 4 outages (5 min); Feb: 3 (9 min); Mar: 7 (57 min); Apr: 4 (25 min); May: 2 (4 min); Jun: 2 (4 min)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Completed Months: January - May 2026 (June partial through Jun 16, 2026)</t>
+          <t>Completed Months: January - June 2026</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2. March 2 remains the worst single day in 2026 (FedRAMP Portal/API, 44 min); April 16 EU Portal/API outage (10 min) was the largest April incident</t>
+          <t>2. March 2 remains the worst single day in 2026 (FedRAMP Portal/API, 44 min); April 16 EU Portal/API outage (10 min) was the largest April incident; Jun had no outages beyond the 2 brief SAST events on Jun 8-9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>YTD Outages: 20 incidents (completed months)</t>
+          <t>YTD Outages: 22 incidents (completed months)</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -576,24 +577,24 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>YTD Outage Time: 100 minutes (1.67 hours) (completed months)</t>
+          <t>YTD Outage Time: 104 minutes (1.73 hours) (completed months)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>4. YTD uptime of 99.9540% continues to exceed the 99.9% SLA target across all five completed months</t>
+          <t>4. YTD uptime of 99.9601% continues to exceed the 99.9% SLA target across all six completed months</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>YTD Uptime: 99.9540% (completed months only)</t>
+          <t>YTD Uptime: 99.9601% (completed months only)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5. SAST Aviator (EU/AMS) accounts for the majority of incidents across all months; FedRAMP had the single worst day on Mar 2 (44 min)</t>
+          <t>5. Jun 24-25 saw a large scheduled maintenance window across EMEA, EU, AMS, APAC, SGP with no associated outages; FedRAMP maintained on Jun 27</t>
         </is>
       </c>
     </row>
@@ -732,22 +733,16 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>2*</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>4*</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>0.07*</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="n">
+      <c r="B20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E20" s="6" t="n">
         <v>0.9999074074074074</v>
       </c>
     </row>
@@ -759,23 +754,21 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0*</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0*</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0.0*</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -920,71 +913,71 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.9995401030169242</v>
+        <v>0.9996009821976672</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* June 2026 is in progress (partial through June 16, 2026). Will be finalized after June 30, 2026.</t>
+          <t>* July 2026 is in progress. Will be finalized after July 31, 2026.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026 SLA Performance (Completed Months: Jan - May)</t>
+          <t>2026 SLA Performance (Completed Months: Jan - Jun)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Total Period Minutes (completed): 217,440</t>
+          <t>Total Period Minutes (completed): 260,640</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Total Outage Minutes: 100</t>
+          <t>Total Outage Minutes: 104</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Uptime Minutes: 217,340</t>
+          <t>Uptime Minutes: 260,536</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Uptime Percentage: 99.9540%</t>
+          <t>Uptime Percentage: 99.9601%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Outage Count: 20 incidents</t>
+          <t>Outage Count: 22 incidents</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Average Outage Duration: 5.00 minutes</t>
+          <t>Average Outage Duration: 4.73 minutes</t>
         </is>
       </c>
     </row>
@@ -1008,6 +1001,4507 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F150"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Event Type</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Start Date Time</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>End Date Time</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>Duration Minutes</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T00:18:00Z</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-27T00:18:00Z</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T18:24:00Z</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T18:24:00Z</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T18:23:00Z</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EU</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T18:23:00Z</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EU</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T04:06:00Z</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T04:06:00Z</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T00:26:00Z</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EU</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-25T00:26:00Z</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EU</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T23:19:00Z</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T23:19:00Z</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T13:57:00Z</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T13:57:00Z</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - SGP</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T13:51:00Z</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-24T13:51:00Z</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - APAC</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-23T17:55:00Z</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Jun 23, 2026 6:45 PM GMT</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T21:08:00Z</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Jun 22, 2026 9:40 PM GMT</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-11T11:50:00Z</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>20253</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-11T11:50:00Z</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>20253</v>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09T21:09:00Z</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Jun 09, 2026 9:11 PM GMT</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09T16:55:00Z</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>1789</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09T16:55:00Z</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1789</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-08T19:11:00Z</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Jun 08, 2026 7:13 PM GMT</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04T21:22:00Z</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>903</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04T21:22:00Z</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>903</v>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28T03:57:00Z</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>May 28, 2026 5:43 AM GMT</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28T03:57:00Z</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>May 28, 2026 5:43 AM GMT</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28T02:06:00Z</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>May 28, 2026 3:03 AM GMT</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28T02:06:00Z</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>May 28, 2026 3:03 AM GMT</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28T01:07:00Z</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>May 28, 2026 1:40 AM GMT</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EU</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-28T01:07:00Z</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>May 28, 2026 1:40 AM GMT</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EU</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27T23:50:00Z</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>May 28, 2026 1:06 AM GMT</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27T23:50:00Z</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>May 28, 2026 1:06 AM GMT</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27T15:12:00Z</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>May 27, 2026 5:14 PM GMT</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27T15:12:00Z</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>May 27, 2026 5:14 PM GMT</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - APAC</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27T15:12:00Z</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>May 27, 2026 5:14 PM GMT</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-27T15:12:00Z</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>May 27, 2026 5:14 PM GMT</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - SGP</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14T12:22:00Z</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>May 26, 2026 1:56 PM GMT</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>17374</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14T12:22:00Z</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>May 26, 2026 1:56 PM GMT</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>17374</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13T14:30:00Z</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>May 13, 2026 2:35 PM GMT</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13T14:30:00Z</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>May 13, 2026 2:35 PM GMT</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11T14:06:00Z</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>May 12, 2026 1:19 AM GMT</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>673</v>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11T14:06:00Z</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>May 12, 2026 1:19 AM GMT</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - SGP</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>673</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10T21:09:00Z</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>May 10, 2026 9:11 PM GMT</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09T19:11:00Z</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>May 09, 2026 7:13 PM GMT</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-08T09:39:00Z</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>May 08, 2026 11:51 AM GMT</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-08T09:39:00Z</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>May 08, 2026 11:51 AM GMT</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07T19:05:00Z</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>May 08, 2026 6:20 PM GMT</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>1395</v>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07T19:05:00Z</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>May 08, 2026 6:20 PM GMT</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>1395</v>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04T17:22:00Z</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>May 04, 2026 6:34 PM GMT</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-04T17:22:00Z</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>May 04, 2026 6:34 PM GMT</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - APAC</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30T03:17:00Z</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30T03:17:00Z</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30T00:52:00Z</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30T00:52:00Z</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30T00:20:00Z</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EU</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30T00:20:00Z</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EU</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29T22:53:00Z</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29T22:53:00Z</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29T15:45:00Z</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29T15:45:00Z</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - APAC</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29T15:45:00Z</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29T15:45:00Z</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - SGP</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24T18:12:00Z</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-24T18:12:00Z</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22T16:29:00Z</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>May 04, 2026 4:21 PM GMT</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>17272</v>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-22T16:29:00Z</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>May 04, 2026 4:21 PM GMT</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>17272</v>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21T20:43:00Z</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EU</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>1187</v>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21T20:43:00Z</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EU</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>1187</v>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-17T22:57:00Z</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>4284</v>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-17T22:57:00Z</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>4284</v>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16T14:28:00Z</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EU</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16T14:26:00Z</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EU</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10T20:56:00Z</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09T21:04:00Z</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09T19:11:00Z</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09T18:04:00Z</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08T04:10:00Z</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-08T04:09:00Z</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Service Degradation</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-07T18:03:00Z</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02T00:27:00Z</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-02T00:27:00Z</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-26T03:52:00Z</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-26T03:52:00Z</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25T23:07:00Z</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25T23:07:00Z</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25T14:07:00Z</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25T14:07:00Z</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - APAC</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25T14:07:00Z</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-25T14:07:00Z</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - SGP</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-20T21:04:00Z</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-20T17:44:00Z</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:11:00Z</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:11:00Z</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18T00:43:00Z</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-17T22:16:00Z</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-17T22:16:00Z</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-17T19:46:00Z</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-13T00:37:00Z</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-11T23:50:00Z</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05T05:01:00Z</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05T05:01:00Z</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05T01:20:00Z</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05T01:20:00Z</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-04T23:49:00Z</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-04T23:49:00Z</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:35:00Z</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:35:00Z</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - APAC</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:35:00Z</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-04T14:35:00Z</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - SGP</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02T16:51:00Z</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02T16:51:00Z</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02T14:44:00Z</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02T14:42:00Z</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02T14:41:00Z</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-26T16:39:00Z</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - SGP</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-20T15:28:00Z</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-20T15:28:00Z</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - APAC</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-18T19:36:00Z</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-18T19:36:00Z</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-15T19:46:00Z</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-14T22:07:00Z</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T16:28:00Z</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T16:28:00Z</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - SGP</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T04:56:00Z</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T04:56:00Z</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T01:57:00Z</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T01:57:00Z</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-04T23:58:00Z</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-04T23:58:00Z</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30T19:08:00Z</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30T19:08:00Z</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:46:00Z</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:45:00Z</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T16:24:00Z</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>4982</v>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T15:14:00Z</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T21:13:00Z</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:24:00Z</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-10T15:08:00Z</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: July 02, 2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1401,7 +5895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1451,7 +5945,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: June 16, 2026 (mid-month update; Jun 2026 partial data added through Jun 16: 2 outages (EU SAST Aviator Jun 8 2 min, AMS SAST Aviator Jun 9 2 min) + AMS service degradation Jun 9-10; times converted from BST to GMT).</t>
+          <t>Last updated: July 2, 2026 (Jun 2026 finalized: 2 outages (EU SAST Aviator Jun 8 2 min, AMS SAST Aviator Jun 9 2 min), 4 total outage minutes, 99.9907% uptime; new maintenance events Jun 4-5, 22-27 added; AMS service degradation Jun 11-Jun 25 recorded; times converted from BST to GMT).</t>
         </is>
       </c>
     </row>
@@ -2138,7 +6632,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Last updated: June 16, 2026</t>
+          <t>Last updated: July 2, 2026</t>
         </is>
       </c>
     </row>
@@ -2307,41 +6801,39 @@
       <c r="F5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="G5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="M5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N5" s="12" t="n">
-        <v>0.9997838484179544</v>
+        <v>0.9998196746470227</v>
       </c>
     </row>
     <row r="6">
@@ -2365,41 +6857,39 @@
       <c r="F6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="M6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M6" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N6" s="12" t="n">
-        <v>0.9999540103016924</v>
+        <v>0.9999616329036218</v>
       </c>
     </row>
     <row r="7">
@@ -2423,13 +6913,11 @@
       <c r="F7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -2481,13 +6969,11 @@
       <c r="F8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -2539,13 +7025,11 @@
       <c r="F9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -2597,13 +7081,11 @@
       <c r="F10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -2655,13 +7137,11 @@
       <c r="F11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -2713,13 +7193,11 @@
       <c r="F12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -2771,13 +7249,11 @@
       <c r="F13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -2829,41 +7305,39 @@
       <c r="F14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="G14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="M14" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N14" s="12" t="n">
-        <v>0.9999770051508462</v>
+        <v>0.9999808164518109</v>
       </c>
     </row>
     <row r="15">
@@ -2887,41 +7361,39 @@
       <c r="F15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="G15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="K15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K15" s="14" t="inlineStr">
+      <c r="L15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="M15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N15" s="12" t="n">
-        <v>0.9999540103016924</v>
+        <v>0.9999616329036218</v>
       </c>
     </row>
     <row r="16">
@@ -2945,41 +7417,39 @@
       <c r="F16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="L16" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="M16" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N16" s="12" t="n">
-        <v>0.9999540103016924</v>
+        <v>0.9999616329036218</v>
       </c>
     </row>
     <row r="18">
@@ -3082,41 +7552,39 @@
       <c r="F20" s="12" t="n">
         <v>0.9999551971326165</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="12" t="n">
         <v>0.9999537037037037</v>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="K20" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K20" s="14" t="inlineStr">
+      <c r="L20" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L20" s="14" t="inlineStr">
+      <c r="M20" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N20" s="12" t="n">
-        <v>0.9999310154525386</v>
+        <v>0.9999347759361572</v>
       </c>
     </row>
     <row r="21">
@@ -3140,41 +7608,39 @@
       <c r="F21" s="12" t="n">
         <v>0.9999551971326165</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="12" t="n">
         <v>0.9999537037037037</v>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="K21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
+      <c r="L21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L21" s="14" t="inlineStr">
+      <c r="M21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N21" s="12" t="n">
-        <v>0.9999494113318617</v>
+        <v>0.9999501227747084</v>
       </c>
     </row>
     <row r="23">
@@ -3277,13 +7743,11 @@
       <c r="F25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -3335,47 +7799,45 @@
       <c r="F26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="G26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="K26" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K26" s="14" t="inlineStr">
+      <c r="L26" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="M26" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N26" s="12" t="n">
-        <v>0.9999954010301693</v>
+        <v>0.9999961632903622</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* June 2026 is in progress. Partial data shown in italics.</t>
+          <t>* July 2026 is in progress. Partial data shown in italics.</t>
         </is>
       </c>
     </row>
@@ -5104,7 +9566,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="85" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>June 2026 - Monthly Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Period:</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>June 1 - 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Total Minutes:</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>43,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Outage Count:</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Outage Minutes:</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Uptime %:</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>99.9907%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SLA Status:</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>MEETING TARGET (99.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Daily Outage Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Outage Count</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Outage Minutes</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Uptime Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0.9986111111111111</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>0.9986111111111111</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Services Affected</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Detailed Incidents</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>1. June 08, 2026 - Outage (2 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Time: 7:11 PM GMT-7:13 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2. June 09, 2026 - Outage (2 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Time: 9:09 PM GMT-9:11 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5117,21 +9828,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>June 2026 - Monthly Detail (Partial)</t>
+          <t>July 2026 - Monthly Detail (In Progress)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Month in progress. Partial data through June 16, 2026. Will be finalized after June 30, 2026.</t>
+          <t>Month in progress. Will be finalized after July 31, 2026.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Monthly Summary (Partial)</t>
+          <t>Monthly Summary (In Progress)</t>
         </is>
       </c>
     </row>
@@ -5143,7 +9854,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>June 1 - 30, 2026</t>
+          <t>July 1 - 31, 2026</t>
         </is>
       </c>
     </row>
@@ -5155,7 +9866,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>43,200</t>
+          <t>44,640</t>
         </is>
       </c>
     </row>
@@ -5167,7 +9878,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5179,3872 +9890,19 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Uptime % (partial, not final):</t>
+          <t>Status:</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>99.9907%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Status:</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
           <t>IN PROGRESS</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F128"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="B1" s="17" t="inlineStr">
-        <is>
-          <t>Start Date Time</t>
-        </is>
-      </c>
-      <c r="C1" s="17" t="inlineStr">
-        <is>
-          <t>End Date Time</t>
-        </is>
-      </c>
-      <c r="D1" s="17" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="E1" s="17" t="inlineStr">
-        <is>
-          <t>Duration Minutes</t>
-        </is>
-      </c>
-      <c r="F1" s="17" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-09T21:09:00Z</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Jun 09, 2026 9:11 PM GMT</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-09T16:55:00Z</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>1789</v>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-09T16:55:00Z</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1789</v>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-08T19:11:00Z</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Jun 08, 2026 7:13 PM GMT</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-28T03:57:00Z</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-28T03:57:00Z</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-28T02:06:00Z</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-28T02:06:00Z</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-28T01:07:00Z</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-28T01:07:00Z</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EU</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-27T23:50:00Z</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-27T23:50:00Z</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EMEA</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-27T15:12:00Z</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-27T15:12:00Z</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - APAC</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-27T15:12:00Z</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-27T15:12:00Z</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - SGP</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14T12:22:00Z</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>17374</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14T12:22:00Z</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>17374</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-13T14:30:00Z</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-13T14:30:00Z</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11T14:06:00Z</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>673</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-11T14:06:00Z</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - SGP</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>673</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-10T21:09:00Z</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>May 10, 2026 9:11 PM GMT</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-09T19:11:00Z</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>May 09, 2026 7:13 PM GMT</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-08T09:39:00Z</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-08T09:39:00Z</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-07T19:05:00Z</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>1395</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-07T19:05:00Z</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>1395</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-04T17:22:00Z</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-04T17:22:00Z</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - APAC</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30T03:17:00Z</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>162</v>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30T03:17:00Z</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>162</v>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30T00:52:00Z</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30T00:52:00Z</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30T00:20:00Z</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30T00:20:00Z</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EU</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-29T22:53:00Z</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-29T22:53:00Z</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EMEA</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-29T15:45:00Z</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>273</v>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-29T15:45:00Z</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - APAC</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>273</v>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-29T15:45:00Z</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>273</v>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-29T15:45:00Z</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - SGP</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>273</v>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-24T18:12:00Z</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>242</v>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-24T18:12:00Z</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EMEA</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>242</v>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-22T16:29:00Z</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>17272</v>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-22T16:29:00Z</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>17272</v>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-21T20:43:00Z</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>1187</v>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-21T20:43:00Z</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EU</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>1187</v>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-17T22:57:00Z</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>4284</v>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-17T22:57:00Z</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>4284</v>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-16T14:28:00Z</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-16T14:26:00Z</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EU</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-10T20:56:00Z</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-09T21:04:00Z</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-09T19:11:00Z</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-09T18:04:00Z</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>211</v>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-08T04:10:00Z</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-08T04:09:00Z</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Service Degradation</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-07T18:03:00Z</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-02T00:27:00Z</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-02T00:27:00Z</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-26T03:52:00Z</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>203</v>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-26T03:52:00Z</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>203</v>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-25T23:07:00Z</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-25T23:07:00Z</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EMEA</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-25T14:07:00Z</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-25T14:07:00Z</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - APAC</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-25T14:07:00Z</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-25T14:07:00Z</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - SGP</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-20T21:04:00Z</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-20T17:44:00Z</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-18T19:11:00Z</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-18T19:11:00Z</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EMEA</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-18T00:43:00Z</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-17T22:16:00Z</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>198</v>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-17T22:16:00Z</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>198</v>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-17T19:46:00Z</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-13T00:37:00Z</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-11T23:50:00Z</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-05T05:01:00Z</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>164</v>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-05T05:01:00Z</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>164</v>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-05T01:20:00Z</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-05T01:20:00Z</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-04T23:49:00Z</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-04T23:49:00Z</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EMEA</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:35:00Z</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:35:00Z</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - APAC</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:35:00Z</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-04T14:35:00Z</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - SGP</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-02T16:51:00Z</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-02T16:51:00Z</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-02T14:44:00Z</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-02T14:42:00Z</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-02T14:41:00Z</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-26T16:39:00Z</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - SGP</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-20T15:28:00Z</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>207</v>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-20T15:28:00Z</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - APAC</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>207</v>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-18T19:36:00Z</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
-        </is>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B100" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-18T19:36:00Z</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>159</v>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-15T19:46:00Z</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-14T22:07:00Z</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-05T16:28:00Z</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-05T16:28:00Z</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - SGP</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-05T04:56:00Z</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-05T04:56:00Z</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-05T01:57:00Z</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-05T01:57:00Z</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-04T23:58:00Z</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-04T23:58:00Z</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EMEA</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-30T19:08:00Z</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="n">
-        <v>4234</v>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-30T19:08:00Z</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EMEA</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="n">
-        <v>4234</v>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-27T14:46:00Z</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-27T14:45:00Z</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-23T23:57:00Z</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>1595</v>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-23T23:57:00Z</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>1595</v>
-      </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-16T16:24:00Z</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="n">
-        <v>4982</v>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-16T15:14:00Z</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-15T21:13:00Z</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>1070</v>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-15T04:24:00Z</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand - Vulncat</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Outage</t>
-        </is>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-10T15:08:00Z</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-08T04:54:00Z</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-08T04:54:00Z</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - AMS</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-08T01:13:00Z</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="n">
-        <v>137</v>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-08T01:13:00Z</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - FedRAMP</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="n">
-        <v>137</v>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-08T00:24:00Z</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-08T00:24:00Z</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>Fortify on Demand API - EMEA</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: June 16, 2026</t>
         </is>
       </c>
     </row>

--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -754,21 +754,21 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>0*</t>
+          <t>3*</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>0*</t>
+          <t>17*</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>0.0*</t>
+          <t>0.28*</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>1</v>
+        <v>0.9996191756272401</v>
       </c>
     </row>
     <row r="22">
@@ -928,7 +928,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* July 2026 is in progress. Will be finalized after July 31, 2026.</t>
+          <t>* July 2026 is in progress (partial through July 16, 2026). Will be finalized after July 31, 2026.</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1052,90 +1052,90 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-07-08T16:34:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Jul 08, 2026 4:38 PM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-07-07T22:42:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Jul 07, 2026 10:49 PM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-07-06T16:05:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Jul 06, 2026 4:11 PM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1147,21 +1147,21 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>192</v>
+        <v>22</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1177,21 +1177,21 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>164</v>
+        <v>22</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1237,21 +1237,21 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>252</v>
+        <v>192</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1267,21 +1267,21 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>252</v>
+        <v>164</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -1297,21 +1297,21 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>42</v>
+        <v>164</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>42</v>
+        <v>252</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>98</v>
+        <v>252</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -1387,21 +1387,21 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -1417,21 +1417,21 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T17:55:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Jun 23, 2026 6:45 PM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T21:08:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Jun 22, 2026 9:40 PM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -1592,26 +1592,26 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>20253</v>
+        <v>116</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -1622,26 +1622,26 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-06-23T17:55:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jun 23, 2026 6:45 PM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>20253</v>
+        <v>50</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -1652,17 +1652,17 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T21:09:00Z</t>
+          <t>2026-06-22T21:08:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Jun 09, 2026 9:11 PM GMT</t>
+          <t>Jun 22, 2026 9:40 PM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1789</v>
+        <v>20253</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1789</v>
+        <v>20253</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -1747,17 +1747,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-08T19:11:00Z</t>
+          <t>2026-06-09T21:09:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Jun 08, 2026 7:13 PM GMT</t>
+          <t>Jun 09, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -1772,17 +1772,17 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>903</v>
+        <v>1789</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -1802,17 +1802,17 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>903</v>
+        <v>1789</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -1832,30 +1832,30 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-08T19:11:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 08, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -1867,25 +1867,25 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>106</v>
+        <v>903</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -1897,25 +1897,25 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>57</v>
+        <v>903</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -1927,21 +1927,21 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -2047,21 +2047,21 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -2137,21 +2137,21 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
@@ -2192,26 +2192,26 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>17374</v>
+        <v>122</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -2222,26 +2222,26 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>17374</v>
+        <v>122</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -2252,26 +2252,26 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -2287,21 +2287,21 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>5</v>
+        <v>17374</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -2312,26 +2312,26 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>673</v>
+        <v>17374</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
@@ -2342,26 +2342,26 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>673</v>
+        <v>5</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -2372,26 +2372,26 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10T21:09:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>May 10, 2026 9:11 PM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -2402,26 +2402,26 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09T19:11:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>May 09, 2026 7:13 PM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2</v>
+        <v>673</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>132</v>
+        <v>673</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -2462,26 +2462,26 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-10T21:09:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 10, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -2492,26 +2492,26 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1395</v>
+        <v>2</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
@@ -2522,26 +2522,26 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1395</v>
+        <v>132</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -2557,21 +2557,21 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -2582,26 +2582,26 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>72</v>
+        <v>1395</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
@@ -2612,30 +2612,30 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>162</v>
+        <v>1395</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -2647,25 +2647,25 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -2677,25 +2677,25 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -2707,21 +2707,21 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
@@ -2737,21 +2737,21 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
@@ -2797,21 +2797,21 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
@@ -2827,21 +2827,21 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
@@ -2857,21 +2857,21 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>273</v>
+        <v>88</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -2887,21 +2887,21 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>273</v>
+        <v>73</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>273</v>
+        <v>73</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -2977,21 +2977,21 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
@@ -3032,26 +3032,26 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>17272</v>
+        <v>273</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
@@ -3062,26 +3062,26 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>17272</v>
+        <v>242</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
@@ -3097,21 +3097,21 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1187</v>
+        <v>242</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
@@ -3122,26 +3122,26 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1187</v>
+        <v>17272</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -3152,26 +3152,26 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>4284</v>
+        <v>17272</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
@@ -3187,21 +3187,21 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>4284</v>
+        <v>1187</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
@@ -3212,26 +3212,26 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:28:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>10</v>
+        <v>1187</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
@@ -3242,26 +3242,26 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:26:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>10</v>
+        <v>4284</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>96</v>
+        <v>4284</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
@@ -3302,26 +3302,26 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -3337,21 +3337,21 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
@@ -3367,21 +3367,21 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>211</v>
+        <v>96</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
@@ -3392,26 +3392,26 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
@@ -3452,26 +3452,26 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
@@ -3482,26 +3482,26 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
@@ -3512,26 +3512,26 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
@@ -3542,17 +3542,17 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3561,11 +3561,11 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3577,25 +3577,25 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3607,25 +3607,25 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3637,21 +3637,21 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
@@ -3697,21 +3697,21 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
@@ -3727,21 +3727,21 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -3787,21 +3787,21 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
@@ -3847,21 +3847,21 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
@@ -3902,26 +3902,26 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
@@ -3937,21 +3937,21 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
@@ -3967,21 +3967,21 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
@@ -3997,21 +3997,21 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
@@ -4022,26 +4022,26 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>4</v>
+        <v>198</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
@@ -4052,26 +4052,26 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>4</v>
+        <v>198</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
@@ -4082,26 +4082,26 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
@@ -4112,26 +4112,26 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>164</v>
+        <v>4</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -4142,26 +4142,26 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
@@ -4177,21 +4177,21 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
@@ -4297,21 +4297,21 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
@@ -4327,21 +4327,21 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -4382,26 +4382,26 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
@@ -4412,26 +4412,26 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
@@ -4442,26 +4442,26 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
@@ -4477,21 +4477,21 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
@@ -4537,111 +4537,111 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>207</v>
+        <v>2</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>207</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>159</v>
+        <v>5</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
@@ -4682,26 +4682,26 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>207</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
@@ -4712,26 +4712,26 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
@@ -4747,21 +4747,21 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>282</v>
+        <v>159</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
@@ -4772,26 +4772,26 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>282</v>
+        <v>2</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
@@ -4802,26 +4802,26 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>127</v>
+        <v>282</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
@@ -4867,21 +4867,21 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>98</v>
+        <v>282</v>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
@@ -4927,21 +4927,21 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
@@ -4957,21 +4957,21 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
@@ -4987,25 +4987,25 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>4234</v>
+        <v>98</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5017,81 +5017,81 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>4234</v>
+        <v>88</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>4234</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
@@ -5107,21 +5107,21 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>1595</v>
+        <v>4234</v>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
@@ -5132,26 +5132,26 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-01-27T14:46:00Z</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1595</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
@@ -5162,26 +5162,26 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-01-27T14:45:00Z</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>4982</v>
+        <v>1</v>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
@@ -5192,26 +5192,26 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>1595</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
@@ -5227,21 +5227,21 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1070</v>
+        <v>1595</v>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
@@ -5252,26 +5252,26 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-01-16T16:24:00Z</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>4982</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-01-16T15:14:00Z</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
@@ -5317,21 +5317,21 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-15T21:13:00Z</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>140</v>
+        <v>1070</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
@@ -5342,26 +5342,26 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-15T04:24:00Z</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
@@ -5372,26 +5372,26 @@
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-10T15:08:00Z</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-08T04:54:00Z</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
@@ -5437,21 +5437,21 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-01-08T04:54:00Z</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
@@ -5467,32 +5467,122 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="C151" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E149" s="5" t="n">
+      <c r="E152" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F149" s="5" t="inlineStr">
+      <c r="F152" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: July 02, 2026</t>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: July 16, 2026</t>
         </is>
       </c>
     </row>
@@ -5945,7 +6035,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: July 2, 2026 (Jun 2026 finalized: 2 outages (EU SAST Aviator Jun 8 2 min, AMS SAST Aviator Jun 9 2 min), 4 total outage minutes, 99.9907% uptime; new maintenance events Jun 4-5, 22-27 added; AMS service degradation Jun 11-Jun 25 recorded; times converted from BST to GMT).</t>
+          <t>Last updated: July 16, 2026 (mid-month snapshot for Jul 2026 through Jul 16; 3 outages added: Jul 6 APAC Portal 6 min, Jul 7 APAC API 7 min, Jul 8 AMS SAST Aviator 4 min; all times converted from BST to GMT; Jun 2026 previously finalized July 2, 2026).</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6722,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Last updated: July 2, 2026</t>
+          <t>Last updated: July 16, 2026</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7231,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>1</v>
+        <v>0.9998655913978495</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -7197,7 +7287,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>1</v>
+        <v>0.9998431899641577</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -7556,7 +7646,7 @@
         <v>0.9999537037037037</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>1</v>
+        <v>0.999910394265233</v>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
@@ -9835,7 +9925,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Month in progress. Will be finalized after July 31, 2026.</t>
+          <t>Month in progress (partial through July 16, 2026). Will be finalized after July 31, 2026.</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9968,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9980,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
     </row>

--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -16,9 +16,10 @@
     <sheet name="May 2026" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Jun 2026" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Jul 2026" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="2026 Incident Data" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Bucket Mapping" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Notes &amp; Methodology" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Aug 2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026 Incident Data" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Bucket Mapping" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Notes &amp; Methodology" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,55 +547,55 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1. Jan: 4 outages (5 min); Feb: 3 (9 min); Mar: 7 (57 min); Apr: 4 (25 min); May: 2 (4 min); Jun: 2 (4 min)</t>
+          <t>1. Jan: 4 outages (5 min); Feb: 3 (9 min); Mar: 7 (57 min); Apr: 4 (25 min); May: 2 (4 min); Jun: 2 (4 min); Jul: 8 (39 min)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Completed Months: January - June 2026</t>
+          <t>Completed Months: January - July 2026</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2. March 2 remains the worst single day in 2026 (FedRAMP Portal/API, 44 min); April 16 EU Portal/API outage (10 min) was the largest April incident; Jun had no outages beyond the 2 brief SAST events on Jun 8-9</t>
+          <t>2. March 2 remains the single worst day in 2026 (FedRAMP Portal/API, 44 min); July 24 was the largest July event: FedRAMP Portal/API + AMS SAST Aviator + Vulncat across three grouped incidents (10 min, 7 min, 1 min)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>YTD Outages: 22 incidents (completed months)</t>
+          <t>YTD Outages: 30 incidents (completed months)</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>3. SAST Aviator (EU/AMS) continued brief outage pattern: Mar 11, 13, 17, 18; Apr 9 EU SAST 2 min; May 9 EU SAST 2 min, May 10 AMS SAST 2 min; Jun 8 EU SAST 2 min, Jun 9 AMS SAST 2 min</t>
+          <t>3. SAST Aviator (EU/AMS) continued brief outage pattern: Mar 11, 13, 17, 18; Apr 9 EU SAST 2 min; May 9 EU SAST 2 min, May 10 AMS SAST 2 min; Jun 8 EU SAST 2 min, Jun 9 AMS SAST 2 min; Jul 8 AMS SAST 4 min, Jul 24 AMS SAST events</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>YTD Outage Time: 104 minutes (1.73 hours) (completed months)</t>
+          <t>YTD Outage Time: 143 minutes (2.38 hours) (completed months)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>4. YTD uptime of 99.9601% continues to exceed the 99.9% SLA target across all six completed months</t>
+          <t>4. YTD uptime of 99.9532% continues to exceed the 99.9% SLA target across all seven completed months</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>YTD Uptime: 99.9601% (completed months only)</t>
+          <t>YTD Uptime: 99.9532% (completed months only)</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5. Jun 24-25 saw a large scheduled maintenance window across EMEA, EU, AMS, APAC, SGP with no associated outages; FedRAMP maintained on Jun 27</t>
+          <t>5. Jul 29-30 maintenance window covered AMS, EU, EMEA (Jul 30 GMT), APAC/SGP and FedRAMP (Jul 29 GMT) with no associated outages; Jun 24-25 also saw large scheduled maintenance across EMEA, EU, AMS, APAC, SGP</t>
         </is>
       </c>
     </row>
@@ -752,23 +753,17 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>3*</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>17*</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>0.28*</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0.9996191756272401</v>
+      <c r="B21" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.9991263440860215</v>
       </c>
     </row>
     <row r="22">
@@ -779,23 +774,21 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1*</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1*</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0.02*</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0.9999775985663082</v>
       </c>
     </row>
     <row r="23">
@@ -913,71 +906,71 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>0.9996009821976672</v>
+        <v>0.9995315775681342</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* July 2026 is in progress (partial through July 16, 2026). Will be finalized after July 31, 2026.</t>
+          <t>* August 2026 is in progress. Will be finalized after August 31, 2026.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026 SLA Performance (Completed Months: Jan - Jun)</t>
+          <t>2026 SLA Performance (Completed Months: Jan - Jul)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Total Period Minutes (completed): 260,640</t>
+          <t>Total Period Minutes (completed): 305,280</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Total Outage Minutes: 104</t>
+          <t>Total Outage Minutes: 143</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Uptime Minutes: 260,536</t>
+          <t>Uptime Minutes: 305,137</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Uptime Percentage: 99.9601%</t>
+          <t>Uptime Percentage: 99.9532%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Outage Count: 22 incidents</t>
+          <t>Outage Count: 30 incidents</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Average Outage Duration: 4.73 minutes</t>
+          <t>Average Outage Duration: 4.77 minutes</t>
         </is>
       </c>
     </row>
@@ -1006,7 +999,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>August 2026 - Monthly Detail (In Progress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Month in progress. Will be finalized after August 31, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Summary (In Progress)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Period:</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>August 1 - 31, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Total Minutes:</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>44,640</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Outage Count (to date):</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Outage Minutes (to date):</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Status:</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1057,51 +1152,51 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-08T16:34:00Z</t>
+          <t>2026-08-01T12:15:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Jul 08, 2026 4:38 PM GMT</t>
+          <t>Aug 01, 2026 12:16 PM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-07T22:42:00Z</t>
+          <t>2026-07-30T04:56:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Jul 07, 2026 10:49 PM GMT</t>
+          <t>Jul 30, 2026 7:22 AM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>7</v>
+        <v>146</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -1112,26 +1207,26 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-07-06T16:05:00Z</t>
+          <t>2026-07-30T04:56:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Jul 06, 2026 4:11 PM GMT</t>
+          <t>Jul 30, 2026 7:22 AM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -1147,25 +1242,25 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-07-30T02:27:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Jul 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1177,25 +1272,25 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-07-30T02:27:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Jul 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1302,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-07-30T01:35:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Jul 30, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1221,11 +1316,11 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1332,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-07-30T01:35:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Jul 30, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1251,11 +1346,11 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1267,25 +1362,25 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-07-29T21:45:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jul 29, 2026 11:02 PM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1297,25 +1392,25 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-07-29T21:45:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jul 29, 2026 11:02 PM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1327,25 +1422,25 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>252</v>
+        <v>53</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1357,25 +1452,25 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>252</v>
+        <v>53</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1387,25 +1482,25 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1417,252 +1512,252 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-07-24T11:09:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-07-24T11:02:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jul 24, 2026 11:09 AM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jul 24, 2026 11:06 AM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>116</v>
+        <v>6</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-07-24T02:45:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jul 24, 2026 2:47 AM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T17:55:00Z</t>
+          <t>2026-07-20T08:26:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Jun 23, 2026 6:45 PM GMT</t>
+          <t>Jul 20, 2026 8:28 AM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T21:08:00Z</t>
+          <t>2026-07-08T16:34:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Jun 22, 2026 9:40 PM GMT</t>
+          <t>Jul 08, 2026 4:38 PM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1671,97 +1766,97 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-07-07T22:42:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jul 07, 2026 10:49 PM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>20253</v>
+        <v>7</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-07-06T16:05:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jul 06, 2026 4:11 PM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>20253</v>
+        <v>6</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T21:09:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Jun 09, 2026 9:11 PM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -1772,26 +1867,26 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1789</v>
+        <v>22</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -1802,26 +1897,26 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1789</v>
+        <v>192</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -1832,26 +1927,26 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-06-08T19:11:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Jun 08, 2026 7:13 PM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -1867,21 +1962,21 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>903</v>
+        <v>164</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -1897,21 +1992,21 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>903</v>
+        <v>164</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -1927,12 +2022,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1941,11 +2036,11 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -1957,12 +2052,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1971,11 +2066,11 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -1987,25 +2082,25 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2017,25 +2112,25 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2047,25 +2142,25 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2077,25 +2172,25 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2107,25 +2202,25 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2137,25 +2232,25 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2262,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2181,11 +2276,11 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2292,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2211,11 +2306,11 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2227,25 +2322,25 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-23T17:55:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 23, 2026 6:45 PM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2257,25 +2352,25 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-22T21:08:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 22, 2026 9:40 PM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2382,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2301,11 +2396,11 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>17374</v>
+        <v>20253</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2412,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2331,41 +2426,41 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>17374</v>
+        <v>20253</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-06-09T21:09:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>Jun 09, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2377,145 +2472,145 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>5</v>
+        <v>1789</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>673</v>
+        <v>1789</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-06-08T19:11:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>Jun 08, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>673</v>
+        <v>2</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10T21:09:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>May 10, 2026 9:11 PM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>903</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09T19:11:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>May 09, 2026 7:13 PM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>2</v>
+        <v>903</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2527,12 +2622,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -2541,7 +2636,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -2557,12 +2652,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2571,7 +2666,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -2582,26 +2677,26 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1395</v>
+        <v>57</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
@@ -2612,26 +2707,26 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1395</v>
+        <v>57</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
@@ -2647,21 +2742,21 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
@@ -2677,21 +2772,21 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
@@ -2707,25 +2802,25 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -2737,25 +2832,25 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -2767,25 +2862,25 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -2797,25 +2892,25 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -2827,25 +2922,25 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -2857,145 +2952,145 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>73</v>
+        <v>17374</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>73</v>
+        <v>17374</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>273</v>
+        <v>5</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>273</v>
+        <v>5</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3102,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3021,11 +3116,11 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>273</v>
+        <v>673</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3132,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3051,88 +3146,88 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>273</v>
+        <v>673</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-05-10T21:09:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>May 10, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-05-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>May 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3141,28 +3236,28 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>17272</v>
+        <v>132</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3171,71 +3266,71 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>17272</v>
+        <v>132</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1187</v>
+        <v>1395</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1187</v>
+        <v>1395</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3247,25 +3342,25 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>4284</v>
+        <v>72</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3277,51 +3372,51 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>4284</v>
+        <v>72</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:28:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -3332,26 +3427,26 @@
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:26:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
@@ -3367,21 +3462,21 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
@@ -3397,21 +3492,21 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
@@ -3422,26 +3517,26 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
@@ -3457,21 +3552,21 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>211</v>
+        <v>88</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
@@ -3482,26 +3577,26 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
@@ -3512,26 +3607,26 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
@@ -3542,26 +3637,26 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
@@ -3577,21 +3672,21 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>50</v>
+        <v>273</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
@@ -3607,21 +3702,21 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>50</v>
+        <v>273</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
@@ -3637,25 +3732,25 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3762,25 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3697,85 +3792,85 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>150</v>
+        <v>17272</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>123</v>
+        <v>17272</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3787,25 +3882,25 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>123</v>
+        <v>1187</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3817,25 +3912,25 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>123</v>
+        <v>1187</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3847,25 +3942,25 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>123</v>
+        <v>4284</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3877,85 +3972,85 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>90</v>
+        <v>4284</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -3967,85 +4062,85 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4057,25 +4152,25 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4087,17 +4182,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -4105,7 +4200,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4117,55 +4212,55 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4177,25 +4272,25 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4207,25 +4302,25 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4237,21 +4332,21 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>85</v>
+        <v>203</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
@@ -4267,21 +4362,21 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>85</v>
+        <v>203</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
@@ -4297,12 +4392,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -4311,7 +4406,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
@@ -4327,12 +4422,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -4341,7 +4436,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
@@ -4357,12 +4452,12 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -4371,7 +4466,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
@@ -4387,12 +4482,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -4401,7 +4496,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
@@ -4417,12 +4512,12 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -4431,7 +4526,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
@@ -4447,12 +4542,12 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -4461,7 +4556,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
@@ -4472,26 +4567,26 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
@@ -4502,26 +4597,26 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
@@ -4532,26 +4627,26 @@
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
@@ -4562,26 +4657,26 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
@@ -4597,21 +4692,21 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
@@ -4622,30 +4717,30 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>5</v>
+        <v>198</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -4657,175 +4752,175 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>207</v>
+        <v>2</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>159</v>
+        <v>4</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>159</v>
+        <v>4</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -4837,25 +4932,25 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -4867,25 +4962,25 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -4897,25 +4992,25 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -4927,25 +5022,25 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -4957,25 +5052,25 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -4987,25 +5082,25 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5017,25 +5112,25 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5047,85 +5142,85 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>4234</v>
+        <v>11</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>4234</v>
+        <v>5</v>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5137,25 +5232,25 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5167,85 +5262,85 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1595</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1595</v>
+        <v>5</v>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5257,55 +5352,55 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>4982</v>
+        <v>207</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>207</v>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5317,55 +5412,55 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>1070</v>
+        <v>159</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5377,12 +5472,12 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -5395,37 +5490,37 @@
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5437,25 +5532,25 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>140</v>
+        <v>282</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5467,25 +5562,25 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>137</v>
+        <v>282</v>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5497,25 +5592,25 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5527,25 +5622,25 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -5557,32 +5652,632 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
+          <t>2026-02-05T01:57:00Z</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T01:57:00Z</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-04T23:58:00Z</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-04T23:58:00Z</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30T19:08:00Z</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30T19:08:00Z</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:46:00Z</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:45:00Z</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T16:24:00Z</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n">
+        <v>4982</v>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T15:14:00Z</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T21:13:00Z</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:24:00Z</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-10T15:08:00Z</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
+      <c r="C171" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E152" s="5" t="n">
+      <c r="E172" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F152" s="5" t="inlineStr">
+      <c r="F172" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: July 16, 2026</t>
+    <row r="173">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: August 02, 2026</t>
         </is>
       </c>
     </row>
@@ -5591,7 +6286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5985,7 +6680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6035,7 +6730,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: July 16, 2026 (mid-month snapshot for Jul 2026 through Jul 16; 3 outages added: Jul 6 APAC Portal 6 min, Jul 7 APAC API 7 min, Jul 8 AMS SAST Aviator 4 min; all times converted from BST to GMT; Jun 2026 previously finalized July 2, 2026).</t>
+          <t>Last updated: August 2, 2026 (July 2026 finalized; 7 new outages added for Jul 17-31: Jul 20 Vulncat 2 min, Jul 24 FedRAMP Portal/API + AMS SAST + Vulncat multi-component event, all times converted from BST to GMT; Aug 1 Vulncat outage 1 min added to Aug stub; Jul 29-30 maintenance window added).</t>
         </is>
       </c>
     </row>
@@ -6722,7 +7417,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Last updated: July 16, 2026</t>
+          <t>Last updated: August 2, 2026</t>
         </is>
       </c>
     </row>
@@ -6894,36 +7589,34 @@
       <c r="G5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="H5" s="12" t="n">
+        <v>0.9997759856630825</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="M5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N5" s="12" t="n">
-        <v>0.9998196746470227</v>
+        <v>0.9998132861635221</v>
       </c>
     </row>
     <row r="6">
@@ -6950,36 +7643,34 @@
       <c r="G6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="n">
+        <v>0.9997759856630825</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="M6" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M6" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N6" s="12" t="n">
-        <v>0.9999616329036218</v>
+        <v>0.9999344863731656</v>
       </c>
     </row>
     <row r="7">
@@ -7006,13 +7697,11 @@
       <c r="G7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="14" t="inlineStr">
         <is>
@@ -7062,13 +7751,11 @@
       <c r="G8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
@@ -7118,13 +7805,11 @@
       <c r="G9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="14" t="inlineStr">
         <is>
@@ -7174,13 +7859,11 @@
       <c r="G10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
@@ -7230,36 +7913,34 @@
       <c r="G11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="12" t="n">
         <v>0.9998655913978495</v>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="K11" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K11" s="14" t="inlineStr">
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="M11" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N11" s="12" t="n">
-        <v>1</v>
+        <v>0.9999803459119497</v>
       </c>
     </row>
     <row r="12">
@@ -7286,36 +7967,34 @@
       <c r="G12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.9998431899641577</v>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="K12" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="14" t="inlineStr">
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="M12" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M12" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N12" s="12" t="n">
-        <v>1</v>
+        <v>0.999977070230608</v>
       </c>
     </row>
     <row r="13">
@@ -7342,13 +8021,11 @@
       <c r="G13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="14" t="inlineStr">
         <is>
@@ -7398,36 +8075,34 @@
       <c r="G14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="H14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="L14" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="M14" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N14" s="12" t="n">
-        <v>0.9999808164518109</v>
+        <v>0.9999836215932913</v>
       </c>
     </row>
     <row r="15">
@@ -7454,36 +8129,34 @@
       <c r="G15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="H15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="K15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K15" s="14" t="inlineStr">
+      <c r="L15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="M15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N15" s="12" t="n">
-        <v>0.9999616329036218</v>
+        <v>0.9999672431865828</v>
       </c>
     </row>
     <row r="16">
@@ -7510,36 +8183,34 @@
       <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="H16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="L16" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="M16" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N16" s="12" t="n">
-        <v>0.9999616329036218</v>
+        <v>0.9999672431865828</v>
       </c>
     </row>
     <row r="18">
@@ -7645,36 +8316,34 @@
       <c r="G20" s="12" t="n">
         <v>0.9999537037037037</v>
       </c>
-      <c r="H20" s="13" t="n">
-        <v>0.999910394265233</v>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="H20" s="12" t="n">
+        <v>0.9997535842293906</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="K20" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K20" s="14" t="inlineStr">
+      <c r="L20" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L20" s="14" t="inlineStr">
+      <c r="M20" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N20" s="12" t="n">
-        <v>0.9999347759361572</v>
+        <v>0.9999082809224319</v>
       </c>
     </row>
     <row r="21">
@@ -7701,36 +8370,34 @@
       <c r="G21" s="12" t="n">
         <v>0.9999537037037037</v>
       </c>
-      <c r="H21" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="H21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="K21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
+      <c r="L21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L21" s="14" t="inlineStr">
+      <c r="M21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N21" s="12" t="n">
-        <v>0.9999501227747084</v>
+        <v>0.9999574161425576</v>
       </c>
     </row>
     <row r="23">
@@ -7836,13 +8503,11 @@
       <c r="G25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H25" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
@@ -7892,42 +8557,40 @@
       <c r="G26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="H26" s="12" t="n">
+        <v>0.9997535842293906</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>0.9999775985663082</v>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="K26" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K26" s="14" t="inlineStr">
+      <c r="L26" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="M26" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N26" s="12" t="n">
-        <v>0.9999961632903622</v>
+        <v>0.9999606918238994</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* July 2026 is in progress. Partial data shown in italics.</t>
+          <t>* August 2026 is in progress. Partial data shown in italics.</t>
         </is>
       </c>
     </row>
@@ -9905,7 +10568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -9913,86 +10576,485 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="85" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>July 2026 - Monthly Detail (In Progress)</t>
+          <t>July 2026 - Monthly Detail</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Month in progress (partial through July 16, 2026). Will be finalized after July 31, 2026.</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Monthly Summary</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Monthly Summary (In Progress)</t>
+          <t>Period:</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>July 1 - 31, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Total Minutes:</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>44,640</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Period:</t>
+          <t>Outage Count:</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>July 1 - 31, 2026</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Total Minutes:</t>
+          <t>Outage Minutes:</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>44,640</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Outage Count (to date):</t>
+          <t>Uptime %:</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>99.9126%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Outage Minutes (to date):</t>
+          <t>SLA Status:</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Status:</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+          <t>MEETING TARGET (99.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Daily Outage Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Outage Count</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Outage Minutes</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Uptime Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0.9861111111111112</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>0.9951388888888889</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>0.9958333333333333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>0.9972222222222222</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>0.9986111111111111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Services Affected</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - APAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Detailed Incidents</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>1. July 24, 2026 - Multiple Outages (10 minutes total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Service 1: Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Service 2: Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Service 3: SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Time: 11:00 AM GMT-11:10 AM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2. July 07, 2026 - Outage (7 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Service: Fortify on Demand API - APAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Time: 10:42 PM GMT-10:49 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>3. July 24, 2026 - Outage (7 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Service: Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Time: 11:02 AM GMT-11:09 AM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>4. July 06, 2026 - Outage (6 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Service: Fortify on Demand Tenant Portal - APAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Time: 4:05 PM GMT-4:11 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>5. July 08, 2026 - Outage (4 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Time: 4:34 PM GMT-4:38 PM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>6. July 20, 2026 - Outage (2 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Service: Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Time: 8:26 AM GMT-8:28 AM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>7. July 24, 2026 - Outage (2 minutes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Service: Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Time: 2:45 AM GMT-2:47 AM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>8. July 24, 2026 - Outage (1 minute)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Service: SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Time: 11:09 AM GMT-11:10 AM GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Impact: Brief service disruption</t>
         </is>
       </c>
     </row>

--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -774,21 +774,21 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>1*</t>
+          <t>27*</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>1*</t>
+          <t>1221*</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>0.02*</t>
+          <t>20.35*</t>
         </is>
       </c>
       <c r="E22" s="8" t="n">
-        <v>0.9999775985663082</v>
+        <v>0.9726478494623656</v>
       </c>
     </row>
     <row r="23">
@@ -921,7 +921,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* August 2026 is in progress. Will be finalized after August 31, 2026.</t>
+          <t>* August 2026 is in progress (partial through August 16, 2026). Will be finalized after August 31, 2026.</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Month in progress. Will be finalized after August 31, 2026.</t>
+          <t>Month in progress. Partial data through August 16, 2026. Will be finalized after August 31, 2026.</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1221</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01T12:15:00Z</t>
+          <t>2026-08-15T13:05:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Aug 01, 2026 12:16 PM GMT</t>
+          <t>Aug 15, 2026 1:07 PM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -1177,360 +1177,360 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T04:56:00Z</t>
+          <t>2026-08-15T06:35:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 7:22 AM GMT</t>
+          <t>Aug 15, 2026 6:36 AM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T04:56:00Z</t>
+          <t>2026-08-14T15:35:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 7:22 AM GMT</t>
+          <t>Aug 14, 2026 3:36 PM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T02:27:00Z</t>
+          <t>2026-08-14T13:05:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 5:59 AM GMT</t>
+          <t>Aug 14, 2026 1:06 PM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T02:27:00Z</t>
+          <t>2026-08-14T07:35:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 5:59 AM GMT</t>
+          <t>Aug 14, 2026 7:36 AM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>212</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T01:35:00Z</t>
+          <t>2026-08-14T05:35:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 2:45 AM GMT</t>
+          <t>Aug 14, 2026 5:36 AM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T01:35:00Z</t>
+          <t>2026-08-13T18:05:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 2:45 AM GMT</t>
+          <t>Aug 13, 2026 6:06 PM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T21:45:00Z</t>
+          <t>2026-08-13T14:05:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 11:02 PM GMT</t>
+          <t>Aug 13, 2026 2:06 PM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T21:45:00Z</t>
+          <t>2026-08-13T08:35:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 11:02 PM GMT</t>
+          <t>Aug 13, 2026 8:36 AM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-08-12T16:09:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Aug 12, 2026 4:38 PM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-08-10T12:43:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Aug 10, 2026 12:44 PM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-08-10T10:42:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Aug 10, 2026 12:40 PM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-08-10T10:12:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Aug 10, 2026 10:40 AM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1542,25 +1542,25 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:09:00Z</t>
+          <t>2026-08-10T07:41:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:10 AM GMT</t>
+          <t>Aug 10, 2026 10:10 AM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:02:00Z</t>
+          <t>2026-08-09T20:38:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:09 AM GMT</t>
+          <t>Aug 09, 2026 10:06 PM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1586,11 +1586,11 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1602,25 +1602,25 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:00Z</t>
+          <t>2026-08-09T20:08:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:10 AM GMT</t>
+          <t>Aug 09, 2026 8:36 PM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1632,25 +1632,25 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:00Z</t>
+          <t>2026-08-09T19:12:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:10 AM GMT</t>
+          <t>Aug 09, 2026 8:06 PM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1662,25 +1662,25 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:00Z</t>
+          <t>2026-08-09T16:12:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:06 AM GMT</t>
+          <t>Aug 09, 2026 7:10 PM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T02:45:00Z</t>
+          <t>2026-08-09T13:12:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 2:47 AM GMT</t>
+          <t>Aug 09, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1706,11 +1706,11 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2</v>
+        <v>178</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20T08:26:00Z</t>
+          <t>2026-08-09T11:32:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Jul 20, 2026 8:28 AM GMT</t>
+          <t>Aug 09, 2026 1:11 PM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1736,11 +1736,11 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-08T16:34:00Z</t>
+          <t>2026-08-07T06:57:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Jul 08, 2026 4:38 PM GMT</t>
+          <t>Aug 07, 2026 7:31 AM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1782,25 +1782,25 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-07-07T22:42:00Z</t>
+          <t>2026-08-07T03:38:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Jul 07, 2026 10:49 PM GMT</t>
+          <t>Aug 07, 2026 5:08 AM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1812,145 +1812,145 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-06T16:05:00Z</t>
+          <t>2026-08-07T03:12:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Jul 06, 2026 4:11 PM GMT</t>
+          <t>Aug 07, 2026 3:36 AM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-08-07T02:38:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Aug 07, 2026 3:10 AM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-08-07T01:54:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Aug 07, 2026 2:36 AM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-08-07T01:13:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Aug 07, 2026 1:51 AM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>192</v>
+        <v>38</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-08-01T12:15:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Aug 01, 2026 12:16 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -1962,25 +1962,25 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-07-30T04:56:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jul 30, 2026 7:22 AM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -1992,25 +1992,25 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-07-30T04:56:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jul 30, 2026 7:22 AM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-07-30T02:27:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jul 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2052,25 +2052,25 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-07-30T02:27:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jul 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2082,25 +2082,25 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-07-30T01:35:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jul 30, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2112,25 +2112,25 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-07-30T01:35:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jul 30, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2142,25 +2142,25 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-07-29T21:45:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jul 29, 2026 11:02 PM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2172,25 +2172,25 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-07-29T21:45:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jul 29, 2026 11:02 PM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2202,25 +2202,25 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2262,25 +2262,25 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2292,145 +2292,145 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T17:55:00Z</t>
+          <t>2026-07-24T11:09:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Jun 23, 2026 6:45 PM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T21:08:00Z</t>
+          <t>2026-07-24T11:02:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Jun 22, 2026 9:40 PM GMT</t>
+          <t>Jul 24, 2026 11:09 AM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>20253</v>
+        <v>10</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>20253</v>
+        <v>10</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T21:09:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Jun 09, 2026 9:11 PM GMT</t>
+          <t>Jul 24, 2026 11:06 AM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2456,71 +2456,71 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-07-24T02:45:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jul 24, 2026 2:47 AM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1789</v>
+        <v>2</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-07-20T08:26:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jul 20, 2026 8:28 AM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1789</v>
+        <v>2</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2532,85 +2532,85 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-06-08T19:11:00Z</t>
+          <t>2026-07-08T16:34:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Jun 08, 2026 7:13 PM GMT</t>
+          <t>Jul 08, 2026 4:38 PM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-07-07T22:42:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jul 07, 2026 10:49 PM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>903</v>
+        <v>7</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-07-06T16:05:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jul 06, 2026 4:11 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>903</v>
+        <v>6</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -2622,25 +2622,25 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2652,25 +2652,25 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2682,25 +2682,25 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>57</v>
+        <v>192</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2712,25 +2712,25 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>57</v>
+        <v>192</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2756,11 +2756,11 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2786,11 +2786,11 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2802,25 +2802,25 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2832,25 +2832,25 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2862,25 +2862,25 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2892,25 +2892,25 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2922,25 +2922,25 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -2952,145 +2952,145 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>17374</v>
+        <v>83</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>17374</v>
+        <v>83</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -3102,25 +3102,25 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-06-23T17:55:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>Jun 23, 2026 6:45 PM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>673</v>
+        <v>50</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -3132,145 +3132,145 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-06-22T21:08:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>Jun 22, 2026 9:40 PM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>673</v>
+        <v>32</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10T21:09:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>May 10, 2026 9:11 PM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>20253</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09T19:11:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>May 09, 2026 7:13 PM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>20253</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-06-09T21:09:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>Jun 09, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>132</v>
+        <v>1789</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -3282,55 +3282,55 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1395</v>
+        <v>1789</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-06-08T19:11:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>Jun 08, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1395</v>
+        <v>2</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -3342,25 +3342,25 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>72</v>
+        <v>903</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -3372,25 +3372,25 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>72</v>
+        <v>903</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3416,11 +3416,11 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3446,11 +3446,11 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3476,11 +3476,11 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3506,11 +3506,11 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3536,11 +3536,11 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3566,11 +3566,11 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3596,11 +3596,11 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3612,12 +3612,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3626,11 +3626,11 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3656,11 +3656,11 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>273</v>
+        <v>122</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3686,11 +3686,11 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>273</v>
+        <v>122</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -3716,11 +3716,11 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>273</v>
+        <v>122</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3732,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -3746,71 +3746,71 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>273</v>
+        <v>122</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>242</v>
+        <v>17374</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>242</v>
+        <v>17374</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -3836,11 +3836,11 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>17272</v>
+        <v>5</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -3866,11 +3866,11 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>17272</v>
+        <v>5</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3882,25 +3882,25 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1187</v>
+        <v>673</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -3912,235 +3912,235 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1187</v>
+        <v>673</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-05-10T21:09:00Z</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>May 10, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>4284</v>
+        <v>2</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-05-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>May 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>4284</v>
+        <v>2</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:28:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:26:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>96</v>
+        <v>1395</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>30</v>
+        <v>1395</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -4152,51 +4152,51 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>211</v>
+        <v>72</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>162</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
@@ -4207,26 +4207,26 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -4237,22 +4237,22 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -4272,21 +4272,21 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
@@ -4302,21 +4302,21 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
@@ -4332,25 +4332,25 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>203</v>
+        <v>88</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4362,25 +4362,25 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>203</v>
+        <v>73</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4392,25 +4392,25 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4422,25 +4422,25 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4452,25 +4452,25 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>123</v>
+        <v>273</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4482,25 +4482,25 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>123</v>
+        <v>273</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4512,25 +4512,25 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>123</v>
+        <v>273</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4542,25 +4542,25 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>123</v>
+        <v>242</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4572,85 +4572,85 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>42</v>
+        <v>17272</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>99</v>
+        <v>17272</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4662,55 +4662,55 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>99</v>
+        <v>1187</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>1187</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4722,12 +4722,12 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -4736,11 +4736,11 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>198</v>
+        <v>4284</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -4766,11 +4766,11 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>198</v>
+        <v>4284</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4782,25 +4782,25 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4812,42 +4812,42 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -4856,11 +4856,11 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4872,55 +4872,55 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -4932,42 +4932,42 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>85</v>
+        <v>211</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -4976,71 +4976,71 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5052,25 +5052,25 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5082,25 +5082,25 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -5112,21 +5112,21 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
@@ -5142,21 +5142,21 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
@@ -5167,26 +5167,26 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
@@ -5197,26 +5197,26 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
@@ -5227,26 +5227,26 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
@@ -5257,26 +5257,26 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
@@ -5287,26 +5287,26 @@
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
@@ -5317,17 +5317,17 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -5336,11 +5336,11 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5352,25 +5352,25 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5382,25 +5382,25 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>207</v>
+        <v>42</v>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5412,25 +5412,25 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5442,25 +5442,25 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5472,55 +5472,55 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5532,115 +5532,115 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>282</v>
+        <v>198</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>282</v>
+        <v>2</v>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>127</v>
+        <v>4</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>127</v>
+        <v>4</v>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5652,25 +5652,25 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5682,25 +5682,25 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5712,25 +5712,25 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5742,25 +5742,25 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5772,12 +5772,12 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -5786,11 +5786,11 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>4234</v>
+        <v>87</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5802,12 +5802,12 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -5816,71 +5816,71 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>4234</v>
+        <v>87</v>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5892,25 +5892,25 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1595</v>
+        <v>95</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5922,55 +5922,55 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1595</v>
+        <v>95</v>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>4982</v>
+        <v>11</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -5982,55 +5982,55 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>1070</v>
+        <v>31</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -6042,25 +6042,25 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -6072,55 +6072,55 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>140</v>
+        <v>5</v>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -6132,25 +6132,25 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -6162,25 +6162,25 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -6192,25 +6192,25 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -6222,62 +6222,842 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
+          <t>2026-02-15T19:46:00Z</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-14T22:07:00Z</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T16:28:00Z</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T16:28:00Z</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - SGP</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T04:56:00Z</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T04:56:00Z</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T01:57:00Z</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-05T01:57:00Z</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-04T23:58:00Z</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-04T23:58:00Z</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30T19:08:00Z</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30T19:08:00Z</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - EMEA</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="n">
+        <v>4234</v>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:46:00Z</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:45:00Z</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T16:24:00Z</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n">
+        <v>4982</v>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T15:14:00Z</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T21:13:00Z</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:24:00Z</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-10T15:08:00Z</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C172" s="5" t="inlineStr">
+      <c r="C197" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E172" s="5" t="n">
+      <c r="E198" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F172" s="5" t="inlineStr">
+      <c r="F198" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: August 02, 2026</t>
+    <row r="199">
+      <c r="A199" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: August 16, 2026</t>
         </is>
       </c>
     </row>
@@ -6730,7 +7510,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: August 2, 2026 (July 2026 finalized; 7 new outages added for Jul 17-31: Jul 20 Vulncat 2 min, Jul 24 FedRAMP Portal/API + AMS SAST + Vulncat multi-component event, all times converted from BST to GMT; Aug 1 Vulncat outage 1 min added to Aug stub; Jul 29-30 maintenance window added).</t>
+          <t>Last updated: August 16, 2026 (Mid-month update; 26 new Vulncat outages added for Aug 7-15, all BST converted to GMT; large Vulncat outage cluster Aug 7 (260 min), Aug 9 (625 min), Aug 10 (296 min), plus smaller events Aug 12-15; Aug 2026 partial through 2026-08-16).</t>
         </is>
       </c>
     </row>
@@ -7417,7 +8197,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Last updated: August 2, 2026</t>
+          <t>Last updated: August 16, 2026</t>
         </is>
       </c>
     </row>
@@ -8561,7 +9341,7 @@
         <v>0.9997535842293906</v>
       </c>
       <c r="I26" s="13" t="n">
-        <v>0.9999775985663082</v>
+        <v>0.9726478494623656</v>
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>

--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -797,21 +797,21 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>12*</t>
+          <t>18*</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>403*</t>
+          <t>419*</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>6.72*</t>
+          <t>6.98*</t>
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.9906712962962962</v>
+        <v>0.9903009259259259</v>
       </c>
     </row>
     <row r="24">
@@ -917,7 +917,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* September 2026 is in progress (partial through September 2, 2026). Will be finalized after September 30, 2026.</t>
+          <t>* September 2026 is in progress (partial through September 16, 2026). Will be finalized after September 30, 2026.</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Month in progress. Partial data through September 2, 2026. Will be finalized after September 30, 2026.</t>
+          <t>Month in progress. Partial data through September 16, 2026. Will be finalized after September 30, 2026.</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>419</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F308"/>
+  <dimension ref="A1:F322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4827,21 +4827,21 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02T10:28:00Z</t>
+          <t>2026-09-14T15:45:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Sep 02, 2026 10:34 AM GMT</t>
+          <t>Sep 14, 2026 3:49 PM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02T02:55:00Z</t>
+          <t>2026-09-13T18:11:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Sep 02, 2026 3:03 AM GMT</t>
+          <t>Sep 13, 2026 6:13 PM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -4882,26 +4882,26 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T18:51:00Z</t>
+          <t>2026-09-11T20:53:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 6:53 PM GMT</t>
+          <t>Sep 11, 2026 11:14 PM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>141</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -4912,26 +4912,26 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T15:56:00Z</t>
+          <t>2026-09-11T20:53:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 4:11 PM GMT</t>
+          <t>Sep 11, 2026 11:14 PM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -4942,26 +4942,26 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T14:59:00Z</t>
+          <t>2026-09-11T18:19:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 3:51 PM GMT</t>
+          <t>Sep 14, 2026 5:35 PM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>52</v>
+        <v>4276</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -4972,26 +4972,26 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T13:58:00Z</t>
+          <t>2026-09-11T18:19:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 2:57 PM GMT</t>
+          <t>Sep 14, 2026 5:35 PM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>59</v>
+        <v>4276</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -5002,26 +5002,26 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T12:59:00Z</t>
+          <t>2026-09-10T14:56:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 1:57 PM GMT</t>
+          <t>Sep 10, 2026 5:22 PM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -5032,26 +5032,26 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T11:29:00Z</t>
+          <t>2026-09-10T14:56:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 12:57 PM GMT</t>
+          <t>Sep 10, 2026 5:22 PM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -5062,26 +5062,26 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T10:58:00Z</t>
+          <t>2026-09-09T23:31:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 11:27 AM GMT</t>
+          <t>Sep 10, 2026 3:24 AM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>29</v>
+        <v>233</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -5092,26 +5092,26 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T10:27:00Z</t>
+          <t>2026-09-09T23:31:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 10:57 AM GMT</t>
+          <t>Sep 10, 2026 3:24 AM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>30</v>
+        <v>233</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -5127,12 +5127,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T09:59:00Z</t>
+          <t>2026-09-09T07:32:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 10:26 AM GMT</t>
+          <t>Sep 09, 2026 7:34 AM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -5157,21 +5157,21 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T08:28:00Z</t>
+          <t>2026-09-07T21:31:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 8:57 AM GMT</t>
+          <t>Sep 07, 2026 9:33 PM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T19:58:00Z</t>
+          <t>2026-09-07T02:29:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 8:36 PM GMT</t>
+          <t>Sep 07, 2026 2:31 AM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -5201,11 +5201,11 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5217,25 +5217,25 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T19:28:00Z</t>
+          <t>2026-09-07T02:16:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 7:56 PM GMT</t>
+          <t>Sep 07, 2026 2:20 AM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5247,12 +5247,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T18:56:00Z</t>
+          <t>2026-09-02T10:28:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 7:26 PM GMT</t>
+          <t>Sep 02, 2026 10:34 AM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -5261,11 +5261,11 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T10:59:00Z</t>
+          <t>2026-09-02T02:55:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 11:06 AM GMT</t>
+          <t>Sep 02, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -5291,11 +5291,11 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5307,12 +5307,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T09:59:00Z</t>
+          <t>2026-09-01T18:51:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 10:27 AM GMT</t>
+          <t>Sep 01, 2026 6:53 PM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -5321,11 +5321,11 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T08:01:00Z</t>
+          <t>2026-09-01T15:56:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 9:57 AM GMT</t>
+          <t>Sep 01, 2026 4:11 PM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -5351,11 +5351,11 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5367,12 +5367,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T21:29:00Z</t>
+          <t>2026-09-01T14:59:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 9:36 PM GMT</t>
+          <t>Sep 01, 2026 3:51 PM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -5381,11 +5381,11 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T20:28:00Z</t>
+          <t>2026-09-01T13:58:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 9:26 PM GMT</t>
+          <t>Sep 01, 2026 2:57 PM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -5411,11 +5411,11 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T19:28:00Z</t>
+          <t>2026-09-01T12:59:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 8:26 PM GMT</t>
+          <t>Sep 01, 2026 1:57 PM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T10:59:00Z</t>
+          <t>2026-09-01T11:29:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 11:26 AM GMT</t>
+          <t>Sep 01, 2026 12:57 PM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -5471,11 +5471,11 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5487,12 +5487,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T10:35:00Z</t>
+          <t>2026-09-01T10:58:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 10:56 AM GMT</t>
+          <t>Sep 01, 2026 11:27 AM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -5501,11 +5501,11 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T08:29:00Z</t>
+          <t>2026-09-01T10:27:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 9:26 AM GMT</t>
+          <t>Sep 01, 2026 10:57 AM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -5531,11 +5531,11 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5547,12 +5547,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T19:28:00Z</t>
+          <t>2026-09-01T09:59:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 7:33 PM GMT</t>
+          <t>Sep 01, 2026 10:26 AM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -5561,11 +5561,11 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5577,12 +5577,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T16:06:00Z</t>
+          <t>2026-09-01T08:28:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 7:26 PM GMT</t>
+          <t>Sep 01, 2026 8:57 AM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -5591,11 +5591,11 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T12:29:00Z</t>
+          <t>2026-08-31T19:58:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 12:57 PM GMT</t>
+          <t>Aug 31, 2026 8:36 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -5637,12 +5637,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T12:15:00Z</t>
+          <t>2026-08-31T19:28:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 12:27 PM GMT</t>
+          <t>Aug 31, 2026 7:56 PM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -5667,12 +5667,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T11:59:00Z</t>
+          <t>2026-08-31T18:56:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 12:12 PM GMT</t>
+          <t>Aug 31, 2026 7:26 PM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T08:28:00Z</t>
+          <t>2026-08-31T10:59:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 8:56 AM GMT</t>
+          <t>Aug 31, 2026 11:06 AM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -5727,21 +5727,21 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T00:09:00Z</t>
+          <t>2026-08-31T09:59:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 1:54 AM GMT</t>
+          <t>Aug 31, 2026 10:27 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -5757,21 +5757,21 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T00:09:00Z</t>
+          <t>2026-08-31T08:01:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 1:52 AM GMT</t>
+          <t>Aug 31, 2026 9:57 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -5787,12 +5787,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T17:54:00Z</t>
+          <t>2026-08-30T21:29:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 7:42 PM GMT</t>
+          <t>Aug 30, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T16:53:00Z</t>
+          <t>2026-08-30T20:28:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 5:52 PM GMT</t>
+          <t>Aug 30, 2026 9:26 PM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T12:31:00Z</t>
+          <t>2026-08-30T19:28:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 12:56 PM GMT</t>
+          <t>Aug 30, 2026 8:26 PM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -5877,12 +5877,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T12:28:00Z</t>
+          <t>2026-08-30T10:59:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 12:29 PM GMT</t>
+          <t>Aug 30, 2026 11:26 AM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -5907,12 +5907,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T11:58:00Z</t>
+          <t>2026-08-30T10:35:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 12:27 PM GMT</t>
+          <t>Aug 30, 2026 10:56 AM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T11:31:00Z</t>
+          <t>2026-08-30T08:29:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 11:56 AM GMT</t>
+          <t>Aug 30, 2026 9:26 AM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T11:15:00Z</t>
+          <t>2026-08-29T19:28:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 11:28 AM GMT</t>
+          <t>Aug 29, 2026 7:33 PM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -5997,12 +5997,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T11:05:00Z</t>
+          <t>2026-08-29T16:06:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 11:11 AM GMT</t>
+          <t>Aug 29, 2026 7:26 PM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -6027,12 +6027,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T10:12:00Z</t>
+          <t>2026-08-29T12:29:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 10:21 AM GMT</t>
+          <t>Aug 29, 2026 12:57 PM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -6057,12 +6057,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T10:08:00Z</t>
+          <t>2026-08-29T12:15:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 10:10 AM GMT</t>
+          <t>Aug 29, 2026 12:27 PM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T10:02:00Z</t>
+          <t>2026-08-29T11:59:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 10:07 AM GMT</t>
+          <t>Aug 29, 2026 12:12 PM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
@@ -6117,12 +6117,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T07:57:00Z</t>
+          <t>2026-08-29T08:28:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 9:58 AM GMT</t>
+          <t>Aug 29, 2026 8:56 AM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T16:53:00Z</t>
+          <t>2026-08-29T00:09:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 5:58 PM GMT</t>
+          <t>Aug 29, 2026 1:54 AM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -6177,21 +6177,21 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T12:27:00Z</t>
+          <t>2026-08-29T00:09:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:56 PM GMT</t>
+          <t>Aug 29, 2026 1:52 AM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -6207,12 +6207,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T11:58:00Z</t>
+          <t>2026-08-28T17:54:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 12:26 PM GMT</t>
+          <t>Aug 28, 2026 7:42 PM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -6237,12 +6237,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T08:58:00Z</t>
+          <t>2026-08-28T16:53:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 11:56 AM GMT</t>
+          <t>Aug 28, 2026 5:52 PM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>178</v>
+        <v>59</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -6267,12 +6267,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T07:58:00Z</t>
+          <t>2026-08-28T12:31:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 8:56 AM GMT</t>
+          <t>Aug 28, 2026 12:56 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
@@ -6292,26 +6292,26 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T04:03:00Z</t>
+          <t>2026-08-28T12:28:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 6:07 AM GMT</t>
+          <t>Aug 28, 2026 12:29 PM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -6322,26 +6322,26 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T04:03:00Z</t>
+          <t>2026-08-28T11:58:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 6:07 AM GMT</t>
+          <t>Aug 28, 2026 12:27 PM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -6352,26 +6352,26 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T01:11:00Z</t>
+          <t>2026-08-28T11:31:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:38 AM GMT</t>
+          <t>Aug 28, 2026 11:56 AM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
@@ -6382,26 +6382,26 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T01:11:00Z</t>
+          <t>2026-08-28T11:15:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:38 AM GMT</t>
+          <t>Aug 28, 2026 11:28 AM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
@@ -6412,26 +6412,26 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T23:42:00Z</t>
+          <t>2026-08-28T11:05:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:10 AM GMT</t>
+          <t>Aug 28, 2026 11:11 AM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
@@ -6442,26 +6442,26 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T23:42:00Z</t>
+          <t>2026-08-28T10:12:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:10 AM GMT</t>
+          <t>Aug 28, 2026 10:21 AM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
@@ -6477,12 +6477,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T21:32:00Z</t>
+          <t>2026-08-28T10:08:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 9:34 PM GMT</t>
+          <t>Aug 28, 2026 10:10 AM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T21:28:00Z</t>
+          <t>2026-08-28T10:02:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 9:31 PM GMT</t>
+          <t>Aug 28, 2026 10:07 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
@@ -6532,26 +6532,26 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T21:06:00Z</t>
+          <t>2026-08-28T07:57:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 10:38 PM GMT</t>
+          <t>Aug 28, 2026 9:58 AM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
@@ -6562,26 +6562,26 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T21:06:00Z</t>
+          <t>2026-08-27T16:53:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 10:38 PM GMT</t>
+          <t>Aug 27, 2026 5:58 PM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
@@ -6597,12 +6597,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T20:58:00Z</t>
+          <t>2026-08-27T12:27:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 9:26 PM GMT</t>
+          <t>Aug 27, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
@@ -6627,12 +6627,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T20:55:00Z</t>
+          <t>2026-08-27T11:58:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 8:56 PM GMT</t>
+          <t>Aug 27, 2026 12:26 PM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T12:59:00Z</t>
+          <t>2026-08-27T08:58:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 1:00 PM GMT</t>
+          <t>Aug 27, 2026 11:56 AM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>178</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T12:41:00Z</t>
+          <t>2026-08-27T07:58:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 12:43 PM GMT</t>
+          <t>Aug 27, 2026 8:56 AM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -6712,26 +6712,26 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T12:39:00Z</t>
+          <t>2026-08-27T04:03:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 12:40 PM GMT</t>
+          <t>Aug 27, 2026 6:07 AM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -6742,26 +6742,26 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T12:28:00Z</t>
+          <t>2026-08-27T04:03:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 12:37 PM GMT</t>
+          <t>Aug 27, 2026 6:07 AM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -6772,26 +6772,26 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T09:00:00Z</t>
+          <t>2026-08-27T01:11:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 12:26 PM GMT</t>
+          <t>Aug 27, 2026 1:38 AM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>206</v>
+        <v>27</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
@@ -6802,26 +6802,26 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T07:36:00Z</t>
+          <t>2026-08-27T01:11:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 8:26 AM GMT</t>
+          <t>Aug 27, 2026 1:38 AM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
@@ -6832,26 +6832,26 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T07:30:00Z</t>
+          <t>2026-08-26T23:42:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 7:33 AM GMT</t>
+          <t>Aug 27, 2026 1:10 AM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
@@ -6862,26 +6862,26 @@
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-08-25T23:32:00Z</t>
+          <t>2026-08-26T23:42:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Aug 25, 2026 11:38 PM GMT</t>
+          <t>Aug 27, 2026 1:10 AM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-08-25T18:06:00Z</t>
+          <t>2026-08-26T21:32:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Aug 25, 2026 6:11 PM GMT</t>
+          <t>Aug 26, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -6927,12 +6927,12 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24T06:25:00Z</t>
+          <t>2026-08-26T21:28:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Aug 24, 2026 6:26 AM GMT</t>
+          <t>Aug 26, 2026 9:31 PM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
@@ -6952,26 +6952,26 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T20:55:00Z</t>
+          <t>2026-08-26T21:06:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Aug 23, 2026 8:56 PM GMT</t>
+          <t>Aug 26, 2026 10:38 PM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
@@ -6982,26 +6982,26 @@
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T10:59:00Z</t>
+          <t>2026-08-26T21:06:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Aug 23, 2026 2:03 PM GMT</t>
+          <t>Aug 26, 2026 10:38 PM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>184</v>
+        <v>92</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
@@ -7017,12 +7017,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T07:44:00Z</t>
+          <t>2026-08-26T20:58:00Z</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Aug 23, 2026 8:26 AM GMT</t>
+          <t>Aug 26, 2026 9:26 PM GMT</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
@@ -7047,12 +7047,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T07:34:00Z</t>
+          <t>2026-08-26T20:55:00Z</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Aug 23, 2026 7:40 AM GMT</t>
+          <t>Aug 26, 2026 8:56 PM GMT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
@@ -7077,12 +7077,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T14:58:00Z</t>
+          <t>2026-08-26T12:59:00Z</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 3:55 PM GMT</t>
+          <t>Aug 26, 2026 1:00 PM GMT</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -7091,7 +7091,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -7107,12 +7107,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T12:28:00Z</t>
+          <t>2026-08-26T12:41:00Z</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 2:55 PM GMT</t>
+          <t>Aug 26, 2026 12:43 PM GMT</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
@@ -7137,12 +7137,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T10:57:00Z</t>
+          <t>2026-08-26T12:39:00Z</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 12:26 PM GMT</t>
+          <t>Aug 26, 2026 12:40 PM GMT</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
@@ -7167,12 +7167,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T10:35:00Z</t>
+          <t>2026-08-26T12:28:00Z</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 10:55 AM GMT</t>
+          <t>Aug 26, 2026 12:37 PM GMT</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T09:27:00Z</t>
+          <t>2026-08-26T09:00:00Z</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 9:56 AM GMT</t>
+          <t>Aug 26, 2026 12:26 PM GMT</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>29</v>
+        <v>206</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
@@ -7227,12 +7227,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T07:51:00Z</t>
+          <t>2026-08-26T07:36:00Z</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 8:56 AM GMT</t>
+          <t>Aug 26, 2026 8:26 AM GMT</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T07:40:00Z</t>
+          <t>2026-08-26T07:30:00Z</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 7:47 AM GMT</t>
+          <t>Aug 26, 2026 7:33 AM GMT</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
@@ -7287,12 +7287,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T07:37:00Z</t>
+          <t>2026-08-25T23:32:00Z</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 7:38 AM GMT</t>
+          <t>Aug 25, 2026 11:38 PM GMT</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
@@ -7317,12 +7317,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T07:33:00Z</t>
+          <t>2026-08-25T18:06:00Z</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 7:34 AM GMT</t>
+          <t>Aug 25, 2026 6:11 PM GMT</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
@@ -7347,12 +7347,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T17:52:00Z</t>
+          <t>2026-08-24T06:25:00Z</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 6:26 PM GMT</t>
+          <t>Aug 24, 2026 6:26 AM GMT</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T13:59:00Z</t>
+          <t>2026-08-23T20:55:00Z</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 2:12 PM GMT</t>
+          <t>Aug 23, 2026 8:56 PM GMT</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
@@ -7407,12 +7407,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T13:27:00Z</t>
+          <t>2026-08-23T10:59:00Z</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 1:56 PM GMT</t>
+          <t>Aug 23, 2026 2:03 PM GMT</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T12:58:00Z</t>
+          <t>2026-08-23T07:44:00Z</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 1:25 PM GMT</t>
+          <t>Aug 23, 2026 8:26 AM GMT</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -7451,7 +7451,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T09:58:00Z</t>
+          <t>2026-08-23T07:34:00Z</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 12:55 PM GMT</t>
+          <t>Aug 23, 2026 7:40 AM GMT</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>177</v>
+        <v>6</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
@@ -7497,12 +7497,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T09:27:00Z</t>
+          <t>2026-08-22T14:58:00Z</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 9:56 AM GMT</t>
+          <t>Aug 22, 2026 3:55 PM GMT</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
@@ -7527,12 +7527,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T08:58:00Z</t>
+          <t>2026-08-22T12:28:00Z</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 9:25 AM GMT</t>
+          <t>Aug 22, 2026 2:55 PM GMT</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T07:57:00Z</t>
+          <t>2026-08-22T10:57:00Z</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 8:55 AM GMT</t>
+          <t>Aug 22, 2026 12:26 PM GMT</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
@@ -7587,12 +7587,12 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T07:31:00Z</t>
+          <t>2026-08-22T10:35:00Z</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 7:55 AM GMT</t>
+          <t>Aug 22, 2026 10:55 AM GMT</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
@@ -7617,12 +7617,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T19:16:00Z</t>
+          <t>2026-08-22T09:27:00Z</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 7:21 PM GMT</t>
+          <t>Aug 22, 2026 9:56 AM GMT</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
@@ -7647,12 +7647,12 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T06:58:00Z</t>
+          <t>2026-08-22T07:51:00Z</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 7:47 AM GMT</t>
+          <t>Aug 22, 2026 8:56 AM GMT</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
@@ -7677,12 +7677,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T05:58:00Z</t>
+          <t>2026-08-22T07:40:00Z</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 6:55 AM GMT</t>
+          <t>Aug 22, 2026 7:47 AM GMT</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
@@ -7707,12 +7707,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T04:27:00Z</t>
+          <t>2026-08-22T07:37:00Z</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 5:56 AM GMT</t>
+          <t>Aug 22, 2026 7:38 AM GMT</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
@@ -7737,12 +7737,12 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T03:27:00Z</t>
+          <t>2026-08-22T07:33:00Z</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 4:25 AM GMT</t>
+          <t>Aug 22, 2026 7:34 AM GMT</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:58:00Z</t>
+          <t>2026-08-21T17:52:00Z</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 3:25 AM GMT</t>
+          <t>Aug 21, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -7781,7 +7781,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
@@ -7797,12 +7797,12 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:28:00Z</t>
+          <t>2026-08-21T13:59:00Z</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 2:56 AM GMT</t>
+          <t>Aug 21, 2026 2:12 PM GMT</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:12:00Z</t>
+          <t>2026-08-21T13:27:00Z</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 2:25 AM GMT</t>
+          <t>Aug 21, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
@@ -7857,12 +7857,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:04:00Z</t>
+          <t>2026-08-21T12:58:00Z</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 2:07 AM GMT</t>
+          <t>Aug 21, 2026 1:25 PM GMT</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
@@ -7887,12 +7887,12 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:01:00Z</t>
+          <t>2026-08-21T09:58:00Z</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 2:02 AM GMT</t>
+          <t>Aug 21, 2026 12:55 PM GMT</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -7901,7 +7901,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -7917,12 +7917,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:52:00Z</t>
+          <t>2026-08-21T09:27:00Z</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:56 AM GMT</t>
+          <t>Aug 21, 2026 9:56 AM GMT</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
@@ -7947,12 +7947,12 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:48:00Z</t>
+          <t>2026-08-21T08:58:00Z</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:50 AM GMT</t>
+          <t>Aug 21, 2026 9:25 AM GMT</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
@@ -7977,12 +7977,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:44:00Z</t>
+          <t>2026-08-21T07:57:00Z</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:46 AM GMT</t>
+          <t>Aug 21, 2026 8:55 AM GMT</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:39:00Z</t>
+          <t>2026-08-21T07:31:00Z</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:42 AM GMT</t>
+          <t>Aug 21, 2026 7:55 AM GMT</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:12:00Z</t>
+          <t>2026-08-20T19:16:00Z</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:36 AM GMT</t>
+          <t>Aug 20, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
@@ -8067,12 +8067,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T00:43:00Z</t>
+          <t>2026-08-20T06:58:00Z</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:10 AM GMT</t>
+          <t>Aug 20, 2026 7:47 AM GMT</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
@@ -8097,12 +8097,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>2026-08-15T13:05:00Z</t>
+          <t>2026-08-20T05:58:00Z</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Aug 15, 2026 1:07 PM GMT</t>
+          <t>Aug 20, 2026 6:55 AM GMT</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>2026-08-15T06:35:00Z</t>
+          <t>2026-08-20T04:27:00Z</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Aug 15, 2026 6:36 AM GMT</t>
+          <t>Aug 20, 2026 5:56 AM GMT</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
@@ -8157,12 +8157,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14T15:35:00Z</t>
+          <t>2026-08-20T03:27:00Z</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Aug 14, 2026 3:36 PM GMT</t>
+          <t>Aug 20, 2026 4:25 AM GMT</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14T13:05:00Z</t>
+          <t>2026-08-20T02:58:00Z</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Aug 14, 2026 1:06 PM GMT</t>
+          <t>Aug 20, 2026 3:25 AM GMT</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
@@ -8217,12 +8217,12 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14T07:35:00Z</t>
+          <t>2026-08-20T02:28:00Z</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Aug 14, 2026 7:36 AM GMT</t>
+          <t>Aug 20, 2026 2:56 AM GMT</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -8231,7 +8231,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14T05:35:00Z</t>
+          <t>2026-08-20T02:12:00Z</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Aug 14, 2026 5:36 AM GMT</t>
+          <t>Aug 20, 2026 2:25 AM GMT</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -8261,7 +8261,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
@@ -8277,12 +8277,12 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13T18:05:00Z</t>
+          <t>2026-08-20T02:04:00Z</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Aug 13, 2026 6:06 PM GMT</t>
+          <t>Aug 20, 2026 2:07 AM GMT</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
@@ -8307,12 +8307,12 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13T14:05:00Z</t>
+          <t>2026-08-20T02:01:00Z</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Aug 13, 2026 2:06 PM GMT</t>
+          <t>Aug 20, 2026 2:02 AM GMT</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13T08:35:00Z</t>
+          <t>2026-08-20T01:52:00Z</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Aug 13, 2026 8:36 AM GMT</t>
+          <t>Aug 20, 2026 1:56 AM GMT</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12T16:09:00Z</t>
+          <t>2026-08-20T01:48:00Z</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Aug 12, 2026 4:38 PM GMT</t>
+          <t>Aug 20, 2026 1:50 AM GMT</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
@@ -8397,12 +8397,12 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10T12:43:00Z</t>
+          <t>2026-08-20T01:44:00Z</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Aug 10, 2026 12:44 PM GMT</t>
+          <t>Aug 20, 2026 1:46 AM GMT</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10T10:42:00Z</t>
+          <t>2026-08-20T01:39:00Z</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Aug 10, 2026 12:40 PM GMT</t>
+          <t>Aug 20, 2026 1:42 AM GMT</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>118</v>
+        <v>3</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
@@ -8457,12 +8457,12 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10T10:12:00Z</t>
+          <t>2026-08-20T01:12:00Z</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Aug 10, 2026 10:40 AM GMT</t>
+          <t>Aug 20, 2026 1:36 AM GMT</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10T07:41:00Z</t>
+          <t>2026-08-20T00:43:00Z</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Aug 10, 2026 10:10 AM GMT</t>
+          <t>Aug 20, 2026 1:10 AM GMT</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
@@ -8517,12 +8517,12 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T20:38:00Z</t>
+          <t>2026-08-15T13:05:00Z</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 10:06 PM GMT</t>
+          <t>Aug 15, 2026 1:07 PM GMT</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T20:08:00Z</t>
+          <t>2026-08-15T06:35:00Z</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 8:36 PM GMT</t>
+          <t>Aug 15, 2026 6:36 AM GMT</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
@@ -8577,12 +8577,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T19:12:00Z</t>
+          <t>2026-08-14T15:35:00Z</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 8:06 PM GMT</t>
+          <t>Aug 14, 2026 3:36 PM GMT</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
@@ -8607,12 +8607,12 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T16:12:00Z</t>
+          <t>2026-08-14T13:05:00Z</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 7:10 PM GMT</t>
+          <t>Aug 14, 2026 1:06 PM GMT</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>178</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
@@ -8637,12 +8637,12 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T13:12:00Z</t>
+          <t>2026-08-14T07:35:00Z</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 4:10 PM GMT</t>
+          <t>Aug 14, 2026 7:36 AM GMT</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>178</v>
+        <v>1</v>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
@@ -8667,12 +8667,12 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T11:32:00Z</t>
+          <t>2026-08-14T05:35:00Z</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 1:11 PM GMT</t>
+          <t>Aug 14, 2026 5:36 AM GMT</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T06:57:00Z</t>
+          <t>2026-08-13T18:05:00Z</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 7:31 AM GMT</t>
+          <t>Aug 13, 2026 6:06 PM GMT</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
@@ -8727,12 +8727,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T03:38:00Z</t>
+          <t>2026-08-13T14:05:00Z</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 5:08 AM GMT</t>
+          <t>Aug 13, 2026 2:06 PM GMT</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -8741,7 +8741,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T03:12:00Z</t>
+          <t>2026-08-13T08:35:00Z</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 3:36 AM GMT</t>
+          <t>Aug 13, 2026 8:36 AM GMT</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -8771,7 +8771,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T02:38:00Z</t>
+          <t>2026-08-12T16:09:00Z</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 3:10 AM GMT</t>
+          <t>Aug 12, 2026 4:38 PM GMT</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
@@ -8817,12 +8817,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T01:54:00Z</t>
+          <t>2026-08-10T12:43:00Z</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 2:36 AM GMT</t>
+          <t>Aug 10, 2026 12:44 PM GMT</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
@@ -8847,12 +8847,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T01:13:00Z</t>
+          <t>2026-08-10T10:42:00Z</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 1:51 AM GMT</t>
+          <t>Aug 10, 2026 12:40 PM GMT</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
@@ -8877,12 +8877,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01T12:15:00Z</t>
+          <t>2026-08-10T10:12:00Z</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Aug 01, 2026 12:16 PM GMT</t>
+          <t>Aug 10, 2026 10:40 AM GMT</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
@@ -8902,360 +8902,360 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T04:56:00Z</t>
+          <t>2026-08-10T07:41:00Z</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 7:22 AM GMT</t>
+          <t>Aug 10, 2026 10:10 AM GMT</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T04:56:00Z</t>
+          <t>2026-08-09T20:38:00Z</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 7:22 AM GMT</t>
+          <t>Aug 09, 2026 10:06 PM GMT</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T02:27:00Z</t>
+          <t>2026-08-09T20:08:00Z</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 5:59 AM GMT</t>
+          <t>Aug 09, 2026 8:36 PM GMT</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>212</v>
+        <v>28</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T02:27:00Z</t>
+          <t>2026-08-09T19:12:00Z</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 5:59 AM GMT</t>
+          <t>Aug 09, 2026 8:06 PM GMT</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>212</v>
+        <v>54</v>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T01:35:00Z</t>
+          <t>2026-08-09T16:12:00Z</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 2:45 AM GMT</t>
+          <t>Aug 09, 2026 7:10 PM GMT</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T01:35:00Z</t>
+          <t>2026-08-09T13:12:00Z</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 2:45 AM GMT</t>
+          <t>Aug 09, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T21:45:00Z</t>
+          <t>2026-08-09T11:32:00Z</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 11:02 PM GMT</t>
+          <t>Aug 09, 2026 1:11 PM GMT</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T21:45:00Z</t>
+          <t>2026-08-07T06:57:00Z</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 11:02 PM GMT</t>
+          <t>Aug 07, 2026 7:31 AM GMT</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-08-07T03:38:00Z</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Aug 07, 2026 5:08 AM GMT</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-08-07T03:12:00Z</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Aug 07, 2026 3:36 AM GMT</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-08-07T02:38:00Z</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Aug 07, 2026 3:10 AM GMT</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-08-07T01:54:00Z</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Aug 07, 2026 2:36 AM GMT</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -9267,25 +9267,25 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:09:00Z</t>
+          <t>2026-08-07T01:13:00Z</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:10 AM GMT</t>
+          <t>Aug 07, 2026 1:51 AM GMT</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -9297,12 +9297,12 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:02:00Z</t>
+          <t>2026-08-01T12:15:00Z</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:09 AM GMT</t>
+          <t>Aug 01, 2026 12:16 PM GMT</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -9311,37 +9311,37 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:00Z</t>
+          <t>2026-07-30T04:56:00Z</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:10 AM GMT</t>
+          <t>Jul 30, 2026 7:22 AM GMT</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
@@ -9352,26 +9352,26 @@
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:00Z</t>
+          <t>2026-07-30T04:56:00Z</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:10 AM GMT</t>
+          <t>Jul 30, 2026 7:22 AM GMT</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
@@ -9382,26 +9382,26 @@
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:00Z</t>
+          <t>2026-07-30T02:27:00Z</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:06 AM GMT</t>
+          <t>Jul 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>6</v>
+        <v>212</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
@@ -9412,26 +9412,26 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T02:45:00Z</t>
+          <t>2026-07-30T02:27:00Z</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 2:47 AM GMT</t>
+          <t>Jul 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>2</v>
+        <v>212</v>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
@@ -9442,26 +9442,26 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20T08:26:00Z</t>
+          <t>2026-07-30T01:35:00Z</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>Jul 20, 2026 8:28 AM GMT</t>
+          <t>Jul 30, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
@@ -9472,26 +9472,26 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>2026-07-08T16:34:00Z</t>
+          <t>2026-07-30T01:35:00Z</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Jul 08, 2026 4:38 PM GMT</t>
+          <t>Jul 30, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
@@ -9502,26 +9502,26 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>2026-07-07T22:42:00Z</t>
+          <t>2026-07-29T21:45:00Z</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>Jul 07, 2026 10:49 PM GMT</t>
+          <t>Jul 29, 2026 11:02 PM GMT</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
@@ -9532,26 +9532,26 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>2026-07-06T16:05:00Z</t>
+          <t>2026-07-29T21:45:00Z</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Jul 06, 2026 4:11 PM GMT</t>
+          <t>Jul 29, 2026 11:02 PM GMT</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
@@ -9567,25 +9567,25 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -9597,25 +9597,25 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -9627,25 +9627,25 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -9657,325 +9657,325 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-07-24T11:09:00Z</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-07-24T11:02:00Z</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jul 24, 2026 11:09 AM GMT</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>164</v>
+        <v>7</v>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>252</v>
+        <v>10</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>252</v>
+        <v>10</v>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jul 24, 2026 11:06 AM GMT</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-07-24T02:45:00Z</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jul 24, 2026 2:47 AM GMT</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-07-20T08:26:00Z</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jul 20, 2026 8:28 AM GMT</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-07-08T16:34:00Z</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jul 08, 2026 4:38 PM GMT</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-07-07T22:42:00Z</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jul 07, 2026 10:49 PM GMT</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-07-06T16:05:00Z</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jul 06, 2026 4:11 PM GMT</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -9987,21 +9987,21 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
@@ -10017,21 +10017,21 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
@@ -10047,21 +10047,21 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T17:55:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>Jun 23, 2026 6:45 PM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>50</v>
+        <v>192</v>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
@@ -10077,21 +10077,21 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T21:08:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>Jun 22, 2026 9:40 PM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
@@ -10102,26 +10102,26 @@
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>20253</v>
+        <v>164</v>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
@@ -10132,26 +10132,26 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>20253</v>
+        <v>164</v>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
@@ -10162,26 +10162,26 @@
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T21:09:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>Jun 09, 2026 9:11 PM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>2</v>
+        <v>252</v>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
@@ -10192,26 +10192,26 @@
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1789</v>
+        <v>252</v>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
@@ -10222,26 +10222,26 @@
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1789</v>
+        <v>42</v>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
@@ -10252,26 +10252,26 @@
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>2026-06-08T19:11:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Jun 08, 2026 7:13 PM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
@@ -10287,21 +10287,21 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>903</v>
+        <v>98</v>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>903</v>
+        <v>98</v>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
@@ -10347,25 +10347,25 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -10377,25 +10377,25 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -10407,25 +10407,25 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -10437,25 +10437,25 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -10467,25 +10467,25 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-06-23T17:55:00Z</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>Jun 23, 2026 6:45 PM GMT</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -10497,222 +10497,222 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-06-22T21:08:00Z</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>Jun 22, 2026 9:40 PM GMT</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>76</v>
+        <v>20253</v>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>76</v>
+        <v>20253</v>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-09T21:09:00Z</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 09, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>122</v>
+        <v>1789</v>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>122</v>
+        <v>1789</v>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-06-08T19:11:00Z</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>Jun 08, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
@@ -10721,28 +10721,28 @@
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>17374</v>
+        <v>903</v>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
@@ -10751,28 +10751,28 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>17374</v>
+        <v>903</v>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
@@ -10792,17 +10792,17 @@
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
@@ -10827,21 +10827,21 @@
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E202" s="5" t="n">
-        <v>673</v>
+        <v>57</v>
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
@@ -10857,21 +10857,21 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>673</v>
+        <v>57</v>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
@@ -10882,26 +10882,26 @@
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10T21:09:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>May 10, 2026 9:11 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
@@ -10912,26 +10912,26 @@
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09T19:11:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>May 09, 2026 7:13 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E205" s="5" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
@@ -10947,21 +10947,21 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
@@ -10977,21 +10977,21 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E207" s="5" t="n">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
@@ -11002,26 +11002,26 @@
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E208" s="5" t="n">
-        <v>1395</v>
+        <v>122</v>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
@@ -11032,26 +11032,26 @@
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>1395</v>
+        <v>122</v>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
@@ -11067,21 +11067,21 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E210" s="5" t="n">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
@@ -11097,21 +11097,21 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
@@ -11122,17 +11122,17 @@
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
@@ -11141,28 +11141,28 @@
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>162</v>
+        <v>17374</v>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
@@ -11171,71 +11171,71 @@
         </is>
       </c>
       <c r="E213" s="5" t="n">
-        <v>162</v>
+        <v>17374</v>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E215" s="5" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -11247,25 +11247,25 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E216" s="5" t="n">
-        <v>88</v>
+        <v>673</v>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -11277,85 +11277,85 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E217" s="5" t="n">
-        <v>88</v>
+        <v>673</v>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-10T21:09:00Z</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 10, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E218" s="5" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-05-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>May 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E219" s="5" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -11367,25 +11367,25 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E220" s="5" t="n">
-        <v>273</v>
+        <v>132</v>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -11397,85 +11397,85 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E221" s="5" t="n">
-        <v>273</v>
+        <v>132</v>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E222" s="5" t="n">
-        <v>273</v>
+        <v>1395</v>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E223" s="5" t="n">
-        <v>273</v>
+        <v>1395</v>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -11487,25 +11487,25 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E224" s="5" t="n">
-        <v>242</v>
+        <v>72</v>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -11517,42 +11517,42 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E225" s="5" t="n">
-        <v>242</v>
+        <v>72</v>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="E226" s="5" t="n">
-        <v>17272</v>
+        <v>162</v>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
@@ -11572,17 +11572,17 @@
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
@@ -11591,7 +11591,7 @@
         </is>
       </c>
       <c r="E227" s="5" t="n">
-        <v>17272</v>
+        <v>162</v>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
@@ -11607,21 +11607,21 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E228" s="5" t="n">
-        <v>1187</v>
+        <v>78</v>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
@@ -11637,21 +11637,21 @@
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">
-        <v>1187</v>
+        <v>78</v>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
@@ -11667,21 +11667,21 @@
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E230" s="5" t="n">
-        <v>4284</v>
+        <v>88</v>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
@@ -11697,21 +11697,21 @@
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E231" s="5" t="n">
-        <v>4284</v>
+        <v>88</v>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
@@ -11722,26 +11722,26 @@
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:28:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E232" s="5" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
@@ -11752,26 +11752,26 @@
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:26:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E233" s="5" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
@@ -11787,21 +11787,21 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E234" s="5" t="n">
-        <v>96</v>
+        <v>273</v>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
@@ -11817,21 +11817,21 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
-        <v>30</v>
+        <v>273</v>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
@@ -11842,26 +11842,26 @@
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E236" s="5" t="n">
-        <v>2</v>
+        <v>273</v>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
@@ -11877,21 +11877,21 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E237" s="5" t="n">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
@@ -11902,26 +11902,26 @@
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E238" s="5" t="n">
-        <v>2</v>
+        <v>242</v>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
@@ -11932,26 +11932,26 @@
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E239" s="5" t="n">
-        <v>3</v>
+        <v>242</v>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
@@ -11967,12 +11967,12 @@
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="E240" s="5" t="n">
-        <v>78</v>
+        <v>17272</v>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
@@ -11992,26 +11992,26 @@
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E241" s="5" t="n">
-        <v>50</v>
+        <v>17272</v>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
@@ -12027,21 +12027,21 @@
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E242" s="5" t="n">
-        <v>50</v>
+        <v>1187</v>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
@@ -12057,25 +12057,25 @@
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E243" s="5" t="n">
-        <v>203</v>
+        <v>1187</v>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -12087,25 +12087,25 @@
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E244" s="5" t="n">
-        <v>203</v>
+        <v>4284</v>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -12117,85 +12117,85 @@
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E245" s="5" t="n">
-        <v>150</v>
+        <v>4284</v>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E246" s="5" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E247" s="5" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -12207,25 +12207,25 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E248" s="5" t="n">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -12237,55 +12237,55 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E249" s="5" t="n">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E250" s="5" t="n">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -12297,145 +12297,145 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E251" s="5" t="n">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E252" s="5" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E253" s="5" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E254" s="5" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E255" s="5" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -12447,25 +12447,25 @@
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E256" s="5" t="n">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -12477,21 +12477,21 @@
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E257" s="5" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
@@ -12502,26 +12502,26 @@
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E258" s="5" t="n">
-        <v>2</v>
+        <v>203</v>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
@@ -12532,26 +12532,26 @@
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E259" s="5" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
@@ -12562,26 +12562,26 @@
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E260" s="5" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
@@ -12597,21 +12597,21 @@
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E261" s="5" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
@@ -12627,21 +12627,21 @@
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E262" s="5" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
@@ -12657,21 +12657,21 @@
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E263" s="5" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
@@ -12687,21 +12687,21 @@
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E264" s="5" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
@@ -12717,21 +12717,21 @@
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E265" s="5" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
@@ -12747,21 +12747,21 @@
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E266" s="5" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
@@ -12777,21 +12777,21 @@
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E267" s="5" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
@@ -12807,21 +12807,21 @@
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E268" s="5" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
@@ -12832,26 +12832,26 @@
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E269" s="5" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
@@ -12867,21 +12867,21 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E270" s="5" t="n">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
@@ -12892,26 +12892,26 @@
     <row r="271">
       <c r="A271" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E271" s="5" t="n">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
@@ -12927,21 +12927,21 @@
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E272" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
@@ -12957,21 +12957,21 @@
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E273" s="5" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
@@ -12987,21 +12987,21 @@
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E274" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
@@ -13012,26 +13012,26 @@
     <row r="275">
       <c r="A275" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E275" s="5" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
@@ -13042,30 +13042,30 @@
     <row r="276">
       <c r="A276" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E276" s="5" t="n">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -13077,25 +13077,25 @@
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E277" s="5" t="n">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -13107,25 +13107,25 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E278" s="5" t="n">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -13137,25 +13137,25 @@
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E279" s="5" t="n">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -13167,85 +13167,85 @@
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E280" s="5" t="n">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E281" s="5" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E282" s="5" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -13257,12 +13257,12 @@
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
@@ -13271,11 +13271,11 @@
         </is>
       </c>
       <c r="E283" s="5" t="n">
-        <v>282</v>
+        <v>95</v>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
@@ -13301,88 +13301,88 @@
         </is>
       </c>
       <c r="E284" s="5" t="n">
-        <v>282</v>
+        <v>95</v>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E285" s="5" t="n">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E286" s="5" t="n">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
@@ -13391,28 +13391,28 @@
         </is>
       </c>
       <c r="E287" s="5" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
@@ -13421,67 +13421,67 @@
         </is>
       </c>
       <c r="E288" s="5" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E289" s="5" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E290" s="5" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
@@ -13497,25 +13497,25 @@
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E291" s="5" t="n">
-        <v>4234</v>
+        <v>207</v>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -13527,145 +13527,145 @@
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E292" s="5" t="n">
-        <v>4234</v>
+        <v>207</v>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E294" s="5" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E295" s="5" t="n">
-        <v>1595</v>
+        <v>2</v>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E296" s="5" t="n">
-        <v>1595</v>
+        <v>2</v>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -13677,55 +13677,55 @@
       </c>
       <c r="B297" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E297" s="5" t="n">
-        <v>4982</v>
+        <v>282</v>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E298" s="5" t="n">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -13737,85 +13737,85 @@
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E299" s="5" t="n">
-        <v>1070</v>
+        <v>127</v>
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E300" s="5" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E301" s="5" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -13827,25 +13827,25 @@
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E302" s="5" t="n">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="F302" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -13857,25 +13857,25 @@
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E303" s="5" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -13887,25 +13887,25 @@
       </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E304" s="5" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -13917,21 +13917,21 @@
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E305" s="5" t="n">
-        <v>137</v>
+        <v>4234</v>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
@@ -13947,21 +13947,21 @@
       </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E306" s="5" t="n">
-        <v>38</v>
+        <v>4234</v>
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
@@ -13972,37 +13972,457 @@
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:46:00Z</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B308" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27T14:45:00Z</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
+        </is>
+      </c>
+      <c r="D308" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="inlineStr">
+        <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B307" s="5" t="inlineStr">
+      <c r="B309" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F309" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B310" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-23T23:57:00Z</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F310" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B311" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T16:24:00Z</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="n">
+        <v>4982</v>
+      </c>
+      <c r="F311" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B312" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16T15:14:00Z</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
+        </is>
+      </c>
+      <c r="D312" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F312" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T21:13:00Z</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / ams-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F313" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15T04:24:00Z</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand - Vulncat</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F314" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="inlineStr">
+        <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-10T15:08:00Z</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F315" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F316" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D318" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F318" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F319" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
         <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C307" s="5" t="inlineStr">
+      <c r="C320" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D307" s="5" t="inlineStr">
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F320" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E307" s="5" t="n">
+      <c r="E321" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F307" s="5" t="inlineStr">
+      <c r="F321" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: September 02, 2026</t>
+    <row r="322">
+      <c r="A322" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: September 16, 2026</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14875,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: September 2, 2026 (Month-end update; Aug 2026 finalized with 100+ Vulncat outage events Aug 17-31, FedRAMP Portal/API outage Aug 29 (105 min), Aug 26-27 maintenance window; Sep 2026 stub added with partial data through Sep 2, 2026; all BST times converted to GMT).</t>
+          <t>Last updated: September 16, 2026 (Mid-month update; Sep 2026 partial data through Sep 16, 2026; added 6 new outages Sep 7-14 and non-outage events Sep 7-14; all BST times converted to GMT).</t>
         </is>
       </c>
     </row>
@@ -15142,7 +15562,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Last updated: September 2, 2026</t>
+          <t>Last updated: September 16, 2026</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15845,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>1</v>
+        <v>0.9999074074074074</v>
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
@@ -15633,7 +16053,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>1</v>
+        <v>0.9999074074074074</v>
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
@@ -16024,7 +16444,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>1</v>
+        <v>0.9999537037037037</v>
       </c>
       <c r="K20" s="15" t="inlineStr">
         <is>
@@ -16259,7 +16679,7 @@
         <v>0.8974014336917563</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>0.9906712962962962</v>
+        <v>0.9905324074074074</v>
       </c>
       <c r="K26" s="15" t="inlineStr">
         <is>

--- a/FoD_Uptime_Report_2026.xlsx
+++ b/FoD_Uptime_Report_2026.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5. Sep 2026 maintenance: EU Sep 18, SGP Sep 24, FedRAMP Sep 25 with no associated outages; Sep 4-5 AMS maintenance window; Sep 22 AMS service degradation (not counted). Aug 26-27 maintenance covered FedRAMP, EMEA, EU, AMS with no associated outages.</t>
+          <t>5. Sep 2026 maintenance: EU Sep 18, SGP Sep 24, FedRAMP Sep 25; Sep 4-5 AMS maintenance; Sep 22 AMS service degradation (not counted). Oct partial (through Oct 15): 0 core service outages; SGP service degradation Oct 3 and Oct 12, AMS service degradation Oct 5 (none counted toward official figure).</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>* October 2026 is in progress (partial through October 2, 2026). Will be finalized after October 31, 2026.</t>
+          <t>* October 2026 is in progress (partial through October 15, 2026). Will be finalized after October 31, 2026.</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Month in progress. Partial data through October 2, 2026. Will be finalized after October 31, 2026.</t>
+          <t>Month in progress. Partial data through October 15, 2026. Will be finalized after October 31, 2026.</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F349"/>
+  <dimension ref="A1:F355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2092,26 +2092,26 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T04:26:00Z</t>
+          <t>2026-10-12T06:16:00Z</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Oct 01, 2026 5:49 AM GMT</t>
+          <t>Oct 12, 2026 10:02 PM GMT</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>83</v>
+        <v>946</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -2122,26 +2122,26 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T04:26:00Z</t>
+          <t>2026-10-12T06:16:00Z</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Oct 01, 2026 5:49 AM GMT</t>
+          <t>Oct 12, 2026 10:02 PM GMT</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>83</v>
+        <v>946</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -2152,26 +2152,26 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T02:13:00Z</t>
+          <t>2026-10-05T02:36:00Z</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Oct 01, 2026 3:39 AM GMT</t>
+          <t>Oct 05, 2026 5:42 AM GMT</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -2182,26 +2182,26 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T02:13:00Z</t>
+          <t>2026-10-05T02:36:00Z</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Oct 01, 2026 3:39 AM GMT</t>
+          <t>Oct 05, 2026 5:42 AM GMT</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -2212,26 +2212,26 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:00Z</t>
+          <t>2026-10-03T05:54:00Z</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Oct 01, 2026 1:55 AM GMT</t>
+          <t>Oct 04, 2026 5:21 AM GMT</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>113</v>
+        <v>1407</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -2242,26 +2242,26 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-10-01T00:02:00Z</t>
+          <t>2026-10-03T05:54:00Z</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Oct 01, 2026 1:55 AM GMT</t>
+          <t>Oct 04, 2026 5:21 AM GMT</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>113</v>
+        <v>1407</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-25T20:39:00Z</t>
+          <t>2026-10-01T04:26:00Z</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sep 25, 2026 10:19 PM GMT</t>
+          <t>Oct 01, 2026 5:49 AM GMT</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
@@ -2307,25 +2307,25 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-09-25T20:39:00Z</t>
+          <t>2026-10-01T04:26:00Z</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Sep 25, 2026 10:19 PM GMT</t>
+          <t>Oct 01, 2026 5:49 AM GMT</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
@@ -2337,25 +2337,25 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24T15:16:00Z</t>
+          <t>2026-10-01T02:13:00Z</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Sep 24, 2026 5:45 PM GMT</t>
+          <t>Oct 01, 2026 3:39 AM GMT</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
@@ -2367,85 +2367,85 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-09-24T15:16:00Z</t>
+          <t>2026-10-01T02:13:00Z</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Sep 24, 2026 5:45 PM GMT</t>
+          <t>Oct 01, 2026 3:39 AM GMT</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22T10:34:00Z</t>
+          <t>2026-10-01T00:02:00Z</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Sep 22, 2026 1:31 PM GMT</t>
+          <t>Oct 01, 2026 1:55 AM GMT</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-09-22T10:34:00Z</t>
+          <t>2026-10-01T00:02:00Z</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Sep 22, 2026 1:31 PM GMT</t>
+          <t>Oct 01, 2026 1:55 AM GMT</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
     </row>
@@ -2457,21 +2457,21 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-09-18T18:19:00Z</t>
+          <t>2026-09-25T20:39:00Z</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Sep 18, 2026 8:04 PM GMT</t>
+          <t>Sep 25, 2026 10:19 PM GMT</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-09-18T18:19:00Z</t>
+          <t>2026-09-25T20:39:00Z</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Sep 18, 2026 8:04 PM GMT</t>
+          <t>Sep 25, 2026 10:19 PM GMT</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -2512,26 +2512,26 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2026-09-17T21:11:00Z</t>
+          <t>2026-09-24T15:16:00Z</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Sep 17, 2026 10:04 PM GMT</t>
+          <t>Sep 24, 2026 5:45 PM GMT</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -2542,26 +2542,26 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14T15:45:00Z</t>
+          <t>2026-09-24T15:16:00Z</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Sep 14, 2026 3:49 PM GMT</t>
+          <t>Sep 24, 2026 5:45 PM GMT</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>4</v>
+        <v>149</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -2572,26 +2572,26 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>2026-09-13T18:11:00Z</t>
+          <t>2026-09-22T10:34:00Z</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Sep 13, 2026 6:13 PM GMT</t>
+          <t>Sep 22, 2026 1:31 PM GMT</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -2607,21 +2607,21 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11T20:53:00Z</t>
+          <t>2026-09-22T10:34:00Z</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Sep 11, 2026 11:14 PM GMT</t>
+          <t>Sep 22, 2026 1:31 PM GMT</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -2632,26 +2632,26 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11T20:53:00Z</t>
+          <t>2026-09-18T18:19:00Z</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Sep 11, 2026 11:14 PM GMT</t>
+          <t>Sep 18, 2026 8:04 PM GMT</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -2667,21 +2667,21 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11T18:19:00Z</t>
+          <t>2026-09-18T18:19:00Z</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Sep 14, 2026 5:35 PM GMT</t>
+          <t>Sep 18, 2026 8:04 PM GMT</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>4276</v>
+        <v>105</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -2692,26 +2692,26 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11T18:19:00Z</t>
+          <t>2026-09-17T21:11:00Z</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Sep 14, 2026 5:35 PM GMT</t>
+          <t>Sep 17, 2026 10:04 PM GMT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4276</v>
+        <v>53</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -2722,17 +2722,17 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-09-10T14:56:00Z</t>
+          <t>2026-09-14T15:45:00Z</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Sep 10, 2026 5:22 PM GMT</t>
+          <t>Sep 14, 2026 3:49 PM GMT</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>146</v>
+        <v>4</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -2752,26 +2752,26 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2026-09-10T14:56:00Z</t>
+          <t>2026-09-13T18:11:00Z</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Sep 10, 2026 5:22 PM GMT</t>
+          <t>Sep 13, 2026 6:13 PM GMT</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-09-09T23:31:00Z</t>
+          <t>2026-09-11T20:53:00Z</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Sep 10, 2026 3:24 AM GMT</t>
+          <t>Sep 11, 2026 11:14 PM GMT</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>2026-09-09T23:31:00Z</t>
+          <t>2026-09-11T20:53:00Z</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Sep 10, 2026 3:24 AM GMT</t>
+          <t>Sep 11, 2026 11:14 PM GMT</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -2842,26 +2842,26 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-09-09T07:32:00Z</t>
+          <t>2026-09-11T18:19:00Z</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Sep 09, 2026 7:34 AM GMT</t>
+          <t>Sep 14, 2026 5:35 PM GMT</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>4276</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -2872,26 +2872,26 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>2026-09-07T21:31:00Z</t>
+          <t>2026-09-11T18:19:00Z</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Sep 07, 2026 9:33 PM GMT</t>
+          <t>Sep 14, 2026 5:35 PM GMT</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>4276</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -2902,26 +2902,26 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-09-07T02:29:00Z</t>
+          <t>2026-09-10T14:56:00Z</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Sep 07, 2026 2:31 AM GMT</t>
+          <t>Sep 10, 2026 5:22 PM GMT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -2932,26 +2932,26 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>2026-09-07T02:16:00Z</t>
+          <t>2026-09-10T14:56:00Z</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Sep 07, 2026 2:20 AM GMT</t>
+          <t>Sep 10, 2026 5:22 PM GMT</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -2962,26 +2962,26 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-09-05T18:38:00Z</t>
+          <t>2026-09-09T23:31:00Z</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Sep 05, 2026 6:39 PM GMT</t>
+          <t>Sep 10, 2026 3:24 AM GMT</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>233</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -2992,26 +2992,26 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04T22:33:00Z</t>
+          <t>2026-09-09T23:31:00Z</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Sep 05, 2026 4:41 PM GMT</t>
+          <t>Sep 10, 2026 3:24 AM GMT</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1088</v>
+        <v>233</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -3022,26 +3022,26 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04T22:33:00Z</t>
+          <t>2026-09-09T07:32:00Z</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Sep 05, 2026 4:41 PM GMT</t>
+          <t>Sep 09, 2026 7:34 AM GMT</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>1088</v>
+        <v>2</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -3057,21 +3057,21 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04T09:27:00Z</t>
+          <t>2026-09-07T21:31:00Z</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Sep 04, 2026 9:28 AM GMT</t>
+          <t>Sep 07, 2026 9:33 PM GMT</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04T01:28:00Z</t>
+          <t>2026-09-07T02:29:00Z</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Sep 04, 2026 1:54 AM GMT</t>
+          <t>Sep 07, 2026 2:31 AM GMT</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03T23:47:00Z</t>
+          <t>2026-09-07T02:16:00Z</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Sep 04, 2026 1:26 AM GMT</t>
+          <t>Sep 07, 2026 2:20 AM GMT</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03T23:31:00Z</t>
+          <t>2026-09-05T18:38:00Z</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Sep 03, 2026 11:45 PM GMT</t>
+          <t>Sep 05, 2026 6:39 PM GMT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -3172,26 +3172,26 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03T20:19:00Z</t>
+          <t>2026-09-04T22:33:00Z</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Sep 03, 2026 8:27 PM GMT</t>
+          <t>Sep 05, 2026 4:41 PM GMT</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>8</v>
+        <v>1088</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -3202,26 +3202,26 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03T08:27:00Z</t>
+          <t>2026-09-04T22:33:00Z</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Sep 03, 2026 8:57 AM GMT</t>
+          <t>Sep 05, 2026 4:41 PM GMT</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>30</v>
+        <v>1088</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026-09-03T06:21:00Z</t>
+          <t>2026-09-04T09:27:00Z</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Sep 03, 2026 8:26 AM GMT</t>
+          <t>Sep 04, 2026 9:28 AM GMT</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -3267,12 +3267,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02T18:51:00Z</t>
+          <t>2026-09-04T01:28:00Z</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Sep 02, 2026 6:57 PM GMT</t>
+          <t>Sep 04, 2026 1:54 AM GMT</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02T10:28:00Z</t>
+          <t>2026-09-03T23:47:00Z</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Sep 02, 2026 10:34 AM GMT</t>
+          <t>Sep 04, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -3327,12 +3327,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-09-02T02:55:00Z</t>
+          <t>2026-09-03T23:31:00Z</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Sep 02, 2026 3:03 AM GMT</t>
+          <t>Sep 03, 2026 11:45 PM GMT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T18:51:00Z</t>
+          <t>2026-09-03T20:19:00Z</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 6:53 PM GMT</t>
+          <t>Sep 03, 2026 8:27 PM GMT</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3371,7 +3371,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
@@ -3387,12 +3387,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T15:56:00Z</t>
+          <t>2026-09-03T08:27:00Z</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 4:11 PM GMT</t>
+          <t>Sep 03, 2026 8:57 AM GMT</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -3417,12 +3417,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T14:59:00Z</t>
+          <t>2026-09-03T06:21:00Z</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 3:51 PM GMT</t>
+          <t>Sep 03, 2026 8:26 AM GMT</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -3447,12 +3447,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T13:58:00Z</t>
+          <t>2026-09-02T18:51:00Z</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 2:57 PM GMT</t>
+          <t>Sep 02, 2026 6:57 PM GMT</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T12:59:00Z</t>
+          <t>2026-09-02T10:28:00Z</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 1:57 PM GMT</t>
+          <t>Sep 02, 2026 10:34 AM GMT</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -3507,12 +3507,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T11:29:00Z</t>
+          <t>2026-09-02T02:55:00Z</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 12:57 PM GMT</t>
+          <t>Sep 02, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T10:58:00Z</t>
+          <t>2026-09-01T18:51:00Z</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 11:27 AM GMT</t>
+          <t>Sep 01, 2026 6:53 PM GMT</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T10:27:00Z</t>
+          <t>2026-09-01T15:56:00Z</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 10:57 AM GMT</t>
+          <t>Sep 01, 2026 4:11 PM GMT</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -3597,12 +3597,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T09:59:00Z</t>
+          <t>2026-09-01T14:59:00Z</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 10:26 AM GMT</t>
+          <t>Sep 01, 2026 3:51 PM GMT</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T08:58:00Z</t>
+          <t>2026-09-01T13:58:00Z</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 9:57 AM GMT</t>
+          <t>Sep 01, 2026 2:57 PM GMT</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01T08:28:00Z</t>
+          <t>2026-09-01T12:59:00Z</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Sep 01, 2026 8:57 AM GMT</t>
+          <t>Sep 01, 2026 1:57 PM GMT</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T19:58:00Z</t>
+          <t>2026-09-01T11:29:00Z</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 8:36 PM GMT</t>
+          <t>Sep 01, 2026 12:57 PM GMT</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3701,11 +3701,11 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T19:28:00Z</t>
+          <t>2026-09-01T10:58:00Z</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 7:56 PM GMT</t>
+          <t>Sep 01, 2026 11:27 AM GMT</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3731,11 +3731,11 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -3747,12 +3747,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T18:56:00Z</t>
+          <t>2026-09-01T10:27:00Z</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 7:26 PM GMT</t>
+          <t>Sep 01, 2026 10:57 AM GMT</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -3777,12 +3777,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T10:59:00Z</t>
+          <t>2026-09-01T09:59:00Z</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 11:06 AM GMT</t>
+          <t>Sep 01, 2026 10:26 AM GMT</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3791,11 +3791,11 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T09:59:00Z</t>
+          <t>2026-09-01T08:58:00Z</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 10:27 AM GMT</t>
+          <t>Sep 01, 2026 9:57 AM GMT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3821,11 +3821,11 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31T08:01:00Z</t>
+          <t>2026-09-01T08:28:00Z</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Aug 31, 2026 9:57 AM GMT</t>
+          <t>Sep 01, 2026 8:57 AM GMT</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3851,11 +3851,11 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -3867,12 +3867,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T21:29:00Z</t>
+          <t>2026-08-31T19:58:00Z</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 9:36 PM GMT</t>
+          <t>Aug 31, 2026 8:36 PM GMT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
@@ -3897,12 +3897,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T20:28:00Z</t>
+          <t>2026-08-31T19:28:00Z</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 9:26 PM GMT</t>
+          <t>Aug 31, 2026 7:56 PM GMT</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T19:28:00Z</t>
+          <t>2026-08-31T18:56:00Z</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 8:26 PM GMT</t>
+          <t>Aug 31, 2026 7:26 PM GMT</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -3957,12 +3957,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T10:59:00Z</t>
+          <t>2026-08-31T10:59:00Z</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 11:26 AM GMT</t>
+          <t>Aug 31, 2026 11:06 AM GMT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -3987,12 +3987,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T10:35:00Z</t>
+          <t>2026-08-31T09:59:00Z</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 10:56 AM GMT</t>
+          <t>Aug 31, 2026 10:27 AM GMT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>2026-08-30T08:29:00Z</t>
+          <t>2026-08-31T08:01:00Z</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Aug 30, 2026 9:26 AM GMT</t>
+          <t>Aug 31, 2026 9:57 AM GMT</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T19:28:00Z</t>
+          <t>2026-08-30T21:29:00Z</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 7:33 PM GMT</t>
+          <t>Aug 30, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
@@ -4077,12 +4077,12 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T16:06:00Z</t>
+          <t>2026-08-30T20:28:00Z</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 7:26 PM GMT</t>
+          <t>Aug 30, 2026 9:26 PM GMT</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
@@ -4107,12 +4107,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T12:29:00Z</t>
+          <t>2026-08-30T19:28:00Z</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 12:57 PM GMT</t>
+          <t>Aug 30, 2026 8:26 PM GMT</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T12:15:00Z</t>
+          <t>2026-08-30T10:59:00Z</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 12:27 PM GMT</t>
+          <t>Aug 30, 2026 11:26 AM GMT</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T11:59:00Z</t>
+          <t>2026-08-30T10:35:00Z</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 12:12 PM GMT</t>
+          <t>Aug 30, 2026 10:56 AM GMT</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T08:28:00Z</t>
+          <t>2026-08-30T08:29:00Z</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 8:56 AM GMT</t>
+          <t>Aug 30, 2026 9:26 AM GMT</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
@@ -4227,21 +4227,21 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T00:09:00Z</t>
+          <t>2026-08-29T19:28:00Z</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 1:54 AM GMT</t>
+          <t>Aug 29, 2026 7:33 PM GMT</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
@@ -4257,21 +4257,21 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>2026-08-29T00:09:00Z</t>
+          <t>2026-08-29T16:06:00Z</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Aug 29, 2026 1:52 AM GMT</t>
+          <t>Aug 29, 2026 7:26 PM GMT</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>103</v>
+        <v>200</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
@@ -4287,12 +4287,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T17:54:00Z</t>
+          <t>2026-08-29T12:29:00Z</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 7:42 PM GMT</t>
+          <t>Aug 29, 2026 12:57 PM GMT</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -4301,7 +4301,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T16:53:00Z</t>
+          <t>2026-08-29T12:15:00Z</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 5:52 PM GMT</t>
+          <t>Aug 29, 2026 12:27 PM GMT</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
@@ -4347,12 +4347,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T12:31:00Z</t>
+          <t>2026-08-29T11:59:00Z</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 12:56 PM GMT</t>
+          <t>Aug 29, 2026 12:12 PM GMT</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T12:28:00Z</t>
+          <t>2026-08-29T08:28:00Z</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 12:29 PM GMT</t>
+          <t>Aug 29, 2026 8:56 AM GMT</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
@@ -4407,21 +4407,21 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T11:58:00Z</t>
+          <t>2026-08-29T00:09:00Z</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 12:27 PM GMT</t>
+          <t>Aug 29, 2026 1:54 AM GMT</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
@@ -4437,21 +4437,21 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T11:31:00Z</t>
+          <t>2026-08-29T00:09:00Z</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 11:56 AM GMT</t>
+          <t>Aug 29, 2026 1:52 AM GMT</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T11:15:00Z</t>
+          <t>2026-08-28T17:54:00Z</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 11:28 AM GMT</t>
+          <t>Aug 28, 2026 7:42 PM GMT</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T11:05:00Z</t>
+          <t>2026-08-28T16:53:00Z</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 11:11 AM GMT</t>
+          <t>Aug 28, 2026 5:52 PM GMT</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
@@ -4527,12 +4527,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T10:12:00Z</t>
+          <t>2026-08-28T12:31:00Z</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 10:21 AM GMT</t>
+          <t>Aug 28, 2026 12:56 PM GMT</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
@@ -4557,12 +4557,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T10:08:00Z</t>
+          <t>2026-08-28T12:28:00Z</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 10:10 AM GMT</t>
+          <t>Aug 28, 2026 12:29 PM GMT</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T10:02:00Z</t>
+          <t>2026-08-28T11:58:00Z</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 10:07 AM GMT</t>
+          <t>Aug 28, 2026 12:27 PM GMT</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
@@ -4617,12 +4617,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28T07:57:00Z</t>
+          <t>2026-08-28T11:31:00Z</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Aug 28, 2026 9:58 AM GMT</t>
+          <t>Aug 28, 2026 11:56 AM GMT</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>121</v>
+        <v>25</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T16:53:00Z</t>
+          <t>2026-08-28T11:15:00Z</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 5:58 PM GMT</t>
+          <t>Aug 28, 2026 11:28 AM GMT</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
@@ -4677,12 +4677,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T12:27:00Z</t>
+          <t>2026-08-28T11:05:00Z</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:56 PM GMT</t>
+          <t>Aug 28, 2026 11:11 AM GMT</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T11:58:00Z</t>
+          <t>2026-08-28T10:12:00Z</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 12:26 PM GMT</t>
+          <t>Aug 28, 2026 10:21 AM GMT</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T08:58:00Z</t>
+          <t>2026-08-28T10:08:00Z</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 11:56 AM GMT</t>
+          <t>Aug 28, 2026 10:10 AM GMT</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
@@ -4767,12 +4767,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T07:58:00Z</t>
+          <t>2026-08-28T10:02:00Z</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 8:56 AM GMT</t>
+          <t>Aug 28, 2026 10:07 AM GMT</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
@@ -4792,26 +4792,26 @@
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T04:03:00Z</t>
+          <t>2026-08-28T07:57:00Z</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 6:07 AM GMT</t>
+          <t>Aug 28, 2026 9:58 AM GMT</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
@@ -4822,26 +4822,26 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T04:03:00Z</t>
+          <t>2026-08-27T16:53:00Z</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 6:07 AM GMT</t>
+          <t>Aug 27, 2026 5:58 PM GMT</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
@@ -4852,26 +4852,26 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T01:11:00Z</t>
+          <t>2026-08-27T12:27:00Z</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:38 AM GMT</t>
+          <t>Aug 27, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
@@ -4882,26 +4882,26 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>2026-08-27T01:11:00Z</t>
+          <t>2026-08-27T11:58:00Z</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:38 AM GMT</t>
+          <t>Aug 27, 2026 12:26 PM GMT</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
@@ -4912,26 +4912,26 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T23:42:00Z</t>
+          <t>2026-08-27T08:58:00Z</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:10 AM GMT</t>
+          <t>Aug 27, 2026 11:56 AM GMT</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
@@ -4942,26 +4942,26 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T23:42:00Z</t>
+          <t>2026-08-27T07:58:00Z</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Aug 27, 2026 1:10 AM GMT</t>
+          <t>Aug 27, 2026 8:56 AM GMT</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
@@ -4972,26 +4972,26 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T21:32:00Z</t>
+          <t>2026-08-27T04:03:00Z</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 9:34 PM GMT</t>
+          <t>Aug 27, 2026 6:07 AM GMT</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
@@ -5002,26 +5002,26 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T21:28:00Z</t>
+          <t>2026-08-27T04:03:00Z</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 9:31 PM GMT</t>
+          <t>Aug 27, 2026 6:07 AM GMT</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>124</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
@@ -5037,21 +5037,21 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T21:06:00Z</t>
+          <t>2026-08-27T01:11:00Z</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 10:38 PM GMT</t>
+          <t>Aug 27, 2026 1:38 AM GMT</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
@@ -5067,21 +5067,21 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T21:06:00Z</t>
+          <t>2026-08-27T01:11:00Z</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 10:38 PM GMT</t>
+          <t>Aug 27, 2026 1:38 AM GMT</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
@@ -5092,26 +5092,26 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T20:58:00Z</t>
+          <t>2026-08-26T23:42:00Z</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 9:26 PM GMT</t>
+          <t>Aug 27, 2026 1:10 AM GMT</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
@@ -5122,26 +5122,26 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T20:55:00Z</t>
+          <t>2026-08-26T23:42:00Z</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 8:56 PM GMT</t>
+          <t>Aug 27, 2026 1:10 AM GMT</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T12:59:00Z</t>
+          <t>2026-08-26T21:32:00Z</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 1:00 PM GMT</t>
+          <t>Aug 26, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T12:41:00Z</t>
+          <t>2026-08-26T21:28:00Z</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 12:43 PM GMT</t>
+          <t>Aug 26, 2026 9:31 PM GMT</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
@@ -5212,26 +5212,26 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T12:39:00Z</t>
+          <t>2026-08-26T21:06:00Z</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 12:40 PM GMT</t>
+          <t>Aug 26, 2026 10:38 PM GMT</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
@@ -5242,26 +5242,26 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T12:28:00Z</t>
+          <t>2026-08-26T21:06:00Z</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 12:37 PM GMT</t>
+          <t>Aug 26, 2026 10:38 PM GMT</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T09:00:00Z</t>
+          <t>2026-08-26T20:58:00Z</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 12:26 PM GMT</t>
+          <t>Aug 26, 2026 9:26 PM GMT</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>206</v>
+        <v>28</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
@@ -5307,12 +5307,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T07:36:00Z</t>
+          <t>2026-08-26T20:55:00Z</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 8:26 AM GMT</t>
+          <t>Aug 26, 2026 8:56 PM GMT</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>2026-08-26T07:30:00Z</t>
+          <t>2026-08-26T12:59:00Z</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Aug 26, 2026 7:33 AM GMT</t>
+          <t>Aug 26, 2026 1:00 PM GMT</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
@@ -5367,12 +5367,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>2026-08-25T23:32:00Z</t>
+          <t>2026-08-26T12:41:00Z</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Aug 25, 2026 11:38 PM GMT</t>
+          <t>Aug 26, 2026 12:43 PM GMT</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>2026-08-25T18:06:00Z</t>
+          <t>2026-08-26T12:39:00Z</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Aug 25, 2026 6:11 PM GMT</t>
+          <t>Aug 26, 2026 12:40 PM GMT</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>2026-08-24T06:25:00Z</t>
+          <t>2026-08-26T12:28:00Z</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Aug 24, 2026 6:26 AM GMT</t>
+          <t>Aug 26, 2026 12:37 PM GMT</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T20:55:00Z</t>
+          <t>2026-08-26T09:00:00Z</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Aug 23, 2026 8:56 PM GMT</t>
+          <t>Aug 26, 2026 12:26 PM GMT</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>206</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
@@ -5487,12 +5487,12 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T10:59:00Z</t>
+          <t>2026-08-26T07:36:00Z</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Aug 23, 2026 2:03 PM GMT</t>
+          <t>Aug 26, 2026 8:26 AM GMT</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T07:44:00Z</t>
+          <t>2026-08-26T07:30:00Z</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Aug 23, 2026 8:26 AM GMT</t>
+          <t>Aug 26, 2026 7:33 AM GMT</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
@@ -5547,12 +5547,12 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23T07:34:00Z</t>
+          <t>2026-08-25T23:32:00Z</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Aug 23, 2026 7:40 AM GMT</t>
+          <t>Aug 25, 2026 11:38 PM GMT</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T14:58:00Z</t>
+          <t>2026-08-25T18:06:00Z</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 3:55 PM GMT</t>
+          <t>Aug 25, 2026 6:11 PM GMT</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T12:28:00Z</t>
+          <t>2026-08-24T06:25:00Z</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 2:55 PM GMT</t>
+          <t>Aug 24, 2026 6:26 AM GMT</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
@@ -5637,12 +5637,12 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T10:57:00Z</t>
+          <t>2026-08-23T20:55:00Z</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 12:26 PM GMT</t>
+          <t>Aug 23, 2026 8:56 PM GMT</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
@@ -5667,12 +5667,12 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T10:35:00Z</t>
+          <t>2026-08-23T10:59:00Z</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 10:55 AM GMT</t>
+          <t>Aug 23, 2026 2:03 PM GMT</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
@@ -5697,12 +5697,12 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T09:27:00Z</t>
+          <t>2026-08-23T07:44:00Z</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 9:56 AM GMT</t>
+          <t>Aug 23, 2026 8:26 AM GMT</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T07:51:00Z</t>
+          <t>2026-08-23T07:34:00Z</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 8:56 AM GMT</t>
+          <t>Aug 23, 2026 7:40 AM GMT</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T07:40:00Z</t>
+          <t>2026-08-22T14:58:00Z</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 7:47 AM GMT</t>
+          <t>Aug 22, 2026 3:55 PM GMT</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
@@ -5787,12 +5787,12 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T07:37:00Z</t>
+          <t>2026-08-22T12:28:00Z</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 7:38 AM GMT</t>
+          <t>Aug 22, 2026 2:55 PM GMT</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-22T07:33:00Z</t>
+          <t>2026-08-22T10:57:00Z</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Aug 22, 2026 7:34 AM GMT</t>
+          <t>Aug 22, 2026 12:26 PM GMT</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T17:52:00Z</t>
+          <t>2026-08-22T10:35:00Z</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 6:26 PM GMT</t>
+          <t>Aug 22, 2026 10:55 AM GMT</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
@@ -5877,12 +5877,12 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T13:59:00Z</t>
+          <t>2026-08-22T09:27:00Z</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 2:12 PM GMT</t>
+          <t>Aug 22, 2026 9:56 AM GMT</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
@@ -5907,12 +5907,12 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T13:27:00Z</t>
+          <t>2026-08-22T07:51:00Z</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 1:56 PM GMT</t>
+          <t>Aug 22, 2026 8:56 AM GMT</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T12:58:00Z</t>
+          <t>2026-08-22T07:40:00Z</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 1:25 PM GMT</t>
+          <t>Aug 22, 2026 7:47 AM GMT</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T09:58:00Z</t>
+          <t>2026-08-22T07:37:00Z</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 12:55 PM GMT</t>
+          <t>Aug 22, 2026 7:38 AM GMT</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
@@ -5997,12 +5997,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T09:27:00Z</t>
+          <t>2026-08-22T07:33:00Z</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 9:56 AM GMT</t>
+          <t>Aug 22, 2026 7:34 AM GMT</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
@@ -6027,12 +6027,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T08:58:00Z</t>
+          <t>2026-08-21T17:52:00Z</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 9:25 AM GMT</t>
+          <t>Aug 21, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
@@ -6057,12 +6057,12 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T07:57:00Z</t>
+          <t>2026-08-21T13:59:00Z</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 8:55 AM GMT</t>
+          <t>Aug 21, 2026 2:12 PM GMT</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>2026-08-21T07:31:00Z</t>
+          <t>2026-08-21T13:27:00Z</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Aug 21, 2026 7:55 AM GMT</t>
+          <t>Aug 21, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
@@ -6117,12 +6117,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T19:16:00Z</t>
+          <t>2026-08-21T12:58:00Z</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 7:21 PM GMT</t>
+          <t>Aug 21, 2026 1:25 PM GMT</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
@@ -6147,12 +6147,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T06:58:00Z</t>
+          <t>2026-08-21T09:58:00Z</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 7:47 AM GMT</t>
+          <t>Aug 21, 2026 12:55 PM GMT</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>49</v>
+        <v>177</v>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T05:58:00Z</t>
+          <t>2026-08-21T09:27:00Z</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 6:55 AM GMT</t>
+          <t>Aug 21, 2026 9:56 AM GMT</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
@@ -6207,12 +6207,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T04:27:00Z</t>
+          <t>2026-08-21T08:58:00Z</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 5:56 AM GMT</t>
+          <t>Aug 21, 2026 9:25 AM GMT</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
@@ -6237,12 +6237,12 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T03:27:00Z</t>
+          <t>2026-08-21T07:57:00Z</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 4:25 AM GMT</t>
+          <t>Aug 21, 2026 8:55 AM GMT</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:58:00Z</t>
+          <t>2026-08-21T07:31:00Z</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 3:25 AM GMT</t>
+          <t>Aug 21, 2026 7:55 AM GMT</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
@@ -6297,12 +6297,12 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:28:00Z</t>
+          <t>2026-08-20T19:16:00Z</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 2:56 AM GMT</t>
+          <t>Aug 20, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
@@ -6327,12 +6327,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:12:00Z</t>
+          <t>2026-08-20T06:58:00Z</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 2:25 AM GMT</t>
+          <t>Aug 20, 2026 7:47 AM GMT</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
@@ -6357,12 +6357,12 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:04:00Z</t>
+          <t>2026-08-20T05:58:00Z</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 2:07 AM GMT</t>
+          <t>Aug 20, 2026 6:55 AM GMT</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
@@ -6387,12 +6387,12 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T02:01:00Z</t>
+          <t>2026-08-20T04:27:00Z</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 2:02 AM GMT</t>
+          <t>Aug 20, 2026 5:56 AM GMT</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:52:00Z</t>
+          <t>2026-08-20T03:27:00Z</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:56 AM GMT</t>
+          <t>Aug 20, 2026 4:25 AM GMT</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:48:00Z</t>
+          <t>2026-08-20T02:58:00Z</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:50 AM GMT</t>
+          <t>Aug 20, 2026 3:25 AM GMT</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
@@ -6477,12 +6477,12 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:44:00Z</t>
+          <t>2026-08-20T02:28:00Z</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:46 AM GMT</t>
+          <t>Aug 20, 2026 2:56 AM GMT</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
@@ -6507,12 +6507,12 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:39:00Z</t>
+          <t>2026-08-20T02:12:00Z</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:42 AM GMT</t>
+          <t>Aug 20, 2026 2:25 AM GMT</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
@@ -6537,12 +6537,12 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T01:12:00Z</t>
+          <t>2026-08-20T02:04:00Z</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:36 AM GMT</t>
+          <t>Aug 20, 2026 2:07 AM GMT</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
@@ -6567,12 +6567,12 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>2026-08-20T00:43:00Z</t>
+          <t>2026-08-20T02:01:00Z</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Aug 20, 2026 1:10 AM GMT</t>
+          <t>Aug 20, 2026 2:02 AM GMT</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
@@ -6597,12 +6597,12 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>2026-08-15T13:05:00Z</t>
+          <t>2026-08-20T01:52:00Z</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>Aug 15, 2026 1:07 PM GMT</t>
+          <t>Aug 20, 2026 1:56 AM GMT</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -6611,7 +6611,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
@@ -6627,12 +6627,12 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>2026-08-15T06:35:00Z</t>
+          <t>2026-08-20T01:48:00Z</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Aug 15, 2026 6:36 AM GMT</t>
+          <t>Aug 20, 2026 1:50 AM GMT</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14T15:35:00Z</t>
+          <t>2026-08-20T01:44:00Z</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>Aug 14, 2026 3:36 PM GMT</t>
+          <t>Aug 20, 2026 1:46 AM GMT</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14T13:05:00Z</t>
+          <t>2026-08-20T01:39:00Z</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>Aug 14, 2026 1:06 PM GMT</t>
+          <t>Aug 20, 2026 1:42 AM GMT</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
@@ -6717,12 +6717,12 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14T07:35:00Z</t>
+          <t>2026-08-20T01:12:00Z</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>Aug 14, 2026 7:36 AM GMT</t>
+          <t>Aug 20, 2026 1:36 AM GMT</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>2026-08-14T05:35:00Z</t>
+          <t>2026-08-20T00:43:00Z</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Aug 14, 2026 5:36 AM GMT</t>
+          <t>Aug 20, 2026 1:10 AM GMT</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
@@ -6777,12 +6777,12 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13T18:05:00Z</t>
+          <t>2026-08-15T13:05:00Z</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>Aug 13, 2026 6:06 PM GMT</t>
+          <t>Aug 15, 2026 1:07 PM GMT</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
@@ -6807,12 +6807,12 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13T14:05:00Z</t>
+          <t>2026-08-15T06:35:00Z</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Aug 13, 2026 2:06 PM GMT</t>
+          <t>Aug 15, 2026 6:36 AM GMT</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13T08:35:00Z</t>
+          <t>2026-08-14T15:35:00Z</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>Aug 13, 2026 8:36 AM GMT</t>
+          <t>Aug 14, 2026 3:36 PM GMT</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>2026-08-12T16:09:00Z</t>
+          <t>2026-08-14T13:05:00Z</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Aug 12, 2026 4:38 PM GMT</t>
+          <t>Aug 14, 2026 1:06 PM GMT</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10T12:43:00Z</t>
+          <t>2026-08-14T07:35:00Z</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Aug 10, 2026 12:44 PM GMT</t>
+          <t>Aug 14, 2026 7:36 AM GMT</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10T10:42:00Z</t>
+          <t>2026-08-14T05:35:00Z</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Aug 10, 2026 12:40 PM GMT</t>
+          <t>Aug 14, 2026 5:36 AM GMT</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10T10:12:00Z</t>
+          <t>2026-08-13T18:05:00Z</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>Aug 10, 2026 10:40 AM GMT</t>
+          <t>Aug 13, 2026 6:06 PM GMT</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10T07:41:00Z</t>
+          <t>2026-08-13T14:05:00Z</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Aug 10, 2026 10:10 AM GMT</t>
+          <t>Aug 13, 2026 2:06 PM GMT</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
@@ -7001,7 +7001,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
@@ -7017,12 +7017,12 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T20:38:00Z</t>
+          <t>2026-08-13T08:35:00Z</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 10:06 PM GMT</t>
+          <t>Aug 13, 2026 8:36 AM GMT</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
@@ -7047,12 +7047,12 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T20:08:00Z</t>
+          <t>2026-08-12T16:09:00Z</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 8:36 PM GMT</t>
+          <t>Aug 12, 2026 4:38 PM GMT</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
@@ -7077,12 +7077,12 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T19:12:00Z</t>
+          <t>2026-08-10T12:43:00Z</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 8:06 PM GMT</t>
+          <t>Aug 10, 2026 12:44 PM GMT</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
@@ -7091,7 +7091,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
@@ -7107,12 +7107,12 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T16:12:00Z</t>
+          <t>2026-08-10T10:42:00Z</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 7:10 PM GMT</t>
+          <t>Aug 10, 2026 12:40 PM GMT</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
@@ -7137,12 +7137,12 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T13:12:00Z</t>
+          <t>2026-08-10T10:12:00Z</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 4:10 PM GMT</t>
+          <t>Aug 10, 2026 10:40 AM GMT</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>178</v>
+        <v>28</v>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
@@ -7167,12 +7167,12 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09T11:32:00Z</t>
+          <t>2026-08-10T07:41:00Z</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Aug 09, 2026 1:11 PM GMT</t>
+          <t>Aug 10, 2026 10:10 AM GMT</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T06:57:00Z</t>
+          <t>2026-08-09T20:38:00Z</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 7:31 AM GMT</t>
+          <t>Aug 09, 2026 10:06 PM GMT</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
@@ -7227,12 +7227,12 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T03:38:00Z</t>
+          <t>2026-08-09T20:08:00Z</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 5:08 AM GMT</t>
+          <t>Aug 09, 2026 8:36 PM GMT</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T03:12:00Z</t>
+          <t>2026-08-09T19:12:00Z</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 3:36 AM GMT</t>
+          <t>Aug 09, 2026 8:06 PM GMT</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
@@ -7287,12 +7287,12 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T02:38:00Z</t>
+          <t>2026-08-09T16:12:00Z</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 3:10 AM GMT</t>
+          <t>Aug 09, 2026 7:10 PM GMT</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>32</v>
+        <v>178</v>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
@@ -7317,12 +7317,12 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T01:54:00Z</t>
+          <t>2026-08-09T13:12:00Z</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 2:36 AM GMT</t>
+          <t>Aug 09, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>42</v>
+        <v>178</v>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
@@ -7347,12 +7347,12 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>2026-08-07T01:13:00Z</t>
+          <t>2026-08-09T11:32:00Z</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>Aug 07, 2026 1:51 AM GMT</t>
+          <t>Aug 09, 2026 1:11 PM GMT</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>2026-08-01T12:15:00Z</t>
+          <t>2026-08-07T06:57:00Z</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>Aug 01, 2026 12:16 PM GMT</t>
+          <t>Aug 07, 2026 7:31 AM GMT</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
@@ -7402,180 +7402,180 @@
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T04:56:00Z</t>
+          <t>2026-08-07T03:38:00Z</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 7:22 AM GMT</t>
+          <t>Aug 07, 2026 5:08 AM GMT</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T04:56:00Z</t>
+          <t>2026-08-07T03:12:00Z</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 7:22 AM GMT</t>
+          <t>Aug 07, 2026 3:36 AM GMT</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>146</v>
+        <v>24</v>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T02:27:00Z</t>
+          <t>2026-08-07T02:38:00Z</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 5:59 AM GMT</t>
+          <t>Aug 07, 2026 3:10 AM GMT</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>212</v>
+        <v>32</v>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T02:27:00Z</t>
+          <t>2026-08-07T01:54:00Z</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 5:59 AM GMT</t>
+          <t>Aug 07, 2026 2:36 AM GMT</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>212</v>
+        <v>42</v>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T01:35:00Z</t>
+          <t>2026-08-07T01:13:00Z</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 2:45 AM GMT</t>
+          <t>Aug 07, 2026 1:51 AM GMT</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>2026-07-30T01:35:00Z</t>
+          <t>2026-08-01T12:15:00Z</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>Jul 30, 2026 2:45 AM GMT</t>
+          <t>Aug 01, 2026 12:16 PM GMT</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
@@ -7587,21 +7587,21 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T21:45:00Z</t>
+          <t>2026-07-30T04:56:00Z</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 11:02 PM GMT</t>
+          <t>Jul 30, 2026 7:22 AM GMT</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
@@ -7617,21 +7617,21 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T21:45:00Z</t>
+          <t>2026-07-30T04:56:00Z</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 11:02 PM GMT</t>
+          <t>Jul 30, 2026 7:22 AM GMT</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
@@ -7647,21 +7647,21 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-07-30T02:27:00Z</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Jul 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>53</v>
+        <v>212</v>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
@@ -7677,21 +7677,21 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-07-30T02:27:00Z</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Jul 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>53</v>
+        <v>212</v>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
@@ -7707,21 +7707,21 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-07-30T01:35:00Z</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Jul 30, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
@@ -7737,21 +7737,21 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29T14:55:00Z</t>
+          <t>2026-07-30T01:35:00Z</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>Jul 29, 2026 3:48 PM GMT</t>
+          <t>Jul 30, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
@@ -7762,26 +7762,26 @@
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:09:00Z</t>
+          <t>2026-07-29T21:45:00Z</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:10 AM GMT</t>
+          <t>Jul 29, 2026 11:02 PM GMT</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
@@ -7792,26 +7792,26 @@
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:02:00Z</t>
+          <t>2026-07-29T21:45:00Z</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:09 AM GMT</t>
+          <t>Jul 29, 2026 11:02 PM GMT</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
@@ -7822,26 +7822,26 @@
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:10 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
@@ -7852,26 +7852,26 @@
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:10 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
@@ -7882,26 +7882,26 @@
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T11:00:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 11:06 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
@@ -7912,26 +7912,26 @@
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24T02:45:00Z</t>
+          <t>2026-07-29T14:55:00Z</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>Jul 24, 2026 2:47 AM GMT</t>
+          <t>Jul 29, 2026 3:48 PM GMT</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>2026-07-20T08:26:00Z</t>
+          <t>2026-07-24T11:09:00Z</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>Jul 20, 2026 8:28 AM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>2026-07-08T16:34:00Z</t>
+          <t>2026-07-24T11:02:00Z</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>Jul 08, 2026 4:38 PM GMT</t>
+          <t>Jul 24, 2026 11:09 AM GMT</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
@@ -8007,21 +8007,21 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>2026-07-07T22:42:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>Jul 07, 2026 10:49 PM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
@@ -8037,21 +8037,21 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>2026-07-06T16:05:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>Jul 06, 2026 4:11 PM GMT</t>
+          <t>Jul 24, 2026 11:10 AM GMT</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
@@ -8062,180 +8062,180 @@
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-07-24T11:00:00Z</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Jul 24, 2026 11:06 AM GMT</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>2026-06-27T00:18:00Z</t>
+          <t>2026-07-24T02:45:00Z</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>Jun 27, 2026 12:40 AM GMT</t>
+          <t>Jul 24, 2026 2:47 AM GMT</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E202" s="5" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-07-20T08:26:00Z</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Jul 20, 2026 8:28 AM GMT</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>192</v>
+        <v>2</v>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:24:00Z</t>
+          <t>2026-07-08T16:34:00Z</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:36 PM GMT</t>
+          <t>Jul 08, 2026 4:38 PM GMT</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>192</v>
+        <v>4</v>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-07-07T22:42:00Z</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jul 07, 2026 10:49 PM GMT</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E205" s="5" t="n">
-        <v>164</v>
+        <v>7</v>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T18:23:00Z</t>
+          <t>2026-07-06T16:05:00Z</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 9:07 PM GMT</t>
+          <t>Jul 06, 2026 4:11 PM GMT</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
     </row>
@@ -8247,21 +8247,21 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E207" s="5" t="n">
-        <v>252</v>
+        <v>22</v>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
@@ -8277,21 +8277,21 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T04:06:00Z</t>
+          <t>2026-06-27T00:18:00Z</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 8:18 AM GMT</t>
+          <t>Jun 27, 2026 12:40 AM GMT</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E208" s="5" t="n">
-        <v>252</v>
+        <v>22</v>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
@@ -8307,21 +8307,21 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
@@ -8337,21 +8337,21 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>2026-06-25T00:26:00Z</t>
+          <t>2026-06-25T18:24:00Z</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:08 AM GMT</t>
+          <t>Jun 25, 2026 9:36 PM GMT</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E210" s="5" t="n">
-        <v>42</v>
+        <v>192</v>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
@@ -8367,21 +8367,21 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
@@ -8397,21 +8397,21 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T23:19:00Z</t>
+          <t>2026-06-25T18:23:00Z</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 12:57 AM GMT</t>
+          <t>Jun 25, 2026 9:07 PM GMT</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E213" s="5" t="n">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
@@ -8457,21 +8457,21 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:57:00Z</t>
+          <t>2026-06-25T04:06:00Z</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:20 PM GMT</t>
+          <t>Jun 25, 2026 8:18 AM GMT</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
@@ -8487,21 +8487,21 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E215" s="5" t="n">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>2026-06-24T13:51:00Z</t>
+          <t>2026-06-25T00:26:00Z</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Jun 24, 2026 3:47 PM GMT</t>
+          <t>Jun 25, 2026 1:08 AM GMT</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E216" s="5" t="n">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
@@ -8547,21 +8547,21 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>2026-06-23T17:55:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Jun 23, 2026 6:45 PM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E217" s="5" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
@@ -8577,21 +8577,21 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T21:08:00Z</t>
+          <t>2026-06-24T23:19:00Z</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>Jun 22, 2026 9:40 PM GMT</t>
+          <t>Jun 25, 2026 12:57 AM GMT</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E218" s="5" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
@@ -8602,26 +8602,26 @@
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E219" s="5" t="n">
-        <v>20253</v>
+        <v>83</v>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
@@ -8632,26 +8632,26 @@
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>2026-06-11T11:50:00Z</t>
+          <t>2026-06-24T13:57:00Z</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Jun 25, 2026 1:23 PM GMT</t>
+          <t>Jun 24, 2026 3:20 PM GMT</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E220" s="5" t="n">
-        <v>20253</v>
+        <v>83</v>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
@@ -8662,26 +8662,26 @@
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T21:09:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>Jun 09, 2026 9:11 PM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E221" s="5" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
@@ -8692,26 +8692,26 @@
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-06-24T13:51:00Z</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jun 24, 2026 3:47 PM GMT</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E222" s="5" t="n">
-        <v>1789</v>
+        <v>116</v>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
@@ -8722,26 +8722,26 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:00Z</t>
+          <t>2026-06-23T17:55:00Z</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>Jun 10, 2026 10:44 PM GMT</t>
+          <t>Jun 23, 2026 6:45 PM GMT</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E223" s="5" t="n">
-        <v>1789</v>
+        <v>50</v>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
@@ -8752,26 +8752,26 @@
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>2026-06-08T19:11:00Z</t>
+          <t>2026-06-22T21:08:00Z</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>Jun 08, 2026 7:13 PM GMT</t>
+          <t>Jun 22, 2026 9:40 PM GMT</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E224" s="5" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
@@ -8782,17 +8782,17 @@
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="E225" s="5" t="n">
-        <v>903</v>
+        <v>20253</v>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
@@ -8812,17 +8812,17 @@
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04T21:22:00Z</t>
+          <t>2026-06-11T11:50:00Z</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>Jun 05, 2026 12:25 PM GMT</t>
+          <t>Jun 25, 2026 1:23 PM GMT</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="E226" s="5" t="n">
-        <v>903</v>
+        <v>20253</v>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
@@ -8842,120 +8842,120 @@
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-09T21:09:00Z</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 09, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E227" s="5" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T03:57:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 5:43 AM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E228" s="5" t="n">
-        <v>106</v>
+        <v>1789</v>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-09T16:55:00Z</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 10, 2026 10:44 PM GMT</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">
-        <v>57</v>
+        <v>1789</v>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T02:06:00Z</t>
+          <t>2026-06-08T19:11:00Z</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 3:03 AM GMT</t>
+          <t>Jun 08, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E230" s="5" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -8967,25 +8967,25 @@
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E231" s="5" t="n">
-        <v>33</v>
+        <v>903</v>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -8997,25 +8997,25 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>2026-05-28T01:07:00Z</t>
+          <t>2026-06-04T21:22:00Z</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:40 AM GMT</t>
+          <t>Jun 05, 2026 12:25 PM GMT</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E232" s="5" t="n">
-        <v>33</v>
+        <v>903</v>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
     </row>
@@ -9027,21 +9027,21 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E233" s="5" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
@@ -9057,21 +9057,21 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T23:50:00Z</t>
+          <t>2026-05-28T03:57:00Z</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>May 28, 2026 1:06 AM GMT</t>
+          <t>May 28, 2026 5:43 AM GMT</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E234" s="5" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
@@ -9087,21 +9087,21 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
@@ -9117,21 +9117,21 @@
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-28T02:06:00Z</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 3:03 AM GMT</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E236" s="5" t="n">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
@@ -9147,21 +9147,21 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E237" s="5" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
@@ -9177,21 +9177,21 @@
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>2026-05-27T15:12:00Z</t>
+          <t>2026-05-28T01:07:00Z</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>May 27, 2026 5:14 PM GMT</t>
+          <t>May 28, 2026 1:40 AM GMT</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E238" s="5" t="n">
-        <v>122</v>
+        <v>33</v>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
@@ -9202,26 +9202,26 @@
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E239" s="5" t="n">
-        <v>17374</v>
+        <v>76</v>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
@@ -9232,26 +9232,26 @@
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T12:22:00Z</t>
+          <t>2026-05-27T23:50:00Z</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>May 26, 2026 1:56 PM GMT</t>
+          <t>May 28, 2026 1:06 AM GMT</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E240" s="5" t="n">
-        <v>17374</v>
+        <v>76</v>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
@@ -9262,26 +9262,26 @@
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E241" s="5" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
@@ -9292,26 +9292,26 @@
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T14:30:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>May 13, 2026 2:35 PM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E242" s="5" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
@@ -9327,12 +9327,12 @@
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="E243" s="5" t="n">
-        <v>673</v>
+        <v>122</v>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>2026-05-11T14:06:00Z</t>
+          <t>2026-05-27T15:12:00Z</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>May 12, 2026 1:19 AM GMT</t>
+          <t>May 27, 2026 5:14 PM GMT</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="E244" s="5" t="n">
-        <v>673</v>
+        <v>122</v>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
@@ -9382,26 +9382,26 @@
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-10T21:09:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>May 10, 2026 9:11 PM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E245" s="5" t="n">
-        <v>2</v>
+        <v>17374</v>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
@@ -9412,26 +9412,26 @@
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>2026-05-09T19:11:00Z</t>
+          <t>2026-05-14T12:22:00Z</t>
         </is>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>May 09, 2026 7:13 PM GMT</t>
+          <t>May 26, 2026 1:56 PM GMT</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E246" s="5" t="n">
-        <v>2</v>
+        <v>17374</v>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
@@ -9442,17 +9442,17 @@
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="E247" s="5" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
@@ -9472,17 +9472,17 @@
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08T09:39:00Z</t>
+          <t>2026-05-13T14:30:00Z</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 11:51 AM GMT</t>
+          <t>May 13, 2026 2:35 PM GMT</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="E248" s="5" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
@@ -9502,26 +9502,26 @@
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E249" s="5" t="n">
-        <v>1395</v>
+        <v>673</v>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
@@ -9532,26 +9532,26 @@
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T19:05:00Z</t>
+          <t>2026-05-11T14:06:00Z</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>May 08, 2026 6:20 PM GMT</t>
+          <t>May 12, 2026 1:19 AM GMT</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E250" s="5" t="n">
-        <v>1395</v>
+        <v>673</v>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
@@ -9562,26 +9562,26 @@
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-10T21:09:00Z</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 10, 2026 9:11 PM GMT</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E251" s="5" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
@@ -9592,26 +9592,26 @@
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>2026-05-04T17:22:00Z</t>
+          <t>2026-05-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 6:34 PM GMT</t>
+          <t>May 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E252" s="5" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
@@ -9627,12 +9627,12 @@
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
@@ -9641,11 +9641,11 @@
         </is>
       </c>
       <c r="E253" s="5" t="n">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T03:17:00Z</t>
+          <t>2026-05-08T09:39:00Z</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 5:59 AM GMT</t>
+          <t>May 08, 2026 11:51 AM GMT</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
@@ -9671,71 +9671,71 @@
         </is>
       </c>
       <c r="E254" s="5" t="n">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E255" s="5" t="n">
-        <v>78</v>
+        <v>1395</v>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:52:00Z</t>
+          <t>2026-05-07T19:05:00Z</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 2:10 AM GMT</t>
+          <t>May 08, 2026 6:20 PM GMT</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E256" s="5" t="n">
-        <v>78</v>
+        <v>1395</v>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -9747,25 +9747,25 @@
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E257" s="5" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -9777,25 +9777,25 @@
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30T00:20:00Z</t>
+          <t>2026-05-04T17:22:00Z</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 1:48 AM GMT</t>
+          <t>May 04, 2026 6:34 PM GMT</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E258" s="5" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
     </row>
@@ -9807,21 +9807,21 @@
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E259" s="5" t="n">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
@@ -9837,21 +9837,21 @@
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T22:53:00Z</t>
+          <t>2026-04-30T03:17:00Z</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>Apr 30, 2026 12:06 AM GMT</t>
+          <t>Apr 30, 2026 5:59 AM GMT</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E260" s="5" t="n">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
@@ -9867,21 +9867,21 @@
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E261" s="5" t="n">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-30T00:52:00Z</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 2:10 AM GMT</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E262" s="5" t="n">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
@@ -9927,21 +9927,21 @@
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E263" s="5" t="n">
-        <v>273</v>
+        <v>88</v>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
@@ -9957,21 +9957,21 @@
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29T15:45:00Z</t>
+          <t>2026-04-30T00:20:00Z</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>Apr 29, 2026 8:18 PM GMT</t>
+          <t>Apr 30, 2026 1:48 AM GMT</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E264" s="5" t="n">
-        <v>273</v>
+        <v>88</v>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="E265" s="5" t="n">
-        <v>242</v>
+        <v>73</v>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
@@ -10017,12 +10017,12 @@
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>2026-04-24T18:12:00Z</t>
+          <t>2026-04-29T22:53:00Z</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 10:14 PM GMT</t>
+          <t>Apr 30, 2026 12:06 AM GMT</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="E266" s="5" t="n">
-        <v>242</v>
+        <v>73</v>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
@@ -10042,26 +10042,26 @@
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E267" s="5" t="n">
-        <v>17272</v>
+        <v>273</v>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
@@ -10072,26 +10072,26 @@
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>2026-04-22T16:29:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>May 04, 2026 4:21 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E268" s="5" t="n">
-        <v>17272</v>
+        <v>273</v>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
@@ -10107,21 +10107,21 @@
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E269" s="5" t="n">
-        <v>1187</v>
+        <v>273</v>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
@@ -10137,21 +10137,21 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>2026-04-21T20:43:00Z</t>
+          <t>2026-04-29T15:45:00Z</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>Apr 22, 2026 4:30 PM GMT</t>
+          <t>Apr 29, 2026 8:18 PM GMT</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E270" s="5" t="n">
-        <v>1187</v>
+        <v>273</v>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
@@ -10167,21 +10167,21 @@
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E271" s="5" t="n">
-        <v>4284</v>
+        <v>242</v>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
@@ -10197,21 +10197,21 @@
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>2026-04-17T22:57:00Z</t>
+          <t>2026-04-24T18:12:00Z</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>Apr 20, 2026 10:21 PM GMT</t>
+          <t>Apr 24, 2026 10:14 PM GMT</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E272" s="5" t="n">
-        <v>4284</v>
+        <v>242</v>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
@@ -10222,26 +10222,26 @@
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:28:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:38 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EU</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E273" s="5" t="n">
-        <v>10</v>
+        <v>17272</v>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
@@ -10252,26 +10252,26 @@
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>2026-04-16T14:26:00Z</t>
+          <t>2026-04-22T16:29:00Z</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 2:36 PM GMT</t>
+          <t>May 04, 2026 4:21 PM GMT</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EU</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E274" s="5" t="n">
-        <v>10</v>
+        <v>17272</v>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
@@ -10287,21 +10287,21 @@
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>2026-04-10T20:56:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>Apr 10, 2026 10:32 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E275" s="5" t="n">
-        <v>96</v>
+        <v>1187</v>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
@@ -10317,21 +10317,21 @@
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T21:04:00Z</t>
+          <t>2026-04-21T20:43:00Z</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:34 PM GMT</t>
+          <t>Apr 22, 2026 4:30 PM GMT</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E276" s="5" t="n">
-        <v>30</v>
+        <v>1187</v>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
@@ -10342,26 +10342,26 @@
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T19:11:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 7:13 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E277" s="5" t="n">
-        <v>2</v>
+        <v>4284</v>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
@@ -10377,21 +10377,21 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>2026-04-09T18:04:00Z</t>
+          <t>2026-04-17T22:57:00Z</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>Apr 09, 2026 9:35 PM GMT</t>
+          <t>Apr 20, 2026 10:21 PM GMT</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E278" s="5" t="n">
-        <v>211</v>
+        <v>4284</v>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
@@ -10407,21 +10407,21 @@
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:10:00Z</t>
+          <t>2026-04-16T14:28:00Z</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 16, 2026 2:38 PM GMT</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EU</t>
         </is>
       </c>
       <c r="E279" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
@@ -10437,21 +10437,21 @@
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:09:00Z</t>
+          <t>2026-04-16T14:26:00Z</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>Apr 08, 2026 4:12 AM GMT</t>
+          <t>Apr 16, 2026 2:36 PM GMT</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - EU</t>
         </is>
       </c>
       <c r="E280" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
@@ -10462,26 +10462,26 @@
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>Service Degradation</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>2026-04-07T18:03:00Z</t>
+          <t>2026-04-10T20:56:00Z</t>
         </is>
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>Apr 07, 2026 7:21 PM GMT</t>
+          <t>Apr 10, 2026 10:32 PM GMT</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E281" s="5" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
@@ -10497,21 +10497,21 @@
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-09T21:04:00Z</t>
         </is>
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 09, 2026 9:34 PM GMT</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E282" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
@@ -10522,26 +10522,26 @@
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02T00:27:00Z</t>
+          <t>2026-04-09T19:11:00Z</t>
         </is>
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>Apr 02, 2026 1:17 AM GMT</t>
+          <t>Apr 09, 2026 7:13 PM GMT</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E283" s="5" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
@@ -10557,115 +10557,115 @@
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-09T18:04:00Z</t>
         </is>
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 09, 2026 9:35 PM GMT</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E284" s="5" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>2026-03-26T03:52:00Z</t>
+          <t>2026-04-08T04:10:00Z</t>
         </is>
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 7:15 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E285" s="5" t="n">
-        <v>203</v>
+        <v>2</v>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-08T04:09:00Z</t>
         </is>
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 08, 2026 4:12 AM GMT</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E286" s="5" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Service Degradation</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T23:07:00Z</t>
+          <t>2026-04-07T18:03:00Z</t>
         </is>
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 1:37 AM GMT</t>
+          <t>Apr 07, 2026 7:21 PM GMT</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E287" s="5" t="n">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -10677,25 +10677,25 @@
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E288" s="5" t="n">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -10707,25 +10707,25 @@
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-04-02T00:27:00Z</t>
         </is>
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Apr 02, 2026 1:17 AM GMT</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E289" s="5" t="n">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
     </row>
@@ -10737,21 +10737,21 @@
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E290" s="5" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
@@ -10767,21 +10767,21 @@
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>2026-03-25T14:07:00Z</t>
+          <t>2026-03-26T03:52:00Z</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 4:10 PM GMT</t>
+          <t>Mar 26, 2026 7:15 AM GMT</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E291" s="5" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
@@ -10797,21 +10797,21 @@
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T21:04:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 10:34 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E292" s="5" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
@@ -10827,21 +10827,21 @@
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T17:44:00Z</t>
+          <t>2026-03-25T23:07:00Z</t>
         </is>
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>Mar 20, 2026 6:26 PM GMT</t>
+          <t>Mar 26, 2026 1:37 AM GMT</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E293" s="5" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
@@ -10857,21 +10857,21 @@
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E294" s="5" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
@@ -10887,21 +10887,21 @@
       </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T19:11:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 8:50 PM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E295" s="5" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
@@ -10912,26 +10912,26 @@
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
         <is>
-          <t>2026-03-18T00:43:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 12:46 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E296" s="5" t="n">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
@@ -10947,21 +10947,21 @@
       </c>
       <c r="B297" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-25T14:07:00Z</t>
         </is>
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 25, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E297" s="5" t="n">
-        <v>198</v>
+        <v>123</v>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
@@ -10977,21 +10977,21 @@
       </c>
       <c r="B298" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T22:16:00Z</t>
+          <t>2026-03-20T21:04:00Z</t>
         </is>
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>Mar 18, 2026 1:34 AM GMT</t>
+          <t>Mar 20, 2026 10:34 PM GMT</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E298" s="5" t="n">
-        <v>198</v>
+        <v>90</v>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
@@ -11002,17 +11002,17 @@
     <row r="299">
       <c r="A299" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17T19:46:00Z</t>
+          <t>2026-03-20T17:44:00Z</t>
         </is>
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>Mar 17, 2026 7:48 PM GMT</t>
+          <t>Mar 20, 2026 6:26 PM GMT</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E299" s="5" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
@@ -11032,26 +11032,26 @@
     <row r="300">
       <c r="A300" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13T00:37:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>Mar 13, 2026 12:41 AM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E300" s="5" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
@@ -11062,26 +11062,26 @@
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
         <is>
-          <t>2026-03-11T23:50:00Z</t>
+          <t>2026-03-18T19:11:00Z</t>
         </is>
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>Mar 11, 2026 11:54 PM GMT</t>
+          <t>Mar 18, 2026 8:50 PM GMT</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E301" s="5" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
@@ -11092,26 +11092,26 @@
     <row r="302">
       <c r="A302" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-18T00:43:00Z</t>
         </is>
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 18, 2026 12:46 AM GMT</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E302" s="5" t="n">
-        <v>164</v>
+        <v>3</v>
       </c>
       <c r="F302" s="5" t="inlineStr">
         <is>
@@ -11127,21 +11127,21 @@
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T05:01:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 7:45 AM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E303" s="5" t="n">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
@@ -11157,21 +11157,21 @@
       </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-17T22:16:00Z</t>
         </is>
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 18, 2026 1:34 AM GMT</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E304" s="5" t="n">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
@@ -11182,26 +11182,26 @@
     <row r="305">
       <c r="A305" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>2026-03-05T01:20:00Z</t>
+          <t>2026-03-17T19:46:00Z</t>
         </is>
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 2:45 AM GMT</t>
+          <t>Mar 17, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E305" s="5" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
@@ -11212,26 +11212,26 @@
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-13T00:37:00Z</t>
         </is>
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 13, 2026 12:41 AM GMT</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E306" s="5" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
@@ -11242,26 +11242,26 @@
     <row r="307">
       <c r="A307" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T23:49:00Z</t>
+          <t>2026-03-11T23:50:00Z</t>
         </is>
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>Mar 05, 2026 1:16 AM GMT</t>
+          <t>Mar 11, 2026 11:54 PM GMT</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E307" s="5" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
@@ -11277,21 +11277,21 @@
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E308" s="5" t="n">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="F308" s="5" t="inlineStr">
         <is>
@@ -11307,21 +11307,21 @@
       </c>
       <c r="B309" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T05:01:00Z</t>
         </is>
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 7:45 AM GMT</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E309" s="5" t="n">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="F309" s="5" t="inlineStr">
         <is>
@@ -11337,21 +11337,21 @@
       </c>
       <c r="B310" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E310" s="5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
@@ -11367,21 +11367,21 @@
       </c>
       <c r="B311" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04T14:35:00Z</t>
+          <t>2026-03-05T01:20:00Z</t>
         </is>
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>Mar 04, 2026 4:10 PM GMT</t>
+          <t>Mar 05, 2026 2:45 AM GMT</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E311" s="5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F311" s="5" t="inlineStr">
         <is>
@@ -11392,26 +11392,26 @@
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B312" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 5:02 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E312" s="5" t="n">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
@@ -11422,26 +11422,26 @@
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B313" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T16:51:00Z</t>
+          <t>2026-03-04T23:49:00Z</t>
         </is>
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 4:56 PM GMT</t>
+          <t>Mar 05, 2026 1:16 AM GMT</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E313" s="5" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
@@ -11452,26 +11452,26 @@
     <row r="314">
       <c r="A314" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B314" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:44:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 3:15 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E314" s="5" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
@@ -11482,26 +11482,26 @@
     <row r="315">
       <c r="A315" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B315" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:42:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:44 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E315" s="5" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
@@ -11512,26 +11512,26 @@
     <row r="316">
       <c r="A316" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B316" s="5" t="inlineStr">
         <is>
-          <t>2026-03-02T14:41:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>Mar 02, 2026 2:42 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E316" s="5" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
@@ -11542,17 +11542,17 @@
     <row r="317">
       <c r="A317" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B317" s="5" t="inlineStr">
         <is>
-          <t>2026-02-26T16:39:00Z</t>
+          <t>2026-03-04T14:35:00Z</t>
         </is>
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>Feb 26, 2026 4:44 PM GMT</t>
+          <t>Mar 04, 2026 4:10 PM GMT</t>
         </is>
       </c>
       <c r="D317" s="5" t="inlineStr">
@@ -11561,131 +11561,131 @@
         </is>
       </c>
       <c r="E317" s="5" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="F317" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B318" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 02, 2026 5:02 PM GMT</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - APAC</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E318" s="5" t="n">
-        <v>207</v>
+        <v>11</v>
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B319" s="5" t="inlineStr">
         <is>
-          <t>2026-02-20T15:28:00Z</t>
+          <t>2026-03-02T16:51:00Z</t>
         </is>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>Feb 20, 2026 6:55 PM GMT</t>
+          <t>Mar 02, 2026 4:56 PM GMT</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - APAC</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E319" s="5" t="n">
-        <v>207</v>
+        <v>5</v>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B320" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-02T14:44:00Z</t>
         </is>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 02, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E320" s="5" t="n">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="F320" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B321" s="5" t="inlineStr">
         <is>
-          <t>2026-02-18T19:36:00Z</t>
+          <t>2026-03-02T14:42:00Z</t>
         </is>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>Feb 18, 2026 10:15 PM GMT</t>
+          <t>Mar 02, 2026 2:44 PM GMT</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E321" s="5" t="n">
-        <v>159</v>
+        <v>2</v>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -11697,25 +11697,25 @@
       </c>
       <c r="B322" s="5" t="inlineStr">
         <is>
-          <t>2026-02-15T19:46:00Z</t>
+          <t>2026-03-02T14:41:00Z</t>
         </is>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>Feb 15, 2026 7:48 PM GMT</t>
+          <t>Mar 02, 2026 2:42 PM GMT</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E322" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
     </row>
@@ -11727,21 +11727,21 @@
       </c>
       <c r="B323" s="5" t="inlineStr">
         <is>
-          <t>2026-02-14T22:07:00Z</t>
+          <t>2026-02-26T16:39:00Z</t>
         </is>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>Feb 14, 2026 10:09 PM GMT</t>
+          <t>Feb 26, 2026 4:44 PM GMT</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E323" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
@@ -11757,21 +11757,21 @@
       </c>
       <c r="B324" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - SGP</t>
+          <t>Fortify on Demand Tenant Portal - APAC</t>
         </is>
       </c>
       <c r="E324" s="5" t="n">
-        <v>282</v>
+        <v>207</v>
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
@@ -11787,21 +11787,21 @@
       </c>
       <c r="B325" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T16:28:00Z</t>
+          <t>2026-02-20T15:28:00Z</t>
         </is>
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 9:10 PM GMT</t>
+          <t>Feb 20, 2026 6:55 PM GMT</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - SGP</t>
+          <t>Fortify on Demand API - APAC</t>
         </is>
       </c>
       <c r="E325" s="5" t="n">
-        <v>282</v>
+        <v>207</v>
       </c>
       <c r="F325" s="5" t="inlineStr">
         <is>
@@ -11817,12 +11817,12 @@
       </c>
       <c r="B326" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D326" s="5" t="inlineStr">
@@ -11831,7 +11831,7 @@
         </is>
       </c>
       <c r="E326" s="5" t="n">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="F326" s="5" t="inlineStr">
         <is>
@@ -11847,12 +11847,12 @@
       </c>
       <c r="B327" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T04:56:00Z</t>
+          <t>2026-02-18T19:36:00Z</t>
         </is>
       </c>
       <c r="C327" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 7:03 AM GMT</t>
+          <t>Feb 18, 2026 10:15 PM GMT</t>
         </is>
       </c>
       <c r="D327" s="5" t="inlineStr">
@@ -11861,7 +11861,7 @@
         </is>
       </c>
       <c r="E327" s="5" t="n">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="F327" s="5" t="inlineStr">
         <is>
@@ -11872,26 +11872,26 @@
     <row r="328">
       <c r="A328" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B328" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-15T19:46:00Z</t>
         </is>
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 15, 2026 7:48 PM GMT</t>
         </is>
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E328" s="5" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F328" s="5" t="inlineStr">
         <is>
@@ -11902,26 +11902,26 @@
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B329" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05T01:57:00Z</t>
+          <t>2026-02-14T22:07:00Z</t>
         </is>
       </c>
       <c r="C329" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 3:35 AM GMT</t>
+          <t>Feb 14, 2026 10:09 PM GMT</t>
         </is>
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E329" s="5" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F329" s="5" t="inlineStr">
         <is>
@@ -11937,21 +11937,21 @@
       </c>
       <c r="B330" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - SGP</t>
         </is>
       </c>
       <c r="E330" s="5" t="n">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="F330" s="5" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
       </c>
       <c r="B331" s="5" t="inlineStr">
         <is>
-          <t>2026-02-04T23:58:00Z</t>
+          <t>2026-02-05T16:28:00Z</t>
         </is>
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>Feb 05, 2026 1:26 AM GMT</t>
+          <t>Feb 05, 2026 9:10 PM GMT</t>
         </is>
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - SGP</t>
         </is>
       </c>
       <c r="E331" s="5" t="n">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="F331" s="5" t="inlineStr">
         <is>
@@ -11997,25 +11997,25 @@
       </c>
       <c r="B332" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E332" s="5" t="n">
-        <v>4234</v>
+        <v>127</v>
       </c>
       <c r="F332" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -12027,85 +12027,85 @@
       </c>
       <c r="B333" s="5" t="inlineStr">
         <is>
-          <t>2026-01-30T19:08:00Z</t>
+          <t>2026-02-05T04:56:00Z</t>
         </is>
       </c>
       <c r="C333" s="5" t="inlineStr">
         <is>
-          <t>Feb 02, 2026 5:42 PM GMT</t>
+          <t>Feb 05, 2026 7:03 AM GMT</t>
         </is>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - EMEA</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E333" s="5" t="n">
-        <v>4234</v>
+        <v>127</v>
       </c>
       <c r="F333" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B334" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:46:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:47 PM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E334" s="5" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F334" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B335" s="5" t="inlineStr">
         <is>
-          <t>2026-01-27T14:45:00Z</t>
+          <t>2026-02-05T01:57:00Z</t>
         </is>
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t>Jan 27, 2026 2:46 PM GMT</t>
+          <t>Feb 05, 2026 3:35 AM GMT</t>
         </is>
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E335" s="5" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F335" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -12117,25 +12117,25 @@
       </c>
       <c r="B336" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C336" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E336" s="5" t="n">
-        <v>1595</v>
+        <v>88</v>
       </c>
       <c r="F336" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -12147,25 +12147,25 @@
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
-          <t>2026-01-23T23:57:00Z</t>
+          <t>2026-02-04T23:58:00Z</t>
         </is>
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>Jan 25, 2026 2:32 AM GMT</t>
+          <t>Feb 05, 2026 1:26 AM GMT</t>
         </is>
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E337" s="5" t="n">
-        <v>1595</v>
+        <v>88</v>
       </c>
       <c r="F337" s="5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
     </row>
@@ -12177,21 +12177,21 @@
       </c>
       <c r="B338" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T16:24:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C338" s="5" t="inlineStr">
         <is>
-          <t>Jan 20, 2026 3:26 AM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
         </is>
       </c>
       <c r="E338" s="5" t="n">
-        <v>4982</v>
+        <v>4234</v>
       </c>
       <c r="F338" s="5" t="inlineStr">
         <is>
@@ -12202,26 +12202,26 @@
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>2026-01-16T15:14:00Z</t>
+          <t>2026-01-30T19:08:00Z</t>
         </is>
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:15 PM GMT</t>
+          <t>Feb 02, 2026 5:42 PM GMT</t>
         </is>
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
       <c r="E339" s="5" t="n">
-        <v>1</v>
+        <v>4234</v>
       </c>
       <c r="F339" s="5" t="inlineStr">
         <is>
@@ -12232,26 +12232,26 @@
     <row r="340">
       <c r="A340" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B340" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T21:13:00Z</t>
+          <t>2026-01-27T14:46:00Z</t>
         </is>
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>Jan 16, 2026 3:03 PM GMT</t>
+          <t>Jan 27, 2026 2:47 PM GMT</t>
         </is>
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / ams-sast-aviator</t>
+          <t>Fortify on Demand API - FedRAMP</t>
         </is>
       </c>
       <c r="E340" s="5" t="n">
-        <v>1070</v>
+        <v>1</v>
       </c>
       <c r="F340" s="5" t="inlineStr">
         <is>
@@ -12267,17 +12267,17 @@
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>2026-01-15T04:24:00Z</t>
+          <t>2026-01-27T14:45:00Z</t>
         </is>
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
-          <t>Jan 15, 2026 4:25 AM GMT</t>
+          <t>Jan 27, 2026 2:46 PM GMT</t>
         </is>
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand - Vulncat</t>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
         </is>
       </c>
       <c r="E341" s="5" t="n">
@@ -12292,26 +12292,26 @@
     <row r="342">
       <c r="A342" s="5" t="inlineStr">
         <is>
-          <t>Outage</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B342" s="5" t="inlineStr">
         <is>
-          <t>2026-01-10T15:08:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C342" s="5" t="inlineStr">
         <is>
-          <t>Jan 10, 2026 3:10 PM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>SAST Aviator / eu-sast-aviator</t>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
         </is>
       </c>
       <c r="E342" s="5" t="n">
-        <v>2</v>
+        <v>1595</v>
       </c>
       <c r="F342" s="5" t="inlineStr">
         <is>
@@ -12327,21 +12327,21 @@
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-23T23:57:00Z</t>
         </is>
       </c>
       <c r="C343" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 25, 2026 2:32 AM GMT</t>
         </is>
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - AMS</t>
+          <t>Fortify on Demand API - AMS</t>
         </is>
       </c>
       <c r="E343" s="5" t="n">
-        <v>140</v>
+        <v>1595</v>
       </c>
       <c r="F343" s="5" t="inlineStr">
         <is>
@@ -12357,21 +12357,21 @@
       </c>
       <c r="B344" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T04:54:00Z</t>
+          <t>2026-01-16T16:24:00Z</t>
         </is>
       </c>
       <c r="C344" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 7:14 AM GMT</t>
+          <t>Jan 20, 2026 3:26 AM GMT</t>
         </is>
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - AMS</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E344" s="5" t="n">
-        <v>140</v>
+        <v>4982</v>
       </c>
       <c r="F344" s="5" t="inlineStr">
         <is>
@@ -12382,26 +12382,26 @@
     <row r="345">
       <c r="A345" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B345" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-16T15:14:00Z</t>
         </is>
       </c>
       <c r="C345" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 16, 2026 3:15 PM GMT</t>
         </is>
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+          <t>SAST Aviator / eu-sast-aviator</t>
         </is>
       </c>
       <c r="E345" s="5" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="F345" s="5" t="inlineStr">
         <is>
@@ -12417,21 +12417,21 @@
       </c>
       <c r="B346" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T01:13:00Z</t>
+          <t>2026-01-15T21:13:00Z</t>
         </is>
       </c>
       <c r="C346" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 3:30 AM GMT</t>
+          <t>Jan 16, 2026 3:03 PM GMT</t>
         </is>
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand API - FedRAMP</t>
+          <t>SAST Aviator / ams-sast-aviator</t>
         </is>
       </c>
       <c r="E346" s="5" t="n">
-        <v>137</v>
+        <v>1070</v>
       </c>
       <c r="F346" s="5" t="inlineStr">
         <is>
@@ -12442,26 +12442,26 @@
     <row r="347">
       <c r="A347" s="5" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Outage</t>
         </is>
       </c>
       <c r="B347" s="5" t="inlineStr">
         <is>
-          <t>2026-01-08T00:24:00Z</t>
+          <t>2026-01-15T04:24:00Z</t>
         </is>
       </c>
       <c r="C347" s="5" t="inlineStr">
         <is>
-          <t>Jan 08, 2026 1:02 AM GMT</t>
+          <t>Jan 15, 2026 4:25 AM GMT</t>
         </is>
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>Fortify on Demand Tenant Portal - EMEA</t>
+          <t>Fortify on Demand - Vulncat</t>
         </is>
       </c>
       <c r="E347" s="5" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="F347" s="5" t="inlineStr">
         <is>
@@ -12472,37 +12472,217 @@
     <row r="348">
       <c r="A348" s="5" t="inlineStr">
         <is>
+          <t>Outage</t>
+        </is>
+      </c>
+      <c r="B348" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-10T15:08:00Z</t>
+        </is>
+      </c>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>Jan 10, 2026 3:10 PM GMT</t>
+        </is>
+      </c>
+      <c r="D348" s="5" t="inlineStr">
+        <is>
+          <t>SAST Aviator / eu-sast-aviator</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F348" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="inlineStr">
+        <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B348" s="5" t="inlineStr">
+      <c r="B349" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D349" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - AMS</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F349" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B350" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T04:54:00Z</t>
+        </is>
+      </c>
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 7:14 AM GMT</t>
+        </is>
+      </c>
+      <c r="D350" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - AMS</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F350" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B351" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C351" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D351" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F351" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B352" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T01:13:00Z</t>
+        </is>
+      </c>
+      <c r="C352" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 3:30 AM GMT</t>
+        </is>
+      </c>
+      <c r="D352" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand API - FedRAMP</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F352" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B353" s="5" t="inlineStr">
         <is>
           <t>2026-01-08T00:24:00Z</t>
         </is>
       </c>
-      <c r="C348" s="5" t="inlineStr">
+      <c r="C353" s="5" t="inlineStr">
         <is>
           <t>Jan 08, 2026 1:02 AM GMT</t>
         </is>
       </c>
-      <c r="D348" s="5" t="inlineStr">
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>Fortify on Demand Tenant Portal - EMEA</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F353" s="5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="B354" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08T00:24:00Z</t>
+        </is>
+      </c>
+      <c r="C354" s="5" t="inlineStr">
+        <is>
+          <t>Jan 08, 2026 1:02 AM GMT</t>
+        </is>
+      </c>
+      <c r="D354" s="5" t="inlineStr">
         <is>
           <t>Fortify on Demand API - EMEA</t>
         </is>
       </c>
-      <c r="E348" s="5" t="n">
+      <c r="E354" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F348" s="5" t="inlineStr">
+      <c r="F354" s="5" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" s="11" t="inlineStr">
-        <is>
-          <t>Report revised: October 02, 2026</t>
+    <row r="355">
+      <c r="A355" s="11" t="inlineStr">
+        <is>
+          <t>Report revised: October 16, 2026</t>
         </is>
       </c>
     </row>
@@ -12955,7 +13135,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Last updated: October 2, 2026 (Monthly update; Sep 2026 finalized; added Sep 17-30 events and missed Sep 1-5 Vulncat entries; Oct 2026 stub added; all BST times converted to GMT).</t>
+          <t>Last updated: October 16, 2026 (Mid-month update; added Oct 3-12 service degradation events; Oct partial through Oct 15; 0 core outages in Oct to date; all BST times converted to GMT).</t>
         </is>
       </c>
     </row>
@@ -13715,7 +13895,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>Last updated: October 2, 2026</t>
+          <t>Last updated: October 16, 2026</t>
         </is>
       </c>
     </row>
